--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -14,7 +14,12 @@
     <sheet name="JULHO.26 REVISADO" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="LISTA CONTABILIDADE" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$K$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$187</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -188,7 +193,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -246,6 +251,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="5" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -635,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B41"/>
+  <dimension ref="A1:B43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -788,55 +794,38 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
+          <t>JÁ DEFINIDO PELA EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="17" customHeight="1">
+      <c r="A22" s="4" t="inlineStr"/>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>AGNOR: mantida a comissão fixa de R$ 2.000,00 — a linha COMPLEMENTO / COMISSÃO PDV calcula sozinha a diferença (R$ 1.090,49) sobre o apurado de R$ 909,51.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="17" customHeight="1">
+      <c r="A23" s="4" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>JOEL: esteve de férias em agosto/2026 — por isso a venda e a comissão do mês ficaram baixas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" s="4" t="inlineStr"/>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>CAMILA: contratada recentemente; agosto é o primeiro mês completo, com salário integral de R$ 1.621,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="17" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="17" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B25" s="6" t="inlineStr">
-        <is>
-          <t>CAMILA: em julho o salário foi proporcional (R$ 595,00); em agosto está lançado o mês cheio (R$ 1.621,00) — confirmar.</t>
         </is>
       </c>
     </row>
@@ -848,7 +837,7 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>AGNOR: em julho recebeu comissão fixa de R$ 2.000,00 e o apurado de agosto é R$ 909,51 — informar se mantém o fixo (linha COMPLEMENTO / COMISSÃO PDV).</t>
+          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
         </is>
       </c>
     </row>
@@ -860,7 +849,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>DEAN: apurou R$ 975,65 de comissão em agosto, mas não vinha recebendo comissão em folha — confirmar.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
         </is>
       </c>
     </row>
@@ -872,7 +861,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>JOEL: vendeu apenas R$ 5.057,69 em agosto (comissão R$ 103,31) — verificar férias, afastamento ou código de vendedor.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -884,7 +873,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+          <t>JOEL: informar o período de FÉRIAS de agosto/2026 para a contabilidade calcular férias, 1/3, média de comissões e o salário proporcional.</t>
         </is>
       </c>
     </row>
@@ -896,7 +885,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+          <t>DEAN: apurou R$ 975,65 de comissão em agosto, mas não vinha recebendo comissão em folha — confirmar.</t>
         </is>
       </c>
     </row>
@@ -908,29 +897,38 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
+          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="inlineStr">
+        <is>
           <t>DSR de julho/2026 foi calculado com o fator de agosto (5/26) em vez de 4/27 — ver aba JULHO.26 REVISADO e decidir se ajusta em setembro.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>OBSERVAÇÃO TÉCNICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="4" t="inlineStr"/>
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>ABAS DO ARQUIVO</t>
+          <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
@@ -938,15 +936,14 @@
       <c r="A35" s="4" t="inlineStr"/>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
+          <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>ABAS DO ARQUIVO</t>
         </is>
       </c>
     </row>
@@ -954,7 +951,7 @@
       <c r="A37" s="4" t="inlineStr"/>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -962,7 +959,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
         </is>
       </c>
     </row>
@@ -970,24 +967,41 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="4" t="inlineStr"/>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="4" t="inlineStr"/>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
           <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="7" t="inlineStr">
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>Documento gerado a partir da planilha CONISSÕES PLAN.AGOSTO/JULHO ARRAIAL 2026 e do relatório de comissões do InovaFarma.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
     <mergeCell ref="A34:B34"/>
@@ -1002,7 +1016,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1095,9 +1109,8 @@
           <t>Dias do mês</t>
         </is>
       </c>
-      <c r="B9" s="11">
-        <f>B7/B8</f>
-        <v/>
+      <c r="B9" s="9" t="n">
+        <v>31</v>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
@@ -1126,12 +1139,14 @@
           <t>Dias úteis (inclui sábados)</t>
         </is>
       </c>
-      <c r="B11" s="9" t="n">
-        <v>26</v>
-      </c>
-      <c r="C11" s="10">
-        <f>31-5.</f>
-        <v/>
+      <c r="B11" s="9">
+        <f>B9-B10</f>
+        <v/>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Dias do mês menos domingos e feriados.</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1140,10 +1155,13 @@
           <t>Fator DSR (domingos ÷ dias úteis)</t>
         </is>
       </c>
-      <c r="B12" s="9" t="n"/>
+      <c r="B12" s="11">
+        <f>B10/B11</f>
+        <v/>
+      </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Fórmula: =B7/B8. Usado na rubrica REPOUSO REMUNERADO/DSR.</t>
+          <t>Domingos ÷ dias úteis. Usado na rubrica REPOUSO REMUNERADO / DSR da aba HOLERITE AGO.26.</t>
         </is>
       </c>
     </row>
@@ -1232,54 +1250,69 @@
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
+          <t>Comissão fixa acordada — AGNOR</t>
+        </is>
+      </c>
+      <c r="B19" s="12" t="n">
+        <v>2000</v>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
+        <is>
+          <t>Valor fixo mantido pela empresa. O complemento é a diferença entre este valor e a comissão apurada no InovaFarma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
           <t>Desconto vale-transporte 6%</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n">
+      <c r="B20" s="12" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="C19" s="10" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>Valor praticado em jul/2026. 6% do salário base daria R$ 97,26 — CONFERIR.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>INSS / IRRF</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="B21" s="9" t="inlineStr">
-        <is>
-          <t>a calcular</t>
-        </is>
-      </c>
-      <c r="C21" s="10" t="inlineStr">
-        <is>
-          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>a calcular</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
           <t>IRRF</t>
         </is>
       </c>
-      <c r="B22" s="9" t="inlineStr">
+      <c r="B23" s="9" t="inlineStr">
         <is>
           <t>a calcular</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>Calculado pela contabilidade após dedução do INSS e dependentes.</t>
         </is>
@@ -1290,8 +1323,8 @@
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:C8"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1790,11 +1823,12 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>Atenção JOEL: venda bruta de apenas R$ 5.057,69 em agosto (jul/26 foi muito superior) — verificar férias, afastamento ou troca de código de vendedor.</t>
+          <t>JOEL: venda bruta de apenas R$ 5.057,69 porque esteve de FÉRIAS em agosto/2026 — a comissão apurada (R$ 103,31) corresponde só aos dias trabalhados.</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A4:J12"/>
   <mergeCells count="6">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
@@ -1813,7 +1847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K40"/>
+  <dimension ref="A1:K42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1906,132 +1940,142 @@
           <t>PROVENTOS</t>
         </is>
       </c>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="30" t="n">
+      <c r="B6" s="31" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="30" t="n">
+      <c r="C6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="30" t="n">
+      <c r="D6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="E6" s="30" t="n">
+      <c r="E6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="F6" s="30" t="n">
+      <c r="F6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="30" t="n">
+      <c r="G6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="H6" s="30" t="n">
+      <c r="H6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="I6" s="30" t="n">
+      <c r="I6" s="31" t="n">
         <v>1621</v>
       </c>
-      <c r="J6" s="31">
+      <c r="J6" s="32">
         <f>SUM(B6:I6)</f>
         <v/>
       </c>
-      <c r="K6" s="32" t="inlineStr">
-        <is>
-          <t>Piso 2026 R$ 1.621,00. CAMILA: 1º mês completo (em jul/26 foi proporcional R$ 595,00) — confirmar data de admissão.</t>
+      <c r="K6" s="33" t="inlineStr">
+        <is>
+          <t>Piso 2026 R$ 1.621,00. CAMILA: admitida em jul/26 (salário proporcional naquele mês); agosto é o 1º mês completo. JOEL: ajustar aos dias trabalhados por conta das férias.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="30" t="n"/>
-      <c r="C7" s="30" t="n"/>
-      <c r="D7" s="30" t="n">
+      <c r="B7" s="31" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="31" t="n">
         <v>350</v>
       </c>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
-      <c r="H7" s="30" t="n"/>
-      <c r="I7" s="30" t="n"/>
-      <c r="J7" s="31">
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
+      <c r="H7" s="31" t="n"/>
+      <c r="I7" s="31" t="n"/>
+      <c r="J7" s="32">
         <f>SUM(B7:I7)</f>
         <v/>
       </c>
-      <c r="K7" s="32" t="inlineStr">
+      <c r="K7" s="33" t="inlineStr">
         <is>
           <t>Conforme apontamento do ponto (jul/26: EDEY R$ 350,00).</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n"/>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="33" t="n"/>
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n"/>
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n"/>
       <c r="J8" s="20">
         <f>SUM(B8:I8)</f>
         <v/>
       </c>
-      <c r="K8" s="32" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>PREENCHER com o apurado no ponto de agosto/2026.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="34">
+      <c r="B9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F5</f>
         <v/>
       </c>
-      <c r="C9" s="34">
+      <c r="C9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F6</f>
         <v/>
       </c>
-      <c r="D9" s="34">
+      <c r="D9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F7</f>
         <v/>
       </c>
-      <c r="E9" s="34">
+      <c r="E9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F8</f>
         <v/>
       </c>
-      <c r="F9" s="34">
+      <c r="F9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F9</f>
         <v/>
       </c>
-      <c r="G9" s="34">
+      <c r="G9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F10</f>
         <v/>
       </c>
-      <c r="H9" s="34">
+      <c r="H9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F11</f>
         <v/>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F12</f>
         <v/>
       </c>
@@ -2039,33 +2083,36 @@
         <f>SUM(B9:I9)</f>
         <v/>
       </c>
-      <c r="K9" s="32" t="inlineStr">
-        <is>
-          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). DEAN: R$ 975,65 apurado — em jul/26 não houve lançamento de comissão para ele; confirmar.</t>
+      <c r="K9" s="33" t="inlineStr">
+        <is>
+          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo. DEAN: R$ 975,65 apurado — em jul/26 não houve lançamento de comissão para ele; confirmar.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>COMPLEMENTO / COMISSÃO PDV</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n"/>
-      <c r="D10" s="33" t="n"/>
-      <c r="E10" s="33" t="n"/>
-      <c r="F10" s="33" t="n"/>
-      <c r="G10" s="33" t="n"/>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="33" t="n"/>
-      <c r="J10" s="20">
+      <c r="B10" s="31" t="n"/>
+      <c r="C10" s="31">
+        <f>ROUND(PARÂMETROS!$B$19-C9,2)</f>
+        <v/>
+      </c>
+      <c r="D10" s="31" t="n"/>
+      <c r="E10" s="31" t="n"/>
+      <c r="F10" s="31" t="n"/>
+      <c r="G10" s="31" t="n"/>
+      <c r="H10" s="31" t="n"/>
+      <c r="I10" s="31" t="n"/>
+      <c r="J10" s="32">
         <f>SUM(B10:I10)</f>
         <v/>
       </c>
-      <c r="K10" s="32" t="inlineStr">
-        <is>
-          <t>PREENCHER: PDV antigos e complemento de comissão fixa acordada (ex.: AGNOR vinha recebendo R$ 2.000,00 fixos em jul/26).</t>
+      <c r="K10" s="33" t="inlineStr">
+        <is>
+          <t>AGNOR: complemento até a comissão fixa de R$ 2.000,00 (parâmetro na aba PARÂMETROS). Demais: preencher com PDV antigos, se houver.</t>
         </is>
       </c>
     </row>
@@ -2110,785 +2157,860 @@
         <f>SUM(B11:I11)</f>
         <v/>
       </c>
-      <c r="K11" s="32" t="inlineStr">
+      <c r="K11" s="33" t="inlineStr">
         <is>
           <t>Base do DSR junto com as horas extras.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B12" s="35">
-        <f>ROUND((B11+B8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="C12" s="35">
-        <f>ROUND((C11+C8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="D12" s="35">
-        <f>ROUND((D11+D8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="E12" s="35">
-        <f>ROUND((E11+E8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="F12" s="35">
-        <f>ROUND((F11+F8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="G12" s="35">
-        <f>ROUND((G11+G8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="H12" s="35">
-        <f>ROUND((H11+H8)*PARÂMETROS!$B$9,2)</f>
-        <v/>
-      </c>
-      <c r="I12" s="35">
-        <f>ROUND((I11+I8)*PARÂMETROS!$B$9,2)</f>
+      <c r="B12" s="36">
+        <f>ROUND((B11+B8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="C12" s="36">
+        <f>ROUND((C11+C8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="D12" s="36">
+        <f>ROUND((D11+D8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="E12" s="36">
+        <f>ROUND((E11+E8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="F12" s="36">
+        <f>ROUND((F11+F8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="G12" s="36">
+        <f>ROUND((G11+G8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="36">
+        <f>ROUND((H11+H8)*PARÂMETROS!$B$12,2)</f>
+        <v/>
+      </c>
+      <c r="I12" s="36">
+        <f>ROUND((I11+I8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
       <c r="J12" s="20">
         <f>SUM(B12:I12)</f>
         <v/>
       </c>
-      <c r="K12" s="32">
+      <c r="K12" s="33">
         <f> (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026 (fator na aba PARÂMETROS).</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B13" s="30" t="n"/>
-      <c r="C13" s="30" t="n">
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="31" t="n">
         <v>810.5</v>
       </c>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n">
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n">
         <v>810.5</v>
       </c>
-      <c r="H13" s="30" t="n"/>
-      <c r="I13" s="30" t="n"/>
-      <c r="J13" s="31">
+      <c r="H13" s="31" t="n"/>
+      <c r="I13" s="31" t="n"/>
+      <c r="J13" s="32">
         <f>SUM(B13:I13)</f>
         <v/>
       </c>
-      <c r="K13" s="32" t="inlineStr">
+      <c r="K13" s="33" t="inlineStr">
         <is>
           <t>AGNOR e SARA — valor recorrente de jul/26.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="B14" s="30" t="n"/>
-      <c r="C14" s="30" t="n"/>
-      <c r="D14" s="30" t="n"/>
-      <c r="E14" s="30" t="n"/>
-      <c r="F14" s="30" t="n">
+      <c r="B14" s="31" t="n"/>
+      <c r="C14" s="31" t="n"/>
+      <c r="D14" s="31" t="n"/>
+      <c r="E14" s="31" t="n"/>
+      <c r="F14" s="31" t="n">
         <v>307.99</v>
       </c>
-      <c r="G14" s="30" t="n"/>
-      <c r="H14" s="30" t="n"/>
-      <c r="I14" s="30" t="n">
+      <c r="G14" s="31" t="n"/>
+      <c r="H14" s="31" t="n"/>
+      <c r="I14" s="31" t="n">
         <v>307.99</v>
       </c>
-      <c r="J14" s="31">
+      <c r="J14" s="32">
         <f>SUM(B14:I14)</f>
         <v/>
       </c>
-      <c r="K14" s="32" t="inlineStr">
+      <c r="K14" s="33" t="inlineStr">
         <is>
           <t>VALÉRIA e NATI — valor recorrente de jul/26; confirmar se a meta foi batida em agosto.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="33" t="n"/>
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="34" t="n"/>
       <c r="J15" s="20">
         <f>SUM(B15:I15)</f>
         <v/>
       </c>
-      <c r="K15" s="32" t="inlineStr">
+      <c r="K15" s="33" t="inlineStr">
         <is>
           <t>PREENCHER conforme apuração de metas de agosto.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="33" t="n"/>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="33" t="n"/>
-      <c r="G16" s="33" t="n"/>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="33" t="n"/>
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n"/>
+      <c r="G16" s="34" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
       <c r="J16" s="20">
         <f>SUM(B16:I16)</f>
         <v/>
       </c>
-      <c r="K16" s="32" t="inlineStr">
+      <c r="K16" s="33" t="inlineStr">
         <is>
           <t>PREENCHER conforme apuração de pré-vencidos de agosto.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="30" t="inlineStr">
+        <is>
+          <t>FÉRIAS (DIAS GOZADOS)</t>
+        </is>
+      </c>
+      <c r="B17" s="31" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
+      <c r="H17" s="31" t="n"/>
+      <c r="I17" s="31" t="n"/>
+      <c r="J17" s="32">
+        <f>SUM(B17:I17)</f>
+        <v/>
+      </c>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>JOEL esteve de FÉRIAS em agosto/2026 — informar o período para a contabilidade calcular férias, média de comissões e o salário proporcional aos dias trabalhados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="30" t="inlineStr">
+        <is>
+          <t>1/3 CONSTITUCIONAL DE FÉRIAS</t>
+        </is>
+      </c>
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="31" t="n"/>
+      <c r="D18" s="31" t="n"/>
+      <c r="E18" s="31" t="n"/>
+      <c r="F18" s="31" t="n"/>
+      <c r="G18" s="31" t="n"/>
+      <c r="H18" s="31" t="n"/>
+      <c r="I18" s="31" t="n"/>
+      <c r="J18" s="32">
+        <f>SUM(B18:I18)</f>
+        <v/>
+      </c>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="B17" s="34">
+      <c r="B19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G5</f>
         <v/>
       </c>
-      <c r="C17" s="34">
+      <c r="C19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G6</f>
         <v/>
       </c>
-      <c r="D17" s="34">
+      <c r="D19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G7</f>
         <v/>
       </c>
-      <c r="E17" s="34">
+      <c r="E19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G8</f>
         <v/>
       </c>
-      <c r="F17" s="34">
+      <c r="F19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G9</f>
         <v/>
       </c>
-      <c r="G17" s="34">
+      <c r="G19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G10</f>
         <v/>
       </c>
-      <c r="H17" s="34">
+      <c r="H19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G11</f>
         <v/>
       </c>
-      <c r="I17" s="34">
+      <c r="I19" s="35">
         <f>'BASE INOVAFARMA AGO.26'!G12</f>
-        <v/>
-      </c>
-      <c r="J17" s="20">
-        <f>SUM(B17:I17)</f>
-        <v/>
-      </c>
-      <c r="K17" s="32" t="inlineStr">
-        <is>
-          <t>Incentivo de injetáveis apurado no InovaFarma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="29" t="inlineStr">
-        <is>
-          <t>INCENTIVO VITAMINAS</t>
-        </is>
-      </c>
-      <c r="B18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H5</f>
-        <v/>
-      </c>
-      <c r="C18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H6</f>
-        <v/>
-      </c>
-      <c r="D18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H7</f>
-        <v/>
-      </c>
-      <c r="E18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H8</f>
-        <v/>
-      </c>
-      <c r="F18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H9</f>
-        <v/>
-      </c>
-      <c r="G18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H10</f>
-        <v/>
-      </c>
-      <c r="H18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H11</f>
-        <v/>
-      </c>
-      <c r="I18" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!H12</f>
-        <v/>
-      </c>
-      <c r="J18" s="20">
-        <f>SUM(B18:I18)</f>
-        <v/>
-      </c>
-      <c r="K18" s="32" t="inlineStr">
-        <is>
-          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="29" t="inlineStr">
-        <is>
-          <t>OUTROS INCENTIVOS</t>
-        </is>
-      </c>
-      <c r="B19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I5</f>
-        <v/>
-      </c>
-      <c r="C19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I6</f>
-        <v/>
-      </c>
-      <c r="D19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I7</f>
-        <v/>
-      </c>
-      <c r="E19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I8</f>
-        <v/>
-      </c>
-      <c r="F19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I9</f>
-        <v/>
-      </c>
-      <c r="G19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I10</f>
-        <v/>
-      </c>
-      <c r="H19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I11</f>
-        <v/>
-      </c>
-      <c r="I19" s="34">
-        <f>'BASE INOVAFARMA AGO.26'!I12</f>
         <v/>
       </c>
       <c r="J19" s="20">
         <f>SUM(B19:I19)</f>
         <v/>
       </c>
-      <c r="K19" s="32" t="inlineStr">
-        <is>
-          <t>Populares, oficinais e similar normal.</t>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>Incentivo de injetáveis apurado no InovaFarma.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE PROVENTOS</t>
-        </is>
-      </c>
-      <c r="B20" s="20">
-        <f>SUM(B6:B19)-B9-B10</f>
-        <v/>
-      </c>
-      <c r="C20" s="20">
-        <f>SUM(C6:C19)-C9-C10</f>
-        <v/>
-      </c>
-      <c r="D20" s="20">
-        <f>SUM(D6:D19)-D9-D10</f>
-        <v/>
-      </c>
-      <c r="E20" s="20">
-        <f>SUM(E6:E19)-E9-E10</f>
-        <v/>
-      </c>
-      <c r="F20" s="20">
-        <f>SUM(F6:F19)-F9-F10</f>
-        <v/>
-      </c>
-      <c r="G20" s="20">
-        <f>SUM(G6:G19)-G9-G10</f>
-        <v/>
-      </c>
-      <c r="H20" s="20">
-        <f>SUM(H6:H19)-H9-H10</f>
-        <v/>
-      </c>
-      <c r="I20" s="20">
-        <f>SUM(I6:I19)-I9-I10</f>
+      <c r="A20" s="30" t="inlineStr">
+        <is>
+          <t>INCENTIVO VITAMINAS</t>
+        </is>
+      </c>
+      <c r="B20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H5</f>
+        <v/>
+      </c>
+      <c r="C20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H6</f>
+        <v/>
+      </c>
+      <c r="D20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H7</f>
+        <v/>
+      </c>
+      <c r="E20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H8</f>
+        <v/>
+      </c>
+      <c r="F20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H9</f>
+        <v/>
+      </c>
+      <c r="G20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H10</f>
+        <v/>
+      </c>
+      <c r="H20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H11</f>
+        <v/>
+      </c>
+      <c r="I20" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!H12</f>
         <v/>
       </c>
       <c r="J20" s="20">
         <f>SUM(B20:I20)</f>
         <v/>
       </c>
-      <c r="K20" s="32" t="inlineStr">
-        <is>
-          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba comissão InovaFarma + complemento PDV).</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>DESCONTOS  (lançar com sinal negativo)</t>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>Grupo APLICAÇÃO E VITAMINAS INCENTIVO no InovaFarma.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="30" t="inlineStr">
+        <is>
+          <t>OUTROS INCENTIVOS</t>
+        </is>
+      </c>
+      <c r="B21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I5</f>
+        <v/>
+      </c>
+      <c r="C21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I6</f>
+        <v/>
+      </c>
+      <c r="D21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I7</f>
+        <v/>
+      </c>
+      <c r="E21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I8</f>
+        <v/>
+      </c>
+      <c r="F21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I9</f>
+        <v/>
+      </c>
+      <c r="G21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I10</f>
+        <v/>
+      </c>
+      <c r="H21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I11</f>
+        <v/>
+      </c>
+      <c r="I21" s="35">
+        <f>'BASE INOVAFARMA AGO.26'!I12</f>
+        <v/>
+      </c>
+      <c r="J21" s="20">
+        <f>SUM(B21:I21)</f>
+        <v/>
+      </c>
+      <c r="K21" s="33" t="inlineStr">
+        <is>
+          <t>Populares, oficinais e similar normal.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
-        <is>
-          <t>ADIANTAMENTO / VALES</t>
-        </is>
-      </c>
-      <c r="B22" s="33" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="33" t="n"/>
-      <c r="E22" s="33" t="n"/>
-      <c r="F22" s="33" t="n"/>
-      <c r="G22" s="33" t="n"/>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="B22" s="20">
+        <f>SUM(B6:B21)-B9-B10</f>
+        <v/>
+      </c>
+      <c r="C22" s="20">
+        <f>SUM(C6:C21)-C9-C10</f>
+        <v/>
+      </c>
+      <c r="D22" s="20">
+        <f>SUM(D6:D21)-D9-D10</f>
+        <v/>
+      </c>
+      <c r="E22" s="20">
+        <f>SUM(E6:E21)-E9-E10</f>
+        <v/>
+      </c>
+      <c r="F22" s="20">
+        <f>SUM(F6:F21)-F9-F10</f>
+        <v/>
+      </c>
+      <c r="G22" s="20">
+        <f>SUM(G6:G21)-G9-G10</f>
+        <v/>
+      </c>
+      <c r="H22" s="20">
+        <f>SUM(H6:H21)-H9-H10</f>
+        <v/>
+      </c>
+      <c r="I22" s="20">
+        <f>SUM(I6:I21)-I9-I10</f>
+        <v/>
+      </c>
       <c r="J22" s="20">
         <f>SUM(B22:I22)</f>
         <v/>
       </c>
-      <c r="K22" s="32" t="inlineStr">
-        <is>
-          <t>PREENCHER com os vales adiantados durante agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="29" t="inlineStr">
-        <is>
-          <t>ADIANT. VALES INCENT. E APLIC.</t>
-        </is>
-      </c>
-      <c r="B23" s="36">
-        <f>-(B17+B18+B19)</f>
-        <v/>
-      </c>
-      <c r="C23" s="36">
-        <f>-(C17+C18+C19)</f>
-        <v/>
-      </c>
-      <c r="D23" s="36">
-        <f>-(D17+D18+D19)</f>
-        <v/>
-      </c>
-      <c r="E23" s="36">
-        <f>-(E17+E18+E19)</f>
-        <v/>
-      </c>
-      <c r="F23" s="36">
-        <f>-(F17+F18+F19)</f>
-        <v/>
-      </c>
-      <c r="G23" s="36">
-        <f>-(G17+G18+G19)</f>
-        <v/>
-      </c>
-      <c r="H23" s="36">
-        <f>-(H17+H18+H19)</f>
-        <v/>
-      </c>
-      <c r="I23" s="36">
-        <f>-(I17+I18+I19)</f>
-        <v/>
-      </c>
-      <c r="J23" s="31">
-        <f>SUM(B23:I23)</f>
-        <v/>
-      </c>
-      <c r="K23" s="32" t="inlineStr">
-        <is>
-          <t>Estorno dos incentivos já adiantados em dinheiro no mês (mesmo critério de jul/26). AJUSTAR se algum incentivo não foi adiantado.</t>
-        </is>
-      </c>
+      <c r="K22" s="33" t="inlineStr">
+        <is>
+          <t>Soma das rubricas acima (a linha COMISSÃO TOTAL já engloba comissão InovaFarma + complemento PDV).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
+          <t>DESCONTOS  (lançar com sinal negativo)</t>
+        </is>
+      </c>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="29" t="n"/>
+      <c r="F23" s="29" t="n"/>
+      <c r="G23" s="29" t="n"/>
+      <c r="H23" s="29" t="n"/>
+      <c r="I23" s="29" t="n"/>
+      <c r="J23" s="29" t="n"/>
+      <c r="K23" s="29" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>CONVÊNIO</t>
-        </is>
-      </c>
-      <c r="B24" s="33" t="n"/>
-      <c r="C24" s="33" t="n"/>
-      <c r="D24" s="33" t="n"/>
-      <c r="E24" s="33" t="n"/>
-      <c r="F24" s="33" t="n"/>
-      <c r="G24" s="33" t="n"/>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="33" t="n"/>
+      <c r="A24" s="30" t="inlineStr">
+        <is>
+          <t>ADIANTAMENTO / VALES</t>
+        </is>
+      </c>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
+      <c r="E24" s="34" t="n"/>
+      <c r="F24" s="34" t="n"/>
+      <c r="G24" s="34" t="n"/>
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="34" t="n"/>
       <c r="J24" s="20">
         <f>SUM(B24:I24)</f>
         <v/>
       </c>
-      <c r="K24" s="32" t="inlineStr">
+      <c r="K24" s="33" t="inlineStr">
+        <is>
+          <t>PREENCHER com os vales adiantados durante agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="30" t="inlineStr">
+        <is>
+          <t>ADIANT. VALES INCENT. E APLIC.</t>
+        </is>
+      </c>
+      <c r="B25" s="37">
+        <f>-(B19+B20+B21)</f>
+        <v/>
+      </c>
+      <c r="C25" s="37">
+        <f>-(C19+C20+C21)</f>
+        <v/>
+      </c>
+      <c r="D25" s="37">
+        <f>-(D19+D20+D21)</f>
+        <v/>
+      </c>
+      <c r="E25" s="37">
+        <f>-(E19+E20+E21)</f>
+        <v/>
+      </c>
+      <c r="F25" s="37">
+        <f>-(F19+F20+F21)</f>
+        <v/>
+      </c>
+      <c r="G25" s="37">
+        <f>-(G19+G20+G21)</f>
+        <v/>
+      </c>
+      <c r="H25" s="37">
+        <f>-(H19+H20+H21)</f>
+        <v/>
+      </c>
+      <c r="I25" s="37">
+        <f>-(I19+I20+I21)</f>
+        <v/>
+      </c>
+      <c r="J25" s="32">
+        <f>SUM(B25:I25)</f>
+        <v/>
+      </c>
+      <c r="K25" s="33" t="inlineStr">
+        <is>
+          <t>Estorno dos incentivos já adiantados em dinheiro no mês (mesmo critério de jul/26). AJUSTAR se algum incentivo não foi adiantado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="30" t="inlineStr">
+        <is>
+          <t>CONVÊNIO</t>
+        </is>
+      </c>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="34" t="n"/>
+      <c r="D26" s="34" t="n"/>
+      <c r="E26" s="34" t="n"/>
+      <c r="F26" s="34" t="n"/>
+      <c r="G26" s="34" t="n"/>
+      <c r="H26" s="34" t="n"/>
+      <c r="I26" s="34" t="n"/>
+      <c r="J26" s="20">
+        <f>SUM(B26:I26)</f>
+        <v/>
+      </c>
+      <c r="K26" s="33" t="inlineStr">
         <is>
           <t>PREENCHER (jul/26: AGNOR -300, JOEL -500, VALÉRIA -300, SARA -300).</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="B25" s="33" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="33" t="n"/>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="33" t="n"/>
-      <c r="J25" s="20">
-        <f>SUM(B25:I25)</f>
-        <v/>
-      </c>
-      <c r="K25" s="32" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme o ponto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
-        <is>
-          <t>DESCONTO VALE TRANSPORTE 6%</t>
-        </is>
-      </c>
-      <c r="B26" s="30" t="n"/>
-      <c r="C26" s="30" t="n"/>
-      <c r="D26" s="30" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="E26" s="30" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="F26" s="30" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="G26" s="30" t="n"/>
-      <c r="H26" s="30" t="n"/>
-      <c r="I26" s="30" t="n">
-        <v>-84.29000000000001</v>
-      </c>
-      <c r="J26" s="31">
-        <f>SUM(B26:I26)</f>
-        <v/>
-      </c>
-      <c r="K26" s="32" t="inlineStr">
-        <is>
-          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
-        <is>
-          <t>DESCONTO INSS</t>
-        </is>
-      </c>
-      <c r="B27" s="33" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="33" t="n"/>
-      <c r="G27" s="33" t="n"/>
-      <c r="H27" s="33" t="n"/>
-      <c r="I27" s="33" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="34" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="34" t="n"/>
+      <c r="H27" s="34" t="n"/>
+      <c r="I27" s="34" t="n"/>
       <c r="J27" s="20">
         <f>SUM(B27:I27)</f>
         <v/>
       </c>
-      <c r="K27" s="32" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos (tabela progressiva vigente).</t>
+      <c r="K27" s="33" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme o ponto.</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
-        <is>
-          <t>DESCONTO IRRF</t>
-        </is>
-      </c>
-      <c r="B28" s="33" t="n"/>
-      <c r="C28" s="33" t="n"/>
-      <c r="D28" s="33" t="n"/>
-      <c r="E28" s="33" t="n"/>
-      <c r="F28" s="33" t="n"/>
-      <c r="G28" s="33" t="n"/>
-      <c r="H28" s="33" t="n"/>
-      <c r="I28" s="33" t="n"/>
-      <c r="J28" s="20">
+      <c r="A28" s="30" t="inlineStr">
+        <is>
+          <t>DESCONTO VALE TRANSPORTE 6%</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="n"/>
+      <c r="C28" s="31" t="n"/>
+      <c r="D28" s="31" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="G28" s="31" t="n"/>
+      <c r="H28" s="31" t="n"/>
+      <c r="I28" s="31" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="J28" s="32">
         <f>SUM(B28:I28)</f>
         <v/>
       </c>
-      <c r="K28" s="32" t="inlineStr">
-        <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
+      <c r="K28" s="33" t="inlineStr">
+        <is>
+          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="inlineStr">
-        <is>
-          <t>TOTAL DE DESCONTOS</t>
-        </is>
-      </c>
-      <c r="B29" s="20">
-        <f>SUM(B22:B28)</f>
-        <v/>
-      </c>
-      <c r="C29" s="20">
-        <f>SUM(C22:C28)</f>
-        <v/>
-      </c>
-      <c r="D29" s="20">
-        <f>SUM(D22:D28)</f>
-        <v/>
-      </c>
-      <c r="E29" s="20">
-        <f>SUM(E22:E28)</f>
-        <v/>
-      </c>
-      <c r="F29" s="20">
-        <f>SUM(F22:F28)</f>
-        <v/>
-      </c>
-      <c r="G29" s="20">
-        <f>SUM(G22:G28)</f>
-        <v/>
-      </c>
-      <c r="H29" s="20">
-        <f>SUM(H22:H28)</f>
-        <v/>
-      </c>
-      <c r="I29" s="20">
-        <f>SUM(I22:I28)</f>
-        <v/>
-      </c>
+      <c r="A29" s="30" t="inlineStr">
+        <is>
+          <t>DESCONTO INSS</t>
+        </is>
+      </c>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="34" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="34" t="n"/>
+      <c r="G29" s="34" t="n"/>
+      <c r="H29" s="34" t="n"/>
+      <c r="I29" s="34" t="n"/>
       <c r="J29" s="20">
         <f>SUM(B29:I29)</f>
         <v/>
       </c>
-      <c r="K29" s="32" t="inlineStr"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="28" t="inlineStr">
-        <is>
-          <t>LÍQUIDO</t>
+      <c r="K29" s="33" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos (tabela progressiva vigente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="30" t="inlineStr">
+        <is>
+          <t>DESCONTO IRRF</t>
+        </is>
+      </c>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="34" t="n"/>
+      <c r="E30" s="34" t="n"/>
+      <c r="F30" s="34" t="n"/>
+      <c r="G30" s="34" t="n"/>
+      <c r="H30" s="34" t="n"/>
+      <c r="I30" s="34" t="n"/>
+      <c r="J30" s="20">
+        <f>SUM(B30:I30)</f>
+        <v/>
+      </c>
+      <c r="K30" s="33" t="inlineStr">
+        <is>
+          <t>A CALCULAR PELA CONTABILIDADE.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="15" t="inlineStr">
         <is>
-          <t>LÍQUIDO A RECEBER (05/09/2026)</t>
-        </is>
-      </c>
-      <c r="B31" s="37">
-        <f>B20+B29</f>
-        <v/>
-      </c>
-      <c r="C31" s="37">
-        <f>C20+C29</f>
-        <v/>
-      </c>
-      <c r="D31" s="37">
-        <f>D20+D29</f>
-        <v/>
-      </c>
-      <c r="E31" s="37">
-        <f>E20+E29</f>
-        <v/>
-      </c>
-      <c r="F31" s="37">
-        <f>F20+F29</f>
-        <v/>
-      </c>
-      <c r="G31" s="37">
-        <f>G20+G29</f>
-        <v/>
-      </c>
-      <c r="H31" s="37">
-        <f>H20+H29</f>
-        <v/>
-      </c>
-      <c r="I31" s="37">
-        <f>I20+I29</f>
-        <v/>
-      </c>
-      <c r="J31" s="37">
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="B31" s="20">
+        <f>SUM(B24:B30)</f>
+        <v/>
+      </c>
+      <c r="C31" s="20">
+        <f>SUM(C24:C30)</f>
+        <v/>
+      </c>
+      <c r="D31" s="20">
+        <f>SUM(D24:D30)</f>
+        <v/>
+      </c>
+      <c r="E31" s="20">
+        <f>SUM(E24:E30)</f>
+        <v/>
+      </c>
+      <c r="F31" s="20">
+        <f>SUM(F24:F30)</f>
+        <v/>
+      </c>
+      <c r="G31" s="20">
+        <f>SUM(G24:G30)</f>
+        <v/>
+      </c>
+      <c r="H31" s="20">
+        <f>SUM(H24:H30)</f>
+        <v/>
+      </c>
+      <c r="I31" s="20">
+        <f>SUM(I24:I30)</f>
+        <v/>
+      </c>
+      <c r="J31" s="20">
         <f>SUM(B31:I31)</f>
         <v/>
       </c>
-      <c r="K31" s="32" t="inlineStr">
-        <is>
-          <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
-        </is>
-      </c>
+      <c r="K31" s="33" t="inlineStr"/>
     </row>
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="28" t="inlineStr">
         <is>
+          <t>LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="B32" s="29" t="n"/>
+      <c r="C32" s="29" t="n"/>
+      <c r="D32" s="29" t="n"/>
+      <c r="E32" s="29" t="n"/>
+      <c r="F32" s="29" t="n"/>
+      <c r="G32" s="29" t="n"/>
+      <c r="H32" s="29" t="n"/>
+      <c r="I32" s="29" t="n"/>
+      <c r="J32" s="29" t="n"/>
+      <c r="K32" s="29" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="15" t="inlineStr">
+        <is>
+          <t>LÍQUIDO A RECEBER (05/09/2026)</t>
+        </is>
+      </c>
+      <c r="B33" s="38">
+        <f>B22+B31</f>
+        <v/>
+      </c>
+      <c r="C33" s="38">
+        <f>C22+C31</f>
+        <v/>
+      </c>
+      <c r="D33" s="38">
+        <f>D22+D31</f>
+        <v/>
+      </c>
+      <c r="E33" s="38">
+        <f>E22+E31</f>
+        <v/>
+      </c>
+      <c r="F33" s="38">
+        <f>F22+F31</f>
+        <v/>
+      </c>
+      <c r="G33" s="38">
+        <f>G22+G31</f>
+        <v/>
+      </c>
+      <c r="H33" s="38">
+        <f>H22+H31</f>
+        <v/>
+      </c>
+      <c r="I33" s="38">
+        <f>I22+I31</f>
+        <v/>
+      </c>
+      <c r="J33" s="38">
+        <f>SUM(B33:I33)</f>
+        <v/>
+      </c>
+      <c r="K33" s="33" t="inlineStr">
+        <is>
+          <t>Total de proventos menos descontos. Só fica definitivo depois do INSS/IRRF da contabilidade.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="28" t="inlineStr">
+        <is>
           <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
         </is>
       </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="B34" s="29" t="n"/>
+      <c r="C34" s="29" t="n"/>
+      <c r="D34" s="29" t="n"/>
+      <c r="E34" s="29" t="n"/>
+      <c r="F34" s="29" t="n"/>
+      <c r="G34" s="29" t="n"/>
+      <c r="H34" s="29" t="n"/>
+      <c r="I34" s="29" t="n"/>
+      <c r="J34" s="29" t="n"/>
+      <c r="K34" s="29" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>VALE TRANSPORTE (compra set/26)</t>
         </is>
       </c>
-      <c r="B33" s="33" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="33" t="n"/>
-      <c r="H33" s="33" t="n"/>
-      <c r="I33" s="33" t="n"/>
-      <c r="J33" s="20">
-        <f>SUM(B33:I33)</f>
-        <v/>
-      </c>
-      <c r="K33" s="32" t="inlineStr">
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
+      <c r="G35" s="34" t="n"/>
+      <c r="H35" s="34" t="n"/>
+      <c r="I35" s="34" t="n"/>
+      <c r="J35" s="20">
+        <f>SUM(B35:I35)</f>
+        <v/>
+      </c>
+      <c r="K35" s="33" t="inlineStr">
         <is>
           <t>PREENCHER com as passagens compradas para setembro/2026.</t>
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B34" s="33" t="n"/>
-      <c r="C34" s="33" t="n"/>
-      <c r="D34" s="33" t="n"/>
-      <c r="E34" s="33" t="n"/>
-      <c r="F34" s="33" t="n"/>
-      <c r="G34" s="33" t="n"/>
-      <c r="H34" s="33" t="n"/>
-      <c r="I34" s="33" t="n"/>
-      <c r="J34" s="20">
-        <f>SUM(B34:I34)</f>
-        <v/>
-      </c>
-      <c r="K34" s="32" t="inlineStr">
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n"/>
+      <c r="G36" s="34" t="n"/>
+      <c r="H36" s="34" t="n"/>
+      <c r="I36" s="34" t="n"/>
+      <c r="J36" s="20">
+        <f>SUM(B36:I36)</f>
+        <v/>
+      </c>
+      <c r="K36" s="33" t="inlineStr">
         <is>
           <t>PREENCHER conforme escala de domingos/feriados de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="21" t="inlineStr">
-        <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
+          <t>Célula laranja</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B40" s="7" t="inlineStr">
+      <c r="B42" s="7" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="11">
-    <mergeCell ref="A21:K21"/>
-    <mergeCell ref="A30:K30"/>
+  <autoFilter ref="A4:K36"/>
+  <mergeCells count="7">
+    <mergeCell ref="B41:K41"/>
     <mergeCell ref="B40:K40"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="B39:K39"/>
-    <mergeCell ref="A5:K5"/>
-    <mergeCell ref="A32:K32"/>
     <mergeCell ref="B38:K38"/>
+    <mergeCell ref="B42:K42"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="B36:K36"/>
-    <mergeCell ref="B37:K37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2993,328 +3115,338 @@
           <t>PROVENTOS</t>
         </is>
       </c>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="29" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="29" t="n"/>
+      <c r="H5" s="29" t="n"/>
+      <c r="I5" s="29" t="n"/>
+      <c r="J5" s="29" t="n"/>
+      <c r="K5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="33" t="n">
+      <c r="B6" s="34" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="33" t="n">
+      <c r="C6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="E6" s="33" t="n">
+      <c r="E6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="F6" s="33" t="n">
+      <c r="F6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="33" t="n">
+      <c r="G6" s="34" t="n">
         <v>1621</v>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="34" t="n">
         <v>595</v>
       </c>
-      <c r="I6" s="33" t="n">
+      <c r="I6" s="34" t="n">
         <v>1621</v>
       </c>
       <c r="J6" s="20">
         <f>SUM(B6:I6)</f>
         <v/>
       </c>
-      <c r="K6" s="32" t="inlineStr">
+      <c r="K6" s="33" t="inlineStr">
         <is>
           <t>CAMILA proporcional (admissão no mês).</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="33" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n">
+      <c r="B7" s="34" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n">
         <v>350</v>
       </c>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="33" t="n"/>
-      <c r="H7" s="33" t="n"/>
-      <c r="I7" s="33" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="34" t="n"/>
+      <c r="H7" s="34" t="n"/>
+      <c r="I7" s="34" t="n"/>
       <c r="J7" s="20">
         <f>SUM(B7:I7)</f>
         <v/>
       </c>
-      <c r="K7" s="32" t="inlineStr"/>
+      <c r="K7" s="33" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="33" t="n"/>
-      <c r="C8" s="33" t="n"/>
-      <c r="D8" s="33" t="n">
+      <c r="B8" s="34" t="n"/>
+      <c r="C8" s="34" t="n"/>
+      <c r="D8" s="34" t="n">
         <v>442.09</v>
       </c>
-      <c r="E8" s="33" t="n"/>
-      <c r="F8" s="33" t="n"/>
-      <c r="G8" s="33" t="n"/>
-      <c r="H8" s="33" t="n"/>
-      <c r="I8" s="33" t="n">
+      <c r="E8" s="34" t="n"/>
+      <c r="F8" s="34" t="n"/>
+      <c r="G8" s="34" t="n"/>
+      <c r="H8" s="34" t="n"/>
+      <c r="I8" s="34" t="n">
         <v>221.05</v>
       </c>
       <c r="J8" s="20">
         <f>SUM(B8:I8)</f>
         <v/>
       </c>
-      <c r="K8" s="32" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t>Valor lançado na folha. O DSR foi calculado sobre o dobro deste valor — verificar qual é o valor correto das horas extras.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO PRODUTOS + PDV</t>
         </is>
       </c>
-      <c r="B9" s="33" t="n"/>
-      <c r="C9" s="33" t="n">
+      <c r="B9" s="34" t="n"/>
+      <c r="C9" s="34" t="n">
         <v>2000</v>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="34" t="n">
         <v>1202</v>
       </c>
-      <c r="E9" s="33" t="n">
+      <c r="E9" s="34" t="n">
         <v>1693.68</v>
       </c>
-      <c r="F9" s="33" t="n">
+      <c r="F9" s="34" t="n">
         <v>1071</v>
       </c>
-      <c r="G9" s="33" t="n">
+      <c r="G9" s="34" t="n">
         <v>345</v>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="34" t="n">
         <v>120</v>
       </c>
-      <c r="I9" s="33" t="n">
+      <c r="I9" s="34" t="n">
         <v>280</v>
       </c>
       <c r="J9" s="20">
         <f>SUM(B9:I9)</f>
         <v/>
       </c>
-      <c r="K9" s="32" t="inlineStr">
+      <c r="K9" s="33" t="inlineStr">
         <is>
           <t>Comissão do InovaFarma somada aos PDV antigos.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B10" s="33" t="n"/>
-      <c r="C10" s="33" t="n">
+      <c r="B10" s="34" t="n"/>
+      <c r="C10" s="34" t="n">
         <v>384.62</v>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="34" t="n">
         <v>401.19</v>
       </c>
-      <c r="E10" s="33" t="n">
+      <c r="E10" s="34" t="n">
         <v>325.71</v>
       </c>
-      <c r="F10" s="33" t="n">
+      <c r="F10" s="34" t="n">
         <v>205.96</v>
       </c>
-      <c r="G10" s="33" t="n">
+      <c r="G10" s="34" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="H10" s="33" t="n"/>
-      <c r="I10" s="33" t="n">
+      <c r="H10" s="34" t="n"/>
+      <c r="I10" s="34" t="n">
         <v>138.87</v>
       </c>
       <c r="J10" s="20">
         <f>SUM(B10:I10)</f>
         <v/>
       </c>
-      <c r="K10" s="32" t="inlineStr">
+      <c r="K10" s="33" t="inlineStr">
         <is>
           <t>Pago com fator 5/26 = 0,192307 (calendário de AGOSTO). Julho/2026 tem 4 domingos e 27 dias úteis → fator correto 0,148148. Ver conferência abaixo.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B11" s="33" t="n"/>
-      <c r="C11" s="33" t="n">
+      <c r="B11" s="34" t="n"/>
+      <c r="C11" s="34" t="n">
         <v>810.5</v>
       </c>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="33" t="n">
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="34" t="n">
         <v>810.5</v>
       </c>
-      <c r="H11" s="33" t="n"/>
-      <c r="I11" s="33" t="n"/>
+      <c r="H11" s="34" t="n"/>
+      <c r="I11" s="34" t="n"/>
       <c r="J11" s="20">
         <f>SUM(B11:I11)</f>
         <v/>
       </c>
-      <c r="K11" s="32" t="inlineStr"/>
+      <c r="K11" s="33" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="B12" s="33" t="n"/>
-      <c r="C12" s="33" t="n"/>
-      <c r="D12" s="33" t="n"/>
-      <c r="E12" s="33" t="n"/>
-      <c r="F12" s="33" t="n">
+      <c r="B12" s="34" t="n"/>
+      <c r="C12" s="34" t="n"/>
+      <c r="D12" s="34" t="n"/>
+      <c r="E12" s="34" t="n"/>
+      <c r="F12" s="34" t="n">
         <v>307.99</v>
       </c>
-      <c r="G12" s="33" t="n"/>
-      <c r="H12" s="33" t="n"/>
-      <c r="I12" s="33" t="n">
+      <c r="G12" s="34" t="n"/>
+      <c r="H12" s="34" t="n"/>
+      <c r="I12" s="34" t="n">
         <v>307.99</v>
       </c>
       <c r="J12" s="20">
         <f>SUM(B12:I12)</f>
         <v/>
       </c>
-      <c r="K12" s="32" t="inlineStr"/>
+      <c r="K12" s="33" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="B13" s="33" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n">
+      <c r="B13" s="34" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="E13" s="33" t="n">
+      <c r="E13" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="F13" s="33" t="n">
+      <c r="F13" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="G13" s="33" t="n">
+      <c r="G13" s="34" t="n">
         <v>150</v>
       </c>
-      <c r="H13" s="33" t="n"/>
-      <c r="I13" s="33" t="n">
+      <c r="H13" s="34" t="n"/>
+      <c r="I13" s="34" t="n">
         <v>150</v>
       </c>
       <c r="J13" s="20">
         <f>SUM(B13:I13)</f>
         <v/>
       </c>
-      <c r="K13" s="32" t="inlineStr"/>
+      <c r="K13" s="33" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="B14" s="33" t="n"/>
-      <c r="C14" s="33" t="n"/>
-      <c r="D14" s="33" t="n">
+      <c r="B14" s="34" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="33" t="n">
+      <c r="E14" s="34" t="n">
         <v>200</v>
       </c>
-      <c r="F14" s="33" t="n">
+      <c r="F14" s="34" t="n">
         <v>250</v>
       </c>
-      <c r="G14" s="33" t="n">
+      <c r="G14" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="33" t="n"/>
-      <c r="I14" s="33" t="n">
+      <c r="H14" s="34" t="n"/>
+      <c r="I14" s="34" t="n">
         <v>100</v>
       </c>
       <c r="J14" s="20">
         <f>SUM(B14:I14)</f>
         <v/>
       </c>
-      <c r="K14" s="32" t="inlineStr"/>
+      <c r="K14" s="33" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="B15" s="33" t="n"/>
-      <c r="C15" s="33" t="n">
+      <c r="B15" s="34" t="n"/>
+      <c r="C15" s="34" t="n">
         <v>264</v>
       </c>
-      <c r="D15" s="33" t="n">
+      <c r="D15" s="34" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="33" t="n">
+      <c r="E15" s="34" t="n">
         <v>290</v>
       </c>
-      <c r="F15" s="33" t="n">
+      <c r="F15" s="34" t="n">
         <v>292</v>
       </c>
-      <c r="G15" s="33" t="n"/>
-      <c r="H15" s="33" t="n"/>
-      <c r="I15" s="33" t="n"/>
+      <c r="G15" s="34" t="n"/>
+      <c r="H15" s="34" t="n"/>
+      <c r="I15" s="34" t="n"/>
       <c r="J15" s="20">
         <f>SUM(B15:I15)</f>
         <v/>
       </c>
-      <c r="K15" s="32" t="inlineStr"/>
+      <c r="K15" s="33" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="B16" s="33" t="n"/>
-      <c r="C16" s="33" t="n"/>
-      <c r="D16" s="33" t="n"/>
-      <c r="E16" s="33" t="n"/>
-      <c r="F16" s="33" t="n">
+      <c r="B16" s="34" t="n"/>
+      <c r="C16" s="34" t="n"/>
+      <c r="D16" s="34" t="n"/>
+      <c r="E16" s="34" t="n"/>
+      <c r="F16" s="34" t="n">
         <v>40</v>
       </c>
-      <c r="G16" s="33" t="n"/>
-      <c r="H16" s="33" t="n"/>
-      <c r="I16" s="33" t="n"/>
+      <c r="G16" s="34" t="n"/>
+      <c r="H16" s="34" t="n"/>
+      <c r="I16" s="34" t="n"/>
       <c r="J16" s="20">
         <f>SUM(B16:I16)</f>
         <v/>
       </c>
-      <c r="K16" s="32" t="inlineStr"/>
+      <c r="K16" s="33" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
@@ -3358,7 +3490,7 @@
         <f>SUM(B17:I17)</f>
         <v/>
       </c>
-      <c r="K17" s="32" t="inlineStr"/>
+      <c r="K17" s="33" t="inlineStr"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="28" t="inlineStr">
@@ -3366,196 +3498,206 @@
           <t>DESCONTOS</t>
         </is>
       </c>
+      <c r="B18" s="29" t="n"/>
+      <c r="C18" s="29" t="n"/>
+      <c r="D18" s="29" t="n"/>
+      <c r="E18" s="29" t="n"/>
+      <c r="F18" s="29" t="n"/>
+      <c r="G18" s="29" t="n"/>
+      <c r="H18" s="29" t="n"/>
+      <c r="I18" s="29" t="n"/>
+      <c r="J18" s="29" t="n"/>
+      <c r="K18" s="29" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="B19" s="33" t="n"/>
-      <c r="C19" s="33" t="n">
+      <c r="B19" s="34" t="n"/>
+      <c r="C19" s="34" t="n">
         <v>-2300</v>
       </c>
-      <c r="D19" s="33" t="n">
+      <c r="D19" s="34" t="n">
         <v>-1500</v>
       </c>
-      <c r="E19" s="33" t="n">
+      <c r="E19" s="34" t="n">
         <v>-1300</v>
       </c>
-      <c r="F19" s="33" t="n">
+      <c r="F19" s="34" t="n">
         <v>-1300</v>
       </c>
-      <c r="G19" s="33" t="n">
+      <c r="G19" s="34" t="n">
         <v>-1200</v>
       </c>
-      <c r="H19" s="33" t="n"/>
-      <c r="I19" s="33" t="n"/>
+      <c r="H19" s="34" t="n"/>
+      <c r="I19" s="34" t="n"/>
       <c r="J19" s="20">
         <f>SUM(B19:I19)</f>
         <v/>
       </c>
-      <c r="K19" s="32" t="inlineStr"/>
+      <c r="K19" s="33" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="B20" s="33" t="n"/>
-      <c r="C20" s="33" t="n">
+      <c r="B20" s="34" t="n"/>
+      <c r="C20" s="34" t="n">
         <v>-264</v>
       </c>
-      <c r="D20" s="33" t="n">
+      <c r="D20" s="34" t="n">
         <v>-100</v>
       </c>
-      <c r="E20" s="33" t="n">
+      <c r="E20" s="34" t="n">
         <v>-290</v>
       </c>
-      <c r="F20" s="33" t="n">
+      <c r="F20" s="34" t="n">
         <v>-332</v>
       </c>
-      <c r="G20" s="33" t="n"/>
-      <c r="H20" s="33" t="n"/>
-      <c r="I20" s="33" t="n"/>
+      <c r="G20" s="34" t="n"/>
+      <c r="H20" s="34" t="n"/>
+      <c r="I20" s="34" t="n"/>
       <c r="J20" s="20">
         <f>SUM(B20:I20)</f>
         <v/>
       </c>
-      <c r="K20" s="32" t="inlineStr"/>
+      <c r="K20" s="33" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="B21" s="33" t="n"/>
-      <c r="C21" s="33" t="n">
+      <c r="B21" s="34" t="n"/>
+      <c r="C21" s="34" t="n">
         <v>-300</v>
       </c>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="33" t="n">
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n">
         <v>-500</v>
       </c>
-      <c r="F21" s="33" t="n">
+      <c r="F21" s="34" t="n">
         <v>-300</v>
       </c>
-      <c r="G21" s="33" t="n">
+      <c r="G21" s="34" t="n">
         <v>-300</v>
       </c>
-      <c r="H21" s="33" t="n"/>
-      <c r="I21" s="33" t="n"/>
+      <c r="H21" s="34" t="n"/>
+      <c r="I21" s="34" t="n"/>
       <c r="J21" s="20">
         <f>SUM(B21:I21)</f>
         <v/>
       </c>
-      <c r="K21" s="32" t="inlineStr"/>
+      <c r="K21" s="33" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS</t>
         </is>
       </c>
-      <c r="B22" s="33" t="n"/>
-      <c r="C22" s="33" t="n"/>
-      <c r="D22" s="33" t="n"/>
-      <c r="E22" s="33" t="n"/>
-      <c r="F22" s="33" t="n"/>
-      <c r="G22" s="33" t="n"/>
-      <c r="H22" s="33" t="n"/>
-      <c r="I22" s="33" t="n"/>
+      <c r="B22" s="34" t="n"/>
+      <c r="C22" s="34" t="n"/>
+      <c r="D22" s="34" t="n"/>
+      <c r="E22" s="34" t="n"/>
+      <c r="F22" s="34" t="n"/>
+      <c r="G22" s="34" t="n"/>
+      <c r="H22" s="34" t="n"/>
+      <c r="I22" s="34" t="n"/>
       <c r="J22" s="20">
         <f>SUM(B22:I22)</f>
         <v/>
       </c>
-      <c r="K22" s="32" t="inlineStr"/>
+      <c r="K22" s="33" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="B23" s="33" t="n"/>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="33" t="n">
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="E23" s="33" t="n">
+      <c r="E23" s="34" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="F23" s="33" t="n">
+      <c r="F23" s="34" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="G23" s="33" t="n"/>
-      <c r="H23" s="33" t="n"/>
-      <c r="I23" s="33" t="n">
+      <c r="G23" s="34" t="n"/>
+      <c r="H23" s="34" t="n"/>
+      <c r="I23" s="34" t="n">
         <v>-84.29000000000001</v>
       </c>
       <c r="J23" s="20">
         <f>SUM(B23:I23)</f>
         <v/>
       </c>
-      <c r="K23" s="32" t="inlineStr"/>
+      <c r="K23" s="33" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="B24" s="33" t="n">
+      <c r="B24" s="34" t="n">
         <v>-592.27</v>
       </c>
-      <c r="C24" s="33" t="n">
+      <c r="C24" s="34" t="n">
         <v>-480.85</v>
       </c>
-      <c r="D24" s="33" t="n">
+      <c r="D24" s="34" t="n">
         <v>-426.78</v>
       </c>
-      <c r="E24" s="33" t="n">
+      <c r="E24" s="34" t="n">
         <v>-414.75</v>
       </c>
-      <c r="F24" s="33" t="n">
+      <c r="F24" s="34" t="n">
         <v>-373.14</v>
       </c>
-      <c r="G24" s="33" t="n">
+      <c r="G24" s="34" t="n">
         <v>-213.94</v>
       </c>
-      <c r="H24" s="33" t="n"/>
-      <c r="I24" s="33" t="n">
+      <c r="H24" s="34" t="n"/>
+      <c r="I24" s="34" t="n">
         <v>-229.38</v>
       </c>
       <c r="J24" s="20">
         <f>SUM(B24:I24)</f>
         <v/>
       </c>
-      <c r="K24" s="32" t="inlineStr"/>
+      <c r="K24" s="33" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="B25" s="33" t="n">
+      <c r="B25" s="34" t="n">
         <v>-251.04</v>
       </c>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="33" t="n"/>
-      <c r="H25" s="33" t="n"/>
-      <c r="I25" s="33" t="n"/>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="34" t="n"/>
+      <c r="G25" s="34" t="n"/>
+      <c r="H25" s="34" t="n"/>
+      <c r="I25" s="34" t="n"/>
       <c r="J25" s="20">
         <f>SUM(B25:I25)</f>
         <v/>
       </c>
-      <c r="K25" s="32" t="inlineStr"/>
+      <c r="K25" s="33" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="15" t="inlineStr">
@@ -3599,7 +3741,7 @@
         <f>SUM(B26:I26)</f>
         <v/>
       </c>
-      <c r="K26" s="32" t="inlineStr"/>
+      <c r="K26" s="33" t="inlineStr"/>
     </row>
     <row r="27" ht="20" customHeight="1">
       <c r="A27" s="28" t="inlineStr">
@@ -3607,6 +3749,16 @@
           <t>LÍQUIDO</t>
         </is>
       </c>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n"/>
+      <c r="G27" s="29" t="n"/>
+      <c r="H27" s="29" t="n"/>
+      <c r="I27" s="29" t="n"/>
+      <c r="J27" s="29" t="n"/>
+      <c r="K27" s="29" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="15" t="inlineStr">
@@ -3614,79 +3766,79 @@
           <t>LÍQUIDO PAGO (05/08/2026)</t>
         </is>
       </c>
-      <c r="B28" s="37">
+      <c r="B28" s="38">
         <f>B17+B26</f>
         <v/>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="38">
         <f>C17+C26</f>
         <v/>
       </c>
-      <c r="D28" s="37">
+      <c r="D28" s="38">
         <f>D17+D26</f>
         <v/>
       </c>
-      <c r="E28" s="37">
+      <c r="E28" s="38">
         <f>E17+E26</f>
         <v/>
       </c>
-      <c r="F28" s="37">
+      <c r="F28" s="38">
         <f>F17+F26</f>
         <v/>
       </c>
-      <c r="G28" s="37">
+      <c r="G28" s="38">
         <f>G17+G26</f>
         <v/>
       </c>
-      <c r="H28" s="37">
+      <c r="H28" s="38">
         <f>H17+H26</f>
         <v/>
       </c>
-      <c r="I28" s="37">
+      <c r="I28" s="38">
         <f>I17+I26</f>
         <v/>
       </c>
-      <c r="J28" s="37">
+      <c r="J28" s="38">
         <f>SUM(B28:I28)</f>
         <v/>
       </c>
-      <c r="K28" s="32" t="inlineStr"/>
+      <c r="K28" s="33" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>SALDO FINAL DA PLANILHA ORIGINAL</t>
         </is>
       </c>
-      <c r="B29" s="33" t="n">
+      <c r="B29" s="34" t="n">
         <v>4805.1</v>
       </c>
-      <c r="C29" s="33" t="n">
+      <c r="C29" s="34" t="n">
         <v>1735.27</v>
       </c>
-      <c r="D29" s="33" t="n">
+      <c r="D29" s="34" t="n">
         <v>2355.21</v>
       </c>
-      <c r="E29" s="33" t="n">
+      <c r="E29" s="34" t="n">
         <v>1791.35</v>
       </c>
-      <c r="F29" s="33" t="n">
+      <c r="F29" s="34" t="n">
         <v>1648.52</v>
       </c>
-      <c r="G29" s="33" t="n">
+      <c r="G29" s="34" t="n">
         <v>1378.91</v>
       </c>
-      <c r="H29" s="33" t="n">
+      <c r="H29" s="34" t="n">
         <v>715</v>
       </c>
-      <c r="I29" s="33" t="n">
+      <c r="I29" s="34" t="n">
         <v>2505.24</v>
       </c>
       <c r="J29" s="20">
         <f>SUM(B29:I29)</f>
         <v/>
       </c>
-      <c r="K29" s="32" t="inlineStr">
+      <c r="K29" s="33" t="inlineStr">
         <is>
           <t>Valor que constava na aba AGOSTOJULHO.26 do arquivo original.</t>
         </is>
@@ -3734,7 +3886,7 @@
         <f>SUM(B30:I30)</f>
         <v/>
       </c>
-      <c r="K30" s="32" t="inlineStr">
+      <c r="K30" s="33" t="inlineStr">
         <is>
           <t>Deve ser zero — confirma que a revisão não alterou nenhum valor pago.</t>
         </is>
@@ -3746,42 +3898,52 @@
           <t>CONFERÊNCIA DO DSR DE JULHO/2026 (não altera o que já foi pago — decidir se ajusta em setembro)</t>
         </is>
       </c>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="29" t="n"/>
+      <c r="F31" s="29" t="n"/>
+      <c r="G31" s="29" t="n"/>
+      <c r="H31" s="29" t="n"/>
+      <c r="I31" s="29" t="n"/>
+      <c r="J31" s="29" t="n"/>
+      <c r="K31" s="29" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>DSR pago (fator 5/26)</t>
         </is>
       </c>
-      <c r="B32" s="35">
+      <c r="B32" s="36">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C32" s="35">
+      <c r="C32" s="36">
         <f>C10</f>
         <v/>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="36">
         <f>D10</f>
         <v/>
       </c>
-      <c r="E32" s="35">
+      <c r="E32" s="36">
         <f>E10</f>
         <v/>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="36">
         <f>F10</f>
         <v/>
       </c>
-      <c r="G32" s="35">
+      <c r="G32" s="36">
         <f>G10</f>
         <v/>
       </c>
-      <c r="H32" s="35">
+      <c r="H32" s="36">
         <f>H10</f>
         <v/>
       </c>
-      <c r="I32" s="35">
+      <c r="I32" s="36">
         <f>I10</f>
         <v/>
       </c>
@@ -3789,47 +3951,47 @@
         <f>SUM(B32:I32)</f>
         <v/>
       </c>
-      <c r="K32" s="32" t="inlineStr">
+      <c r="K32" s="33" t="inlineStr">
         <is>
           <t>Fator do calendário de agosto aplicado por engano na competência de julho.</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>DSR recalculado (fator 4/27 · comissão + HE)</t>
         </is>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="36">
         <f>ROUND((B9+B8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <f>ROUND((C9+C8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <f>ROUND((D9+D8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <f>ROUND((E9+E8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <f>ROUND((F9+F8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <f>ROUND((G9+G8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <f>ROUND((H9+H8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <f>ROUND((I9+I8)*4/27,2)</f>
         <v/>
       </c>
@@ -3837,7 +3999,7 @@
         <f>SUM(B33:I33)</f>
         <v/>
       </c>
-      <c r="K33" s="32" t="inlineStr">
+      <c r="K33" s="33" t="inlineStr">
         <is>
           <t>Julho/2026: 4 domingos (05, 12, 19 e 26) e 27 dias úteis.</t>
         </is>
@@ -3849,43 +4011,43 @@
           <t>Diferença de DSR (a menor/maior)</t>
         </is>
       </c>
-      <c r="B34" s="31">
+      <c r="B34" s="32">
         <f>ROUND(B33-B32,2)</f>
         <v/>
       </c>
-      <c r="C34" s="31">
+      <c r="C34" s="32">
         <f>ROUND(C33-C32,2)</f>
         <v/>
       </c>
-      <c r="D34" s="31">
+      <c r="D34" s="32">
         <f>ROUND(D33-D32,2)</f>
         <v/>
       </c>
-      <c r="E34" s="31">
+      <c r="E34" s="32">
         <f>ROUND(E33-E32,2)</f>
         <v/>
       </c>
-      <c r="F34" s="31">
+      <c r="F34" s="32">
         <f>ROUND(F33-F32,2)</f>
         <v/>
       </c>
-      <c r="G34" s="31">
+      <c r="G34" s="32">
         <f>ROUND(G33-G32,2)</f>
         <v/>
       </c>
-      <c r="H34" s="31">
+      <c r="H34" s="32">
         <f>ROUND(H33-H32,2)</f>
         <v/>
       </c>
-      <c r="I34" s="31">
+      <c r="I34" s="32">
         <f>ROUND(I33-I32,2)</f>
         <v/>
       </c>
-      <c r="J34" s="31">
+      <c r="J34" s="32">
         <f>SUM(B34:I34)</f>
         <v/>
       </c>
-      <c r="K34" s="32" t="inlineStr">
+      <c r="K34" s="33" t="inlineStr">
         <is>
           <t>Valor negativo = foi pago a mais em julho. Decidir com a contabilidade se compensa em set/26.</t>
         </is>
@@ -3897,130 +4059,136 @@
           <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
         </is>
       </c>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="29" t="n"/>
+      <c r="F35" s="29" t="n"/>
+      <c r="G35" s="29" t="n"/>
+      <c r="H35" s="29" t="n"/>
+      <c r="I35" s="29" t="n"/>
+      <c r="J35" s="29" t="n"/>
+      <c r="K35" s="29" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>VALE TRANSPORTE (passagens de agosto)</t>
         </is>
       </c>
-      <c r="B36" s="33" t="n">
+      <c r="B36" s="34" t="n">
         <v>350</v>
       </c>
-      <c r="C36" s="33" t="n"/>
-      <c r="D36" s="33" t="n">
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n">
         <v>416</v>
       </c>
-      <c r="E36" s="33" t="n"/>
-      <c r="F36" s="33" t="n">
+      <c r="E36" s="34" t="n"/>
+      <c r="F36" s="34" t="n">
         <v>500</v>
       </c>
-      <c r="G36" s="33" t="n"/>
-      <c r="H36" s="33" t="n">
+      <c r="G36" s="34" t="n"/>
+      <c r="H36" s="34" t="n">
         <v>135</v>
       </c>
-      <c r="I36" s="33" t="n">
+      <c r="I36" s="34" t="n">
         <v>288</v>
       </c>
       <c r="J36" s="20">
         <f>SUM(B36:I36)</f>
         <v/>
       </c>
-      <c r="K36" s="32" t="inlineStr">
+      <c r="K36" s="33" t="inlineStr">
         <is>
           <t>Compra registrada na planilha original.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B37" s="33" t="n">
+      <c r="B37" s="34" t="n">
         <v>647</v>
       </c>
-      <c r="C37" s="33" t="n">
+      <c r="C37" s="34" t="n">
         <v>84</v>
       </c>
-      <c r="D37" s="33" t="n">
+      <c r="D37" s="34" t="n">
         <v>48</v>
       </c>
-      <c r="E37" s="33" t="n">
+      <c r="E37" s="34" t="n">
         <v>50</v>
       </c>
-      <c r="F37" s="33" t="n">
+      <c r="F37" s="34" t="n">
         <v>75</v>
       </c>
-      <c r="G37" s="33" t="n">
+      <c r="G37" s="34" t="n">
         <v>84</v>
       </c>
-      <c r="H37" s="33" t="n"/>
-      <c r="I37" s="33" t="n"/>
+      <c r="H37" s="34" t="n"/>
+      <c r="I37" s="34" t="n"/>
       <c r="J37" s="20">
         <f>SUM(B37:I37)</f>
         <v/>
       </c>
-      <c r="K37" s="32" t="inlineStr"/>
+      <c r="K37" s="33" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="38" t="inlineStr">
+      <c r="A39" s="39" t="inlineStr">
         <is>
           <t>AJUSTES FEITOS NESTA REVISÃO (a planilha original continua intacta no arquivo enviado):</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="39" t="inlineStr">
+      <c r="A40" s="40" t="inlineStr">
         <is>
           <t>1. Fórmulas de SALDO FINAL corrigidas — na original o total do DEAN pulava a linha 17 e o do AGNOR começava na linha 4, deixando linhas de fora da soma.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="39" t="inlineStr">
+      <c r="A41" s="40" t="inlineStr">
         <is>
           <t>2. Rubricas separadas em PROVENTOS × DESCONTOS, com subtotais próprios, em vez de uma soma única.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="39" t="inlineStr">
+      <c r="A42" s="40" t="inlineStr">
         <is>
           <t>3. Nomes de rubrica padronizados e coluna de observação com a origem de cada valor.</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="39" t="inlineStr">
+      <c r="A43" s="40" t="inlineStr">
         <is>
           <t>4. Conferência do DSR: em julho foi usado o fator de agosto (5/26) e a base foi o dobro das horas extras lançadas.</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="39" t="inlineStr">
+      <c r="A44" s="40" t="inlineStr">
         <is>
           <t>5. Linha de conferência comparando o líquido revisado com o SALDO FINAL da planilha original (tem que fechar em zero).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="13">
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A35:K35"/>
+  <autoFilter ref="A4:K30"/>
+  <mergeCells count="8">
     <mergeCell ref="A39:K39"/>
     <mergeCell ref="A43:K43"/>
     <mergeCell ref="A41:K41"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A42:K42"/>
-    <mergeCell ref="A5:K5"/>
     <mergeCell ref="A44:K44"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A27:K27"/>
-    <mergeCell ref="A31:K31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4084,3878 +4252,3879 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="inlineStr">
+      <c r="A5" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C5" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D5" s="34">
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D5" s="35">
         <f>'HOLERITE AGO.26'!B6</f>
         <v/>
       </c>
-      <c r="E5" s="40" t="n"/>
+      <c r="E5" s="41" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="29" t="inlineStr">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B6" s="29" t="inlineStr">
+      <c r="B6" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C6" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D6" s="34">
+      <c r="C6" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D6" s="35">
         <f>'HOLERITE AGO.26'!B7</f>
         <v/>
       </c>
-      <c r="E6" s="40" t="n"/>
+      <c r="E6" s="41" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="inlineStr">
+      <c r="A7" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B7" s="29" t="inlineStr">
+      <c r="B7" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C7" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D7" s="34">
+      <c r="C7" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D7" s="35">
         <f>'HOLERITE AGO.26'!B8</f>
         <v/>
       </c>
-      <c r="E7" s="40" t="n"/>
+      <c r="E7" s="41" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="inlineStr">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B8" s="29" t="inlineStr">
+      <c r="B8" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C8" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D8" s="34">
+      <c r="C8" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D8" s="35">
         <f>'HOLERITE AGO.26'!B11</f>
         <v/>
       </c>
-      <c r="E8" s="40" t="n"/>
+      <c r="E8" s="41" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="inlineStr">
+      <c r="A9" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="B9" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D9" s="34">
+      <c r="C9" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D9" s="35">
         <f>'HOLERITE AGO.26'!B12</f>
         <v/>
       </c>
-      <c r="E9" s="40" t="n"/>
+      <c r="E9" s="41" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="inlineStr">
+      <c r="A10" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B10" s="29" t="inlineStr">
+      <c r="B10" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C10" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D10" s="34">
+      <c r="C10" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D10" s="35">
         <f>'HOLERITE AGO.26'!B13</f>
         <v/>
       </c>
-      <c r="E10" s="40" t="n"/>
+      <c r="E10" s="41" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="inlineStr">
+      <c r="A11" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B11" s="29" t="inlineStr">
+      <c r="B11" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C11" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D11" s="34">
+      <c r="C11" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D11" s="35">
         <f>'HOLERITE AGO.26'!B14</f>
         <v/>
       </c>
-      <c r="E11" s="40" t="n"/>
+      <c r="E11" s="41" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="29" t="inlineStr">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B12" s="29" t="inlineStr">
+      <c r="B12" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C12" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D12" s="34">
+      <c r="C12" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D12" s="35">
         <f>'HOLERITE AGO.26'!B15</f>
         <v/>
       </c>
-      <c r="E12" s="40" t="n"/>
+      <c r="E12" s="41" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="inlineStr">
+      <c r="A13" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B13" s="29" t="inlineStr">
+      <c r="B13" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C13" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D13" s="34">
+      <c r="C13" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D13" s="35">
         <f>'HOLERITE AGO.26'!B16</f>
         <v/>
       </c>
-      <c r="E13" s="40" t="n"/>
+      <c r="E13" s="41" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="29" t="inlineStr">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B14" s="29" t="inlineStr">
+      <c r="B14" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D14" s="34">
-        <f>'HOLERITE AGO.26'!B17</f>
-        <v/>
-      </c>
-      <c r="E14" s="40" t="n"/>
+      <c r="C14" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D14" s="35">
+        <f>'HOLERITE AGO.26'!B19</f>
+        <v/>
+      </c>
+      <c r="E14" s="41" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D15" s="34">
-        <f>'HOLERITE AGO.26'!B18</f>
-        <v/>
-      </c>
-      <c r="E15" s="40" t="n"/>
+      <c r="C15" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D15" s="35">
+        <f>'HOLERITE AGO.26'!B20</f>
+        <v/>
+      </c>
+      <c r="E15" s="41" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="29" t="inlineStr">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B16" s="29" t="inlineStr">
+      <c r="B16" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C16" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D16" s="34">
-        <f>'HOLERITE AGO.26'!B19</f>
-        <v/>
-      </c>
-      <c r="E16" s="40" t="n"/>
+      <c r="C16" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D16" s="35">
+        <f>'HOLERITE AGO.26'!B21</f>
+        <v/>
+      </c>
+      <c r="E16" s="41" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="41" t="inlineStr">
+      <c r="A17" s="42" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B17" s="41" t="inlineStr">
+      <c r="B17" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C17" s="41" t="inlineStr">
+      <c r="C17" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D17" s="42">
-        <f>'HOLERITE AGO.26'!B20</f>
+      <c r="D17" s="43">
+        <f>'HOLERITE AGO.26'!B22</f>
         <v/>
       </c>
       <c r="E17" s="18" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="29" t="inlineStr">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B18" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D18" s="34">
-        <f>'HOLERITE AGO.26'!B22</f>
-        <v/>
-      </c>
-      <c r="E18" s="40" t="n"/>
+      <c r="D18" s="35">
+        <f>'HOLERITE AGO.26'!B24</f>
+        <v/>
+      </c>
+      <c r="E18" s="41" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A19" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B19" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C19" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D19" s="34">
-        <f>'HOLERITE AGO.26'!B23</f>
-        <v/>
-      </c>
-      <c r="E19" s="40" t="n"/>
+      <c r="D19" s="35">
+        <f>'HOLERITE AGO.26'!B25</f>
+        <v/>
+      </c>
+      <c r="E19" s="41" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D20" s="34">
-        <f>'HOLERITE AGO.26'!B24</f>
-        <v/>
-      </c>
-      <c r="E20" s="40" t="n"/>
+      <c r="D20" s="35">
+        <f>'HOLERITE AGO.26'!B26</f>
+        <v/>
+      </c>
+      <c r="E20" s="41" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D21" s="34">
-        <f>'HOLERITE AGO.26'!B25</f>
-        <v/>
-      </c>
-      <c r="E21" s="40" t="n"/>
+      <c r="D21" s="35">
+        <f>'HOLERITE AGO.26'!B27</f>
+        <v/>
+      </c>
+      <c r="E21" s="41" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="34">
-        <f>'HOLERITE AGO.26'!B26</f>
-        <v/>
-      </c>
-      <c r="E22" s="40" t="n"/>
+      <c r="D22" s="35">
+        <f>'HOLERITE AGO.26'!B28</f>
+        <v/>
+      </c>
+      <c r="E22" s="41" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="inlineStr">
+      <c r="A23" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B23" s="29" t="inlineStr">
+      <c r="B23" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C23" s="29" t="inlineStr">
+      <c r="C23" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="34">
-        <f>'HOLERITE AGO.26'!B27</f>
-        <v/>
-      </c>
-      <c r="E23" s="40" t="n"/>
+      <c r="D23" s="35">
+        <f>'HOLERITE AGO.26'!B29</f>
+        <v/>
+      </c>
+      <c r="E23" s="41" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="29" t="inlineStr">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B24" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C24" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="34">
-        <f>'HOLERITE AGO.26'!B28</f>
-        <v/>
-      </c>
-      <c r="E24" s="40" t="n"/>
+      <c r="D24" s="35">
+        <f>'HOLERITE AGO.26'!B30</f>
+        <v/>
+      </c>
+      <c r="E24" s="41" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="41" t="inlineStr">
+      <c r="A25" s="42" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B25" s="41" t="inlineStr">
+      <c r="B25" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C25" s="41" t="inlineStr">
+      <c r="C25" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D25" s="42">
-        <f>'HOLERITE AGO.26'!B29</f>
+      <c r="D25" s="43">
+        <f>'HOLERITE AGO.26'!B31</f>
         <v/>
       </c>
       <c r="E25" s="18" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="43" t="inlineStr">
+      <c r="A26" s="44" t="inlineStr">
         <is>
           <t>DEAN</t>
         </is>
       </c>
-      <c r="B26" s="44" t="inlineStr">
+      <c r="B26" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C26" s="44" t="inlineStr">
+      <c r="C26" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D26" s="45">
-        <f>'HOLERITE AGO.26'!B31</f>
-        <v/>
-      </c>
-      <c r="E26" s="46" t="n"/>
+      <c r="D26" s="46">
+        <f>'HOLERITE AGO.26'!B33</f>
+        <v/>
+      </c>
+      <c r="E26" s="47" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="29" t="inlineStr">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B28" s="29" t="inlineStr">
+      <c r="B28" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C28" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D28" s="34">
+      <c r="C28" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D28" s="35">
         <f>'HOLERITE AGO.26'!C6</f>
         <v/>
       </c>
-      <c r="E28" s="40" t="n"/>
+      <c r="E28" s="41" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D29" s="34">
+      <c r="C29" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D29" s="35">
         <f>'HOLERITE AGO.26'!C7</f>
         <v/>
       </c>
-      <c r="E29" s="40" t="n"/>
+      <c r="E29" s="41" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="29" t="inlineStr">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B30" s="29" t="inlineStr">
+      <c r="B30" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C30" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D30" s="34">
+      <c r="C30" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D30" s="35">
         <f>'HOLERITE AGO.26'!C8</f>
         <v/>
       </c>
-      <c r="E30" s="40" t="n"/>
+      <c r="E30" s="41" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="inlineStr">
+      <c r="A31" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B31" s="29" t="inlineStr">
+      <c r="B31" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C31" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D31" s="34">
+      <c r="C31" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D31" s="35">
         <f>'HOLERITE AGO.26'!C11</f>
         <v/>
       </c>
-      <c r="E31" s="40" t="n"/>
+      <c r="E31" s="41" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="29" t="inlineStr">
+      <c r="A32" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B32" s="29" t="inlineStr">
+      <c r="B32" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C32" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D32" s="34">
+      <c r="C32" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D32" s="35">
         <f>'HOLERITE AGO.26'!C12</f>
         <v/>
       </c>
-      <c r="E32" s="40" t="n"/>
+      <c r="E32" s="41" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="inlineStr">
+      <c r="A33" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B33" s="29" t="inlineStr">
+      <c r="B33" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C33" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D33" s="34">
+      <c r="C33" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D33" s="35">
         <f>'HOLERITE AGO.26'!C13</f>
         <v/>
       </c>
-      <c r="E33" s="40" t="n"/>
+      <c r="E33" s="41" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B34" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D34" s="34">
+      <c r="C34" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D34" s="35">
         <f>'HOLERITE AGO.26'!C14</f>
         <v/>
       </c>
-      <c r="E34" s="40" t="n"/>
+      <c r="E34" s="41" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="inlineStr">
+      <c r="A35" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B35" s="29" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C35" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D35" s="34">
+      <c r="C35" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D35" s="35">
         <f>'HOLERITE AGO.26'!C15</f>
         <v/>
       </c>
-      <c r="E35" s="40" t="n"/>
+      <c r="E35" s="41" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="29" t="inlineStr">
+      <c r="A36" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B36" s="29" t="inlineStr">
+      <c r="B36" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C36" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D36" s="34">
+      <c r="C36" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D36" s="35">
         <f>'HOLERITE AGO.26'!C16</f>
         <v/>
       </c>
-      <c r="E36" s="40" t="n"/>
+      <c r="E36" s="41" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="inlineStr">
+      <c r="A37" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B37" s="29" t="inlineStr">
+      <c r="B37" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C37" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D37" s="34">
-        <f>'HOLERITE AGO.26'!C17</f>
-        <v/>
-      </c>
-      <c r="E37" s="40" t="n"/>
+      <c r="C37" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D37" s="35">
+        <f>'HOLERITE AGO.26'!C19</f>
+        <v/>
+      </c>
+      <c r="E37" s="41" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="29" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B38" s="29" t="inlineStr">
+      <c r="B38" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C38" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D38" s="34">
-        <f>'HOLERITE AGO.26'!C18</f>
-        <v/>
-      </c>
-      <c r="E38" s="40" t="n"/>
+      <c r="C38" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D38" s="35">
+        <f>'HOLERITE AGO.26'!C20</f>
+        <v/>
+      </c>
+      <c r="E38" s="41" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="inlineStr">
+      <c r="A39" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B39" s="29" t="inlineStr">
+      <c r="B39" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C39" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D39" s="34">
-        <f>'HOLERITE AGO.26'!C19</f>
-        <v/>
-      </c>
-      <c r="E39" s="40" t="n"/>
+      <c r="C39" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D39" s="35">
+        <f>'HOLERITE AGO.26'!C21</f>
+        <v/>
+      </c>
+      <c r="E39" s="41" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="41" t="inlineStr">
+      <c r="A40" s="42" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B40" s="41" t="inlineStr">
+      <c r="B40" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C40" s="41" t="inlineStr">
+      <c r="C40" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D40" s="42">
-        <f>'HOLERITE AGO.26'!C20</f>
+      <c r="D40" s="43">
+        <f>'HOLERITE AGO.26'!C22</f>
         <v/>
       </c>
       <c r="E40" s="18" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="inlineStr">
+      <c r="A41" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B41" s="29" t="inlineStr">
+      <c r="B41" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C41" s="29" t="inlineStr">
+      <c r="C41" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D41" s="34">
-        <f>'HOLERITE AGO.26'!C22</f>
-        <v/>
-      </c>
-      <c r="E41" s="40" t="n"/>
+      <c r="D41" s="35">
+        <f>'HOLERITE AGO.26'!C24</f>
+        <v/>
+      </c>
+      <c r="E41" s="41" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="29" t="inlineStr">
+      <c r="A42" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B42" s="29" t="inlineStr">
+      <c r="B42" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C42" s="29" t="inlineStr">
+      <c r="C42" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D42" s="34">
-        <f>'HOLERITE AGO.26'!C23</f>
-        <v/>
-      </c>
-      <c r="E42" s="40" t="n"/>
+      <c r="D42" s="35">
+        <f>'HOLERITE AGO.26'!C25</f>
+        <v/>
+      </c>
+      <c r="E42" s="41" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="inlineStr">
+      <c r="A43" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B43" s="29" t="inlineStr">
+      <c r="B43" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C43" s="29" t="inlineStr">
+      <c r="C43" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D43" s="34">
-        <f>'HOLERITE AGO.26'!C24</f>
-        <v/>
-      </c>
-      <c r="E43" s="40" t="n"/>
+      <c r="D43" s="35">
+        <f>'HOLERITE AGO.26'!C26</f>
+        <v/>
+      </c>
+      <c r="E43" s="41" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="29" t="inlineStr">
+      <c r="A44" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B44" s="29" t="inlineStr">
+      <c r="B44" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C44" s="29" t="inlineStr">
+      <c r="C44" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D44" s="34">
-        <f>'HOLERITE AGO.26'!C25</f>
-        <v/>
-      </c>
-      <c r="E44" s="40" t="n"/>
+      <c r="D44" s="35">
+        <f>'HOLERITE AGO.26'!C27</f>
+        <v/>
+      </c>
+      <c r="E44" s="41" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="29" t="inlineStr">
+      <c r="A45" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B45" s="29" t="inlineStr">
+      <c r="B45" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C45" s="29" t="inlineStr">
+      <c r="C45" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D45" s="34">
-        <f>'HOLERITE AGO.26'!C26</f>
-        <v/>
-      </c>
-      <c r="E45" s="40" t="n"/>
+      <c r="D45" s="35">
+        <f>'HOLERITE AGO.26'!C28</f>
+        <v/>
+      </c>
+      <c r="E45" s="41" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="29" t="inlineStr">
+      <c r="A46" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B46" s="29" t="inlineStr">
+      <c r="B46" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C46" s="29" t="inlineStr">
+      <c r="C46" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D46" s="34">
-        <f>'HOLERITE AGO.26'!C27</f>
-        <v/>
-      </c>
-      <c r="E46" s="40" t="n"/>
+      <c r="D46" s="35">
+        <f>'HOLERITE AGO.26'!C29</f>
+        <v/>
+      </c>
+      <c r="E46" s="41" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="29" t="inlineStr">
+      <c r="A47" s="30" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B47" s="29" t="inlineStr">
+      <c r="B47" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C47" s="29" t="inlineStr">
+      <c r="C47" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D47" s="34">
-        <f>'HOLERITE AGO.26'!C28</f>
-        <v/>
-      </c>
-      <c r="E47" s="40" t="n"/>
+      <c r="D47" s="35">
+        <f>'HOLERITE AGO.26'!C30</f>
+        <v/>
+      </c>
+      <c r="E47" s="41" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="41" t="inlineStr">
+      <c r="A48" s="42" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B48" s="41" t="inlineStr">
+      <c r="B48" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C48" s="41" t="inlineStr">
+      <c r="C48" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D48" s="42">
-        <f>'HOLERITE AGO.26'!C29</f>
+      <c r="D48" s="43">
+        <f>'HOLERITE AGO.26'!C31</f>
         <v/>
       </c>
       <c r="E48" s="18" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="43" t="inlineStr">
+      <c r="A49" s="44" t="inlineStr">
         <is>
           <t>AGNOR</t>
         </is>
       </c>
-      <c r="B49" s="44" t="inlineStr">
+      <c r="B49" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C49" s="44" t="inlineStr">
+      <c r="C49" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D49" s="45">
-        <f>'HOLERITE AGO.26'!C31</f>
-        <v/>
-      </c>
-      <c r="E49" s="46" t="n"/>
+      <c r="D49" s="46">
+        <f>'HOLERITE AGO.26'!C33</f>
+        <v/>
+      </c>
+      <c r="E49" s="47" t="n"/>
     </row>
     <row r="51">
-      <c r="A51" s="29" t="inlineStr">
+      <c r="A51" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B51" s="29" t="inlineStr">
+      <c r="B51" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C51" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D51" s="34">
+      <c r="C51" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D51" s="35">
         <f>'HOLERITE AGO.26'!D6</f>
         <v/>
       </c>
-      <c r="E51" s="40" t="n"/>
+      <c r="E51" s="41" t="n"/>
     </row>
     <row r="52">
-      <c r="A52" s="29" t="inlineStr">
+      <c r="A52" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B52" s="29" t="inlineStr">
+      <c r="B52" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C52" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D52" s="34">
+      <c r="C52" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D52" s="35">
         <f>'HOLERITE AGO.26'!D7</f>
         <v/>
       </c>
-      <c r="E52" s="40" t="n"/>
+      <c r="E52" s="41" t="n"/>
     </row>
     <row r="53">
-      <c r="A53" s="29" t="inlineStr">
+      <c r="A53" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B53" s="29" t="inlineStr">
+      <c r="B53" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C53" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D53" s="34">
+      <c r="C53" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D53" s="35">
         <f>'HOLERITE AGO.26'!D8</f>
         <v/>
       </c>
-      <c r="E53" s="40" t="n"/>
+      <c r="E53" s="41" t="n"/>
     </row>
     <row r="54">
-      <c r="A54" s="29" t="inlineStr">
+      <c r="A54" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B54" s="29" t="inlineStr">
+      <c r="B54" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C54" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D54" s="34">
+      <c r="C54" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D54" s="35">
         <f>'HOLERITE AGO.26'!D11</f>
         <v/>
       </c>
-      <c r="E54" s="40" t="n"/>
+      <c r="E54" s="41" t="n"/>
     </row>
     <row r="55">
-      <c r="A55" s="29" t="inlineStr">
+      <c r="A55" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B55" s="29" t="inlineStr">
+      <c r="B55" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C55" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D55" s="34">
+      <c r="C55" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D55" s="35">
         <f>'HOLERITE AGO.26'!D12</f>
         <v/>
       </c>
-      <c r="E55" s="40" t="n"/>
+      <c r="E55" s="41" t="n"/>
     </row>
     <row r="56">
-      <c r="A56" s="29" t="inlineStr">
+      <c r="A56" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B56" s="29" t="inlineStr">
+      <c r="B56" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C56" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D56" s="34">
+      <c r="C56" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D56" s="35">
         <f>'HOLERITE AGO.26'!D13</f>
         <v/>
       </c>
-      <c r="E56" s="40" t="n"/>
+      <c r="E56" s="41" t="n"/>
     </row>
     <row r="57">
-      <c r="A57" s="29" t="inlineStr">
+      <c r="A57" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B57" s="29" t="inlineStr">
+      <c r="B57" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C57" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D57" s="34">
+      <c r="C57" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D57" s="35">
         <f>'HOLERITE AGO.26'!D14</f>
         <v/>
       </c>
-      <c r="E57" s="40" t="n"/>
+      <c r="E57" s="41" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="29" t="inlineStr">
+      <c r="A58" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B58" s="29" t="inlineStr">
+      <c r="B58" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C58" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D58" s="34">
+      <c r="C58" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D58" s="35">
         <f>'HOLERITE AGO.26'!D15</f>
         <v/>
       </c>
-      <c r="E58" s="40" t="n"/>
+      <c r="E58" s="41" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="29" t="inlineStr">
+      <c r="A59" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B59" s="29" t="inlineStr">
+      <c r="B59" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C59" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D59" s="34">
+      <c r="C59" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D59" s="35">
         <f>'HOLERITE AGO.26'!D16</f>
         <v/>
       </c>
-      <c r="E59" s="40" t="n"/>
+      <c r="E59" s="41" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="29" t="inlineStr">
+      <c r="A60" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B60" s="29" t="inlineStr">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C60" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D60" s="34">
-        <f>'HOLERITE AGO.26'!D17</f>
-        <v/>
-      </c>
-      <c r="E60" s="40" t="n"/>
+      <c r="C60" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D60" s="35">
+        <f>'HOLERITE AGO.26'!D19</f>
+        <v/>
+      </c>
+      <c r="E60" s="41" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="29" t="inlineStr">
+      <c r="A61" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B61" s="29" t="inlineStr">
+      <c r="B61" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C61" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D61" s="34">
-        <f>'HOLERITE AGO.26'!D18</f>
-        <v/>
-      </c>
-      <c r="E61" s="40" t="n"/>
+      <c r="C61" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D61" s="35">
+        <f>'HOLERITE AGO.26'!D20</f>
+        <v/>
+      </c>
+      <c r="E61" s="41" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="29" t="inlineStr">
+      <c r="A62" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B62" s="29" t="inlineStr">
+      <c r="B62" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C62" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D62" s="34">
-        <f>'HOLERITE AGO.26'!D19</f>
-        <v/>
-      </c>
-      <c r="E62" s="40" t="n"/>
+      <c r="C62" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D62" s="35">
+        <f>'HOLERITE AGO.26'!D21</f>
+        <v/>
+      </c>
+      <c r="E62" s="41" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="41" t="inlineStr">
+      <c r="A63" s="42" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B63" s="41" t="inlineStr">
+      <c r="B63" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C63" s="41" t="inlineStr">
+      <c r="C63" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D63" s="42">
-        <f>'HOLERITE AGO.26'!D20</f>
+      <c r="D63" s="43">
+        <f>'HOLERITE AGO.26'!D22</f>
         <v/>
       </c>
       <c r="E63" s="18" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="29" t="inlineStr">
+      <c r="A64" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B64" s="29" t="inlineStr">
+      <c r="B64" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C64" s="29" t="inlineStr">
+      <c r="C64" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D64" s="34">
-        <f>'HOLERITE AGO.26'!D22</f>
-        <v/>
-      </c>
-      <c r="E64" s="40" t="n"/>
+      <c r="D64" s="35">
+        <f>'HOLERITE AGO.26'!D24</f>
+        <v/>
+      </c>
+      <c r="E64" s="41" t="n"/>
     </row>
     <row r="65">
-      <c r="A65" s="29" t="inlineStr">
+      <c r="A65" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B65" s="29" t="inlineStr">
+      <c r="B65" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C65" s="29" t="inlineStr">
+      <c r="C65" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D65" s="34">
-        <f>'HOLERITE AGO.26'!D23</f>
-        <v/>
-      </c>
-      <c r="E65" s="40" t="n"/>
+      <c r="D65" s="35">
+        <f>'HOLERITE AGO.26'!D25</f>
+        <v/>
+      </c>
+      <c r="E65" s="41" t="n"/>
     </row>
     <row r="66">
-      <c r="A66" s="29" t="inlineStr">
+      <c r="A66" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B66" s="29" t="inlineStr">
+      <c r="B66" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C66" s="29" t="inlineStr">
+      <c r="C66" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D66" s="34">
-        <f>'HOLERITE AGO.26'!D24</f>
-        <v/>
-      </c>
-      <c r="E66" s="40" t="n"/>
+      <c r="D66" s="35">
+        <f>'HOLERITE AGO.26'!D26</f>
+        <v/>
+      </c>
+      <c r="E66" s="41" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="29" t="inlineStr">
+      <c r="A67" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B67" s="29" t="inlineStr">
+      <c r="B67" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C67" s="29" t="inlineStr">
+      <c r="C67" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D67" s="34">
-        <f>'HOLERITE AGO.26'!D25</f>
-        <v/>
-      </c>
-      <c r="E67" s="40" t="n"/>
+      <c r="D67" s="35">
+        <f>'HOLERITE AGO.26'!D27</f>
+        <v/>
+      </c>
+      <c r="E67" s="41" t="n"/>
     </row>
     <row r="68">
-      <c r="A68" s="29" t="inlineStr">
+      <c r="A68" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B68" s="29" t="inlineStr">
+      <c r="B68" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C68" s="29" t="inlineStr">
+      <c r="C68" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D68" s="34">
-        <f>'HOLERITE AGO.26'!D26</f>
-        <v/>
-      </c>
-      <c r="E68" s="40" t="n"/>
+      <c r="D68" s="35">
+        <f>'HOLERITE AGO.26'!D28</f>
+        <v/>
+      </c>
+      <c r="E68" s="41" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="29" t="inlineStr">
+      <c r="A69" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B69" s="29" t="inlineStr">
+      <c r="B69" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C69" s="29" t="inlineStr">
+      <c r="C69" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D69" s="34">
-        <f>'HOLERITE AGO.26'!D27</f>
-        <v/>
-      </c>
-      <c r="E69" s="40" t="n"/>
+      <c r="D69" s="35">
+        <f>'HOLERITE AGO.26'!D29</f>
+        <v/>
+      </c>
+      <c r="E69" s="41" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="29" t="inlineStr">
+      <c r="A70" s="30" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B70" s="29" t="inlineStr">
+      <c r="B70" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C70" s="29" t="inlineStr">
+      <c r="C70" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D70" s="34">
-        <f>'HOLERITE AGO.26'!D28</f>
-        <v/>
-      </c>
-      <c r="E70" s="40" t="n"/>
+      <c r="D70" s="35">
+        <f>'HOLERITE AGO.26'!D30</f>
+        <v/>
+      </c>
+      <c r="E70" s="41" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="41" t="inlineStr">
+      <c r="A71" s="42" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B71" s="41" t="inlineStr">
+      <c r="B71" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C71" s="41" t="inlineStr">
+      <c r="C71" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D71" s="42">
-        <f>'HOLERITE AGO.26'!D29</f>
+      <c r="D71" s="43">
+        <f>'HOLERITE AGO.26'!D31</f>
         <v/>
       </c>
       <c r="E71" s="18" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="43" t="inlineStr">
+      <c r="A72" s="44" t="inlineStr">
         <is>
           <t>EDEY</t>
         </is>
       </c>
-      <c r="B72" s="44" t="inlineStr">
+      <c r="B72" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C72" s="44" t="inlineStr">
+      <c r="C72" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D72" s="45">
-        <f>'HOLERITE AGO.26'!D31</f>
-        <v/>
-      </c>
-      <c r="E72" s="46" t="n"/>
+      <c r="D72" s="46">
+        <f>'HOLERITE AGO.26'!D33</f>
+        <v/>
+      </c>
+      <c r="E72" s="47" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="29" t="inlineStr">
+      <c r="A74" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B74" s="29" t="inlineStr">
+      <c r="B74" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C74" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D74" s="34">
+      <c r="C74" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D74" s="35">
         <f>'HOLERITE AGO.26'!E6</f>
         <v/>
       </c>
-      <c r="E74" s="40" t="n"/>
+      <c r="E74" s="41" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="29" t="inlineStr">
+      <c r="A75" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B75" s="29" t="inlineStr">
+      <c r="B75" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C75" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D75" s="34">
+      <c r="C75" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D75" s="35">
         <f>'HOLERITE AGO.26'!E7</f>
         <v/>
       </c>
-      <c r="E75" s="40" t="n"/>
+      <c r="E75" s="41" t="n"/>
     </row>
     <row r="76">
-      <c r="A76" s="29" t="inlineStr">
+      <c r="A76" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B76" s="29" t="inlineStr">
+      <c r="B76" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C76" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D76" s="34">
+      <c r="C76" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D76" s="35">
         <f>'HOLERITE AGO.26'!E8</f>
         <v/>
       </c>
-      <c r="E76" s="40" t="n"/>
+      <c r="E76" s="41" t="n"/>
     </row>
     <row r="77">
-      <c r="A77" s="29" t="inlineStr">
+      <c r="A77" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B77" s="29" t="inlineStr">
+      <c r="B77" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C77" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D77" s="34">
+      <c r="C77" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D77" s="35">
         <f>'HOLERITE AGO.26'!E11</f>
         <v/>
       </c>
-      <c r="E77" s="40" t="n"/>
+      <c r="E77" s="41" t="n"/>
     </row>
     <row r="78">
-      <c r="A78" s="29" t="inlineStr">
+      <c r="A78" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B78" s="29" t="inlineStr">
+      <c r="B78" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C78" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D78" s="34">
+      <c r="C78" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D78" s="35">
         <f>'HOLERITE AGO.26'!E12</f>
         <v/>
       </c>
-      <c r="E78" s="40" t="n"/>
+      <c r="E78" s="41" t="n"/>
     </row>
     <row r="79">
-      <c r="A79" s="29" t="inlineStr">
+      <c r="A79" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B79" s="29" t="inlineStr">
+      <c r="B79" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C79" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D79" s="34">
+      <c r="C79" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D79" s="35">
         <f>'HOLERITE AGO.26'!E13</f>
         <v/>
       </c>
-      <c r="E79" s="40" t="n"/>
+      <c r="E79" s="41" t="n"/>
     </row>
     <row r="80">
-      <c r="A80" s="29" t="inlineStr">
+      <c r="A80" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B80" s="29" t="inlineStr">
+      <c r="B80" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C80" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D80" s="34">
+      <c r="C80" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D80" s="35">
         <f>'HOLERITE AGO.26'!E14</f>
         <v/>
       </c>
-      <c r="E80" s="40" t="n"/>
+      <c r="E80" s="41" t="n"/>
     </row>
     <row r="81">
-      <c r="A81" s="29" t="inlineStr">
+      <c r="A81" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B81" s="29" t="inlineStr">
+      <c r="B81" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C81" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D81" s="34">
+      <c r="C81" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D81" s="35">
         <f>'HOLERITE AGO.26'!E15</f>
         <v/>
       </c>
-      <c r="E81" s="40" t="n"/>
+      <c r="E81" s="41" t="n"/>
     </row>
     <row r="82">
-      <c r="A82" s="29" t="inlineStr">
+      <c r="A82" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B82" s="29" t="inlineStr">
+      <c r="B82" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C82" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D82" s="34">
+      <c r="C82" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D82" s="35">
         <f>'HOLERITE AGO.26'!E16</f>
         <v/>
       </c>
-      <c r="E82" s="40" t="n"/>
+      <c r="E82" s="41" t="n"/>
     </row>
     <row r="83">
-      <c r="A83" s="29" t="inlineStr">
+      <c r="A83" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B83" s="29" t="inlineStr">
+      <c r="B83" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C83" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D83" s="34">
-        <f>'HOLERITE AGO.26'!E17</f>
-        <v/>
-      </c>
-      <c r="E83" s="40" t="n"/>
+      <c r="C83" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D83" s="35">
+        <f>'HOLERITE AGO.26'!E19</f>
+        <v/>
+      </c>
+      <c r="E83" s="41" t="n"/>
     </row>
     <row r="84">
-      <c r="A84" s="29" t="inlineStr">
+      <c r="A84" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B84" s="29" t="inlineStr">
+      <c r="B84" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C84" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D84" s="34">
-        <f>'HOLERITE AGO.26'!E18</f>
-        <v/>
-      </c>
-      <c r="E84" s="40" t="n"/>
+      <c r="C84" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D84" s="35">
+        <f>'HOLERITE AGO.26'!E20</f>
+        <v/>
+      </c>
+      <c r="E84" s="41" t="n"/>
     </row>
     <row r="85">
-      <c r="A85" s="29" t="inlineStr">
+      <c r="A85" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B85" s="29" t="inlineStr">
+      <c r="B85" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C85" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D85" s="34">
-        <f>'HOLERITE AGO.26'!E19</f>
-        <v/>
-      </c>
-      <c r="E85" s="40" t="n"/>
+      <c r="C85" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D85" s="35">
+        <f>'HOLERITE AGO.26'!E21</f>
+        <v/>
+      </c>
+      <c r="E85" s="41" t="n"/>
     </row>
     <row r="86">
-      <c r="A86" s="41" t="inlineStr">
+      <c r="A86" s="42" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B86" s="41" t="inlineStr">
+      <c r="B86" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C86" s="41" t="inlineStr">
+      <c r="C86" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D86" s="42">
-        <f>'HOLERITE AGO.26'!E20</f>
+      <c r="D86" s="43">
+        <f>'HOLERITE AGO.26'!E22</f>
         <v/>
       </c>
       <c r="E86" s="18" t="n"/>
     </row>
     <row r="87">
-      <c r="A87" s="29" t="inlineStr">
+      <c r="A87" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B87" s="29" t="inlineStr">
+      <c r="B87" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C87" s="29" t="inlineStr">
+      <c r="C87" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D87" s="34">
-        <f>'HOLERITE AGO.26'!E22</f>
-        <v/>
-      </c>
-      <c r="E87" s="40" t="n"/>
+      <c r="D87" s="35">
+        <f>'HOLERITE AGO.26'!E24</f>
+        <v/>
+      </c>
+      <c r="E87" s="41" t="n"/>
     </row>
     <row r="88">
-      <c r="A88" s="29" t="inlineStr">
+      <c r="A88" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B88" s="29" t="inlineStr">
+      <c r="B88" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C88" s="29" t="inlineStr">
+      <c r="C88" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D88" s="34">
-        <f>'HOLERITE AGO.26'!E23</f>
-        <v/>
-      </c>
-      <c r="E88" s="40" t="n"/>
+      <c r="D88" s="35">
+        <f>'HOLERITE AGO.26'!E25</f>
+        <v/>
+      </c>
+      <c r="E88" s="41" t="n"/>
     </row>
     <row r="89">
-      <c r="A89" s="29" t="inlineStr">
+      <c r="A89" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B89" s="29" t="inlineStr">
+      <c r="B89" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C89" s="29" t="inlineStr">
+      <c r="C89" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D89" s="34">
-        <f>'HOLERITE AGO.26'!E24</f>
-        <v/>
-      </c>
-      <c r="E89" s="40" t="n"/>
+      <c r="D89" s="35">
+        <f>'HOLERITE AGO.26'!E26</f>
+        <v/>
+      </c>
+      <c r="E89" s="41" t="n"/>
     </row>
     <row r="90">
-      <c r="A90" s="29" t="inlineStr">
+      <c r="A90" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B90" s="29" t="inlineStr">
+      <c r="B90" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C90" s="29" t="inlineStr">
+      <c r="C90" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D90" s="34">
-        <f>'HOLERITE AGO.26'!E25</f>
-        <v/>
-      </c>
-      <c r="E90" s="40" t="n"/>
+      <c r="D90" s="35">
+        <f>'HOLERITE AGO.26'!E27</f>
+        <v/>
+      </c>
+      <c r="E90" s="41" t="n"/>
     </row>
     <row r="91">
-      <c r="A91" s="29" t="inlineStr">
+      <c r="A91" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B91" s="29" t="inlineStr">
+      <c r="B91" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C91" s="29" t="inlineStr">
+      <c r="C91" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D91" s="34">
-        <f>'HOLERITE AGO.26'!E26</f>
-        <v/>
-      </c>
-      <c r="E91" s="40" t="n"/>
+      <c r="D91" s="35">
+        <f>'HOLERITE AGO.26'!E28</f>
+        <v/>
+      </c>
+      <c r="E91" s="41" t="n"/>
     </row>
     <row r="92">
-      <c r="A92" s="29" t="inlineStr">
+      <c r="A92" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B92" s="29" t="inlineStr">
+      <c r="B92" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C92" s="29" t="inlineStr">
+      <c r="C92" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D92" s="34">
-        <f>'HOLERITE AGO.26'!E27</f>
-        <v/>
-      </c>
-      <c r="E92" s="40" t="n"/>
+      <c r="D92" s="35">
+        <f>'HOLERITE AGO.26'!E29</f>
+        <v/>
+      </c>
+      <c r="E92" s="41" t="n"/>
     </row>
     <row r="93">
-      <c r="A93" s="29" t="inlineStr">
+      <c r="A93" s="30" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B93" s="29" t="inlineStr">
+      <c r="B93" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C93" s="29" t="inlineStr">
+      <c r="C93" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D93" s="34">
-        <f>'HOLERITE AGO.26'!E28</f>
-        <v/>
-      </c>
-      <c r="E93" s="40" t="n"/>
+      <c r="D93" s="35">
+        <f>'HOLERITE AGO.26'!E30</f>
+        <v/>
+      </c>
+      <c r="E93" s="41" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="41" t="inlineStr">
+      <c r="A94" s="42" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B94" s="41" t="inlineStr">
+      <c r="B94" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C94" s="41" t="inlineStr">
+      <c r="C94" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D94" s="42">
-        <f>'HOLERITE AGO.26'!E29</f>
+      <c r="D94" s="43">
+        <f>'HOLERITE AGO.26'!E31</f>
         <v/>
       </c>
       <c r="E94" s="18" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="43" t="inlineStr">
+      <c r="A95" s="44" t="inlineStr">
         <is>
           <t>JOEL</t>
         </is>
       </c>
-      <c r="B95" s="44" t="inlineStr">
+      <c r="B95" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C95" s="44" t="inlineStr">
+      <c r="C95" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D95" s="45">
-        <f>'HOLERITE AGO.26'!E31</f>
-        <v/>
-      </c>
-      <c r="E95" s="46" t="n"/>
+      <c r="D95" s="46">
+        <f>'HOLERITE AGO.26'!E33</f>
+        <v/>
+      </c>
+      <c r="E95" s="47" t="n"/>
     </row>
     <row r="97">
-      <c r="A97" s="29" t="inlineStr">
+      <c r="A97" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B97" s="29" t="inlineStr">
+      <c r="B97" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C97" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D97" s="34">
+      <c r="C97" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D97" s="35">
         <f>'HOLERITE AGO.26'!F6</f>
         <v/>
       </c>
-      <c r="E97" s="40" t="n"/>
+      <c r="E97" s="41" t="n"/>
     </row>
     <row r="98">
-      <c r="A98" s="29" t="inlineStr">
+      <c r="A98" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B98" s="29" t="inlineStr">
+      <c r="B98" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C98" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D98" s="34">
+      <c r="C98" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D98" s="35">
         <f>'HOLERITE AGO.26'!F7</f>
         <v/>
       </c>
-      <c r="E98" s="40" t="n"/>
+      <c r="E98" s="41" t="n"/>
     </row>
     <row r="99">
-      <c r="A99" s="29" t="inlineStr">
+      <c r="A99" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B99" s="29" t="inlineStr">
+      <c r="B99" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C99" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D99" s="34">
+      <c r="C99" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D99" s="35">
         <f>'HOLERITE AGO.26'!F8</f>
         <v/>
       </c>
-      <c r="E99" s="40" t="n"/>
+      <c r="E99" s="41" t="n"/>
     </row>
     <row r="100">
-      <c r="A100" s="29" t="inlineStr">
+      <c r="A100" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B100" s="29" t="inlineStr">
+      <c r="B100" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C100" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D100" s="34">
+      <c r="C100" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D100" s="35">
         <f>'HOLERITE AGO.26'!F11</f>
         <v/>
       </c>
-      <c r="E100" s="40" t="n"/>
+      <c r="E100" s="41" t="n"/>
     </row>
     <row r="101">
-      <c r="A101" s="29" t="inlineStr">
+      <c r="A101" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B101" s="29" t="inlineStr">
+      <c r="B101" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C101" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D101" s="34">
+      <c r="C101" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D101" s="35">
         <f>'HOLERITE AGO.26'!F12</f>
         <v/>
       </c>
-      <c r="E101" s="40" t="n"/>
+      <c r="E101" s="41" t="n"/>
     </row>
     <row r="102">
-      <c r="A102" s="29" t="inlineStr">
+      <c r="A102" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B102" s="29" t="inlineStr">
+      <c r="B102" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C102" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D102" s="34">
+      <c r="C102" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D102" s="35">
         <f>'HOLERITE AGO.26'!F13</f>
         <v/>
       </c>
-      <c r="E102" s="40" t="n"/>
+      <c r="E102" s="41" t="n"/>
     </row>
     <row r="103">
-      <c r="A103" s="29" t="inlineStr">
+      <c r="A103" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B103" s="29" t="inlineStr">
+      <c r="B103" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C103" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D103" s="34">
+      <c r="C103" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D103" s="35">
         <f>'HOLERITE AGO.26'!F14</f>
         <v/>
       </c>
-      <c r="E103" s="40" t="n"/>
+      <c r="E103" s="41" t="n"/>
     </row>
     <row r="104">
-      <c r="A104" s="29" t="inlineStr">
+      <c r="A104" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B104" s="29" t="inlineStr">
+      <c r="B104" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C104" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D104" s="34">
+      <c r="C104" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D104" s="35">
         <f>'HOLERITE AGO.26'!F15</f>
         <v/>
       </c>
-      <c r="E104" s="40" t="n"/>
+      <c r="E104" s="41" t="n"/>
     </row>
     <row r="105">
-      <c r="A105" s="29" t="inlineStr">
+      <c r="A105" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B105" s="29" t="inlineStr">
+      <c r="B105" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C105" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D105" s="34">
+      <c r="C105" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D105" s="35">
         <f>'HOLERITE AGO.26'!F16</f>
         <v/>
       </c>
-      <c r="E105" s="40" t="n"/>
+      <c r="E105" s="41" t="n"/>
     </row>
     <row r="106">
-      <c r="A106" s="29" t="inlineStr">
+      <c r="A106" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B106" s="29" t="inlineStr">
+      <c r="B106" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C106" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D106" s="34">
-        <f>'HOLERITE AGO.26'!F17</f>
-        <v/>
-      </c>
-      <c r="E106" s="40" t="n"/>
+      <c r="C106" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D106" s="35">
+        <f>'HOLERITE AGO.26'!F19</f>
+        <v/>
+      </c>
+      <c r="E106" s="41" t="n"/>
     </row>
     <row r="107">
-      <c r="A107" s="29" t="inlineStr">
+      <c r="A107" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B107" s="29" t="inlineStr">
+      <c r="B107" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C107" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D107" s="34">
-        <f>'HOLERITE AGO.26'!F18</f>
-        <v/>
-      </c>
-      <c r="E107" s="40" t="n"/>
+      <c r="C107" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D107" s="35">
+        <f>'HOLERITE AGO.26'!F20</f>
+        <v/>
+      </c>
+      <c r="E107" s="41" t="n"/>
     </row>
     <row r="108">
-      <c r="A108" s="29" t="inlineStr">
+      <c r="A108" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B108" s="29" t="inlineStr">
+      <c r="B108" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C108" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D108" s="34">
-        <f>'HOLERITE AGO.26'!F19</f>
-        <v/>
-      </c>
-      <c r="E108" s="40" t="n"/>
+      <c r="C108" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D108" s="35">
+        <f>'HOLERITE AGO.26'!F21</f>
+        <v/>
+      </c>
+      <c r="E108" s="41" t="n"/>
     </row>
     <row r="109">
-      <c r="A109" s="41" t="inlineStr">
+      <c r="A109" s="42" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B109" s="41" t="inlineStr">
+      <c r="B109" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C109" s="41" t="inlineStr">
+      <c r="C109" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D109" s="42">
-        <f>'HOLERITE AGO.26'!F20</f>
+      <c r="D109" s="43">
+        <f>'HOLERITE AGO.26'!F22</f>
         <v/>
       </c>
       <c r="E109" s="18" t="n"/>
     </row>
     <row r="110">
-      <c r="A110" s="29" t="inlineStr">
+      <c r="A110" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B110" s="29" t="inlineStr">
+      <c r="B110" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C110" s="29" t="inlineStr">
+      <c r="C110" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D110" s="34">
-        <f>'HOLERITE AGO.26'!F22</f>
-        <v/>
-      </c>
-      <c r="E110" s="40" t="n"/>
+      <c r="D110" s="35">
+        <f>'HOLERITE AGO.26'!F24</f>
+        <v/>
+      </c>
+      <c r="E110" s="41" t="n"/>
     </row>
     <row r="111">
-      <c r="A111" s="29" t="inlineStr">
+      <c r="A111" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B111" s="29" t="inlineStr">
+      <c r="B111" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C111" s="29" t="inlineStr">
+      <c r="C111" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D111" s="34">
-        <f>'HOLERITE AGO.26'!F23</f>
-        <v/>
-      </c>
-      <c r="E111" s="40" t="n"/>
+      <c r="D111" s="35">
+        <f>'HOLERITE AGO.26'!F25</f>
+        <v/>
+      </c>
+      <c r="E111" s="41" t="n"/>
     </row>
     <row r="112">
-      <c r="A112" s="29" t="inlineStr">
+      <c r="A112" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B112" s="29" t="inlineStr">
+      <c r="B112" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C112" s="29" t="inlineStr">
+      <c r="C112" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D112" s="34">
-        <f>'HOLERITE AGO.26'!F24</f>
-        <v/>
-      </c>
-      <c r="E112" s="40" t="n"/>
+      <c r="D112" s="35">
+        <f>'HOLERITE AGO.26'!F26</f>
+        <v/>
+      </c>
+      <c r="E112" s="41" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="29" t="inlineStr">
+      <c r="A113" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B113" s="29" t="inlineStr">
+      <c r="B113" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C113" s="29" t="inlineStr">
+      <c r="C113" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D113" s="34">
-        <f>'HOLERITE AGO.26'!F25</f>
-        <v/>
-      </c>
-      <c r="E113" s="40" t="n"/>
+      <c r="D113" s="35">
+        <f>'HOLERITE AGO.26'!F27</f>
+        <v/>
+      </c>
+      <c r="E113" s="41" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="29" t="inlineStr">
+      <c r="A114" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B114" s="29" t="inlineStr">
+      <c r="B114" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C114" s="29" t="inlineStr">
+      <c r="C114" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D114" s="34">
-        <f>'HOLERITE AGO.26'!F26</f>
-        <v/>
-      </c>
-      <c r="E114" s="40" t="n"/>
+      <c r="D114" s="35">
+        <f>'HOLERITE AGO.26'!F28</f>
+        <v/>
+      </c>
+      <c r="E114" s="41" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="29" t="inlineStr">
+      <c r="A115" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B115" s="29" t="inlineStr">
+      <c r="B115" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C115" s="29" t="inlineStr">
+      <c r="C115" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D115" s="34">
-        <f>'HOLERITE AGO.26'!F27</f>
-        <v/>
-      </c>
-      <c r="E115" s="40" t="n"/>
+      <c r="D115" s="35">
+        <f>'HOLERITE AGO.26'!F29</f>
+        <v/>
+      </c>
+      <c r="E115" s="41" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="29" t="inlineStr">
+      <c r="A116" s="30" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B116" s="29" t="inlineStr">
+      <c r="B116" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C116" s="29" t="inlineStr">
+      <c r="C116" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D116" s="34">
-        <f>'HOLERITE AGO.26'!F28</f>
-        <v/>
-      </c>
-      <c r="E116" s="40" t="n"/>
+      <c r="D116" s="35">
+        <f>'HOLERITE AGO.26'!F30</f>
+        <v/>
+      </c>
+      <c r="E116" s="41" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="41" t="inlineStr">
+      <c r="A117" s="42" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B117" s="41" t="inlineStr">
+      <c r="B117" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C117" s="41" t="inlineStr">
+      <c r="C117" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D117" s="42">
-        <f>'HOLERITE AGO.26'!F29</f>
+      <c r="D117" s="43">
+        <f>'HOLERITE AGO.26'!F31</f>
         <v/>
       </c>
       <c r="E117" s="18" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="43" t="inlineStr">
+      <c r="A118" s="44" t="inlineStr">
         <is>
           <t>VALÉRIA</t>
         </is>
       </c>
-      <c r="B118" s="44" t="inlineStr">
+      <c r="B118" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C118" s="44" t="inlineStr">
+      <c r="C118" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D118" s="45">
-        <f>'HOLERITE AGO.26'!F31</f>
-        <v/>
-      </c>
-      <c r="E118" s="46" t="n"/>
+      <c r="D118" s="46">
+        <f>'HOLERITE AGO.26'!F33</f>
+        <v/>
+      </c>
+      <c r="E118" s="47" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="29" t="inlineStr">
+      <c r="A120" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B120" s="29" t="inlineStr">
+      <c r="B120" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C120" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D120" s="34">
+      <c r="C120" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D120" s="35">
         <f>'HOLERITE AGO.26'!G6</f>
         <v/>
       </c>
-      <c r="E120" s="40" t="n"/>
+      <c r="E120" s="41" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="29" t="inlineStr">
+      <c r="A121" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B121" s="29" t="inlineStr">
+      <c r="B121" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C121" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D121" s="34">
+      <c r="C121" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D121" s="35">
         <f>'HOLERITE AGO.26'!G7</f>
         <v/>
       </c>
-      <c r="E121" s="40" t="n"/>
+      <c r="E121" s="41" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="29" t="inlineStr">
+      <c r="A122" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B122" s="29" t="inlineStr">
+      <c r="B122" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C122" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D122" s="34">
+      <c r="C122" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D122" s="35">
         <f>'HOLERITE AGO.26'!G8</f>
         <v/>
       </c>
-      <c r="E122" s="40" t="n"/>
+      <c r="E122" s="41" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="29" t="inlineStr">
+      <c r="A123" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B123" s="29" t="inlineStr">
+      <c r="B123" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C123" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D123" s="34">
+      <c r="C123" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D123" s="35">
         <f>'HOLERITE AGO.26'!G11</f>
         <v/>
       </c>
-      <c r="E123" s="40" t="n"/>
+      <c r="E123" s="41" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="29" t="inlineStr">
+      <c r="A124" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B124" s="29" t="inlineStr">
+      <c r="B124" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C124" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D124" s="34">
+      <c r="C124" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D124" s="35">
         <f>'HOLERITE AGO.26'!G12</f>
         <v/>
       </c>
-      <c r="E124" s="40" t="n"/>
+      <c r="E124" s="41" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="29" t="inlineStr">
+      <c r="A125" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B125" s="29" t="inlineStr">
+      <c r="B125" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C125" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D125" s="34">
+      <c r="C125" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D125" s="35">
         <f>'HOLERITE AGO.26'!G13</f>
         <v/>
       </c>
-      <c r="E125" s="40" t="n"/>
+      <c r="E125" s="41" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="29" t="inlineStr">
+      <c r="A126" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B126" s="29" t="inlineStr">
+      <c r="B126" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C126" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D126" s="34">
+      <c r="C126" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D126" s="35">
         <f>'HOLERITE AGO.26'!G14</f>
         <v/>
       </c>
-      <c r="E126" s="40" t="n"/>
+      <c r="E126" s="41" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="29" t="inlineStr">
+      <c r="A127" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B127" s="29" t="inlineStr">
+      <c r="B127" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C127" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D127" s="34">
+      <c r="C127" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D127" s="35">
         <f>'HOLERITE AGO.26'!G15</f>
         <v/>
       </c>
-      <c r="E127" s="40" t="n"/>
+      <c r="E127" s="41" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="29" t="inlineStr">
+      <c r="A128" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B128" s="29" t="inlineStr">
+      <c r="B128" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C128" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D128" s="34">
+      <c r="C128" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D128" s="35">
         <f>'HOLERITE AGO.26'!G16</f>
         <v/>
       </c>
-      <c r="E128" s="40" t="n"/>
+      <c r="E128" s="41" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="29" t="inlineStr">
+      <c r="A129" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B129" s="29" t="inlineStr">
+      <c r="B129" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C129" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D129" s="34">
-        <f>'HOLERITE AGO.26'!G17</f>
-        <v/>
-      </c>
-      <c r="E129" s="40" t="n"/>
+      <c r="C129" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D129" s="35">
+        <f>'HOLERITE AGO.26'!G19</f>
+        <v/>
+      </c>
+      <c r="E129" s="41" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="29" t="inlineStr">
+      <c r="A130" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B130" s="29" t="inlineStr">
+      <c r="B130" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C130" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D130" s="34">
-        <f>'HOLERITE AGO.26'!G18</f>
-        <v/>
-      </c>
-      <c r="E130" s="40" t="n"/>
+      <c r="C130" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D130" s="35">
+        <f>'HOLERITE AGO.26'!G20</f>
+        <v/>
+      </c>
+      <c r="E130" s="41" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="29" t="inlineStr">
+      <c r="A131" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B131" s="29" t="inlineStr">
+      <c r="B131" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C131" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D131" s="34">
-        <f>'HOLERITE AGO.26'!G19</f>
-        <v/>
-      </c>
-      <c r="E131" s="40" t="n"/>
+      <c r="C131" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D131" s="35">
+        <f>'HOLERITE AGO.26'!G21</f>
+        <v/>
+      </c>
+      <c r="E131" s="41" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="41" t="inlineStr">
+      <c r="A132" s="42" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B132" s="41" t="inlineStr">
+      <c r="B132" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C132" s="41" t="inlineStr">
+      <c r="C132" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D132" s="42">
-        <f>'HOLERITE AGO.26'!G20</f>
+      <c r="D132" s="43">
+        <f>'HOLERITE AGO.26'!G22</f>
         <v/>
       </c>
       <c r="E132" s="18" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="29" t="inlineStr">
+      <c r="A133" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B133" s="29" t="inlineStr">
+      <c r="B133" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C133" s="29" t="inlineStr">
+      <c r="C133" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D133" s="34">
-        <f>'HOLERITE AGO.26'!G22</f>
-        <v/>
-      </c>
-      <c r="E133" s="40" t="n"/>
+      <c r="D133" s="35">
+        <f>'HOLERITE AGO.26'!G24</f>
+        <v/>
+      </c>
+      <c r="E133" s="41" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="29" t="inlineStr">
+      <c r="A134" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B134" s="29" t="inlineStr">
+      <c r="B134" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C134" s="29" t="inlineStr">
+      <c r="C134" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D134" s="34">
-        <f>'HOLERITE AGO.26'!G23</f>
-        <v/>
-      </c>
-      <c r="E134" s="40" t="n"/>
+      <c r="D134" s="35">
+        <f>'HOLERITE AGO.26'!G25</f>
+        <v/>
+      </c>
+      <c r="E134" s="41" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="29" t="inlineStr">
+      <c r="A135" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B135" s="29" t="inlineStr">
+      <c r="B135" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C135" s="29" t="inlineStr">
+      <c r="C135" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D135" s="34">
-        <f>'HOLERITE AGO.26'!G24</f>
-        <v/>
-      </c>
-      <c r="E135" s="40" t="n"/>
+      <c r="D135" s="35">
+        <f>'HOLERITE AGO.26'!G26</f>
+        <v/>
+      </c>
+      <c r="E135" s="41" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="29" t="inlineStr">
+      <c r="A136" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B136" s="29" t="inlineStr">
+      <c r="B136" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C136" s="29" t="inlineStr">
+      <c r="C136" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D136" s="34">
-        <f>'HOLERITE AGO.26'!G25</f>
-        <v/>
-      </c>
-      <c r="E136" s="40" t="n"/>
+      <c r="D136" s="35">
+        <f>'HOLERITE AGO.26'!G27</f>
+        <v/>
+      </c>
+      <c r="E136" s="41" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="29" t="inlineStr">
+      <c r="A137" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B137" s="29" t="inlineStr">
+      <c r="B137" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C137" s="29" t="inlineStr">
+      <c r="C137" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D137" s="34">
-        <f>'HOLERITE AGO.26'!G26</f>
-        <v/>
-      </c>
-      <c r="E137" s="40" t="n"/>
+      <c r="D137" s="35">
+        <f>'HOLERITE AGO.26'!G28</f>
+        <v/>
+      </c>
+      <c r="E137" s="41" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="29" t="inlineStr">
+      <c r="A138" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B138" s="29" t="inlineStr">
+      <c r="B138" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C138" s="29" t="inlineStr">
+      <c r="C138" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D138" s="34">
-        <f>'HOLERITE AGO.26'!G27</f>
-        <v/>
-      </c>
-      <c r="E138" s="40" t="n"/>
+      <c r="D138" s="35">
+        <f>'HOLERITE AGO.26'!G29</f>
+        <v/>
+      </c>
+      <c r="E138" s="41" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="29" t="inlineStr">
+      <c r="A139" s="30" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B139" s="29" t="inlineStr">
+      <c r="B139" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C139" s="29" t="inlineStr">
+      <c r="C139" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D139" s="34">
-        <f>'HOLERITE AGO.26'!G28</f>
-        <v/>
-      </c>
-      <c r="E139" s="40" t="n"/>
+      <c r="D139" s="35">
+        <f>'HOLERITE AGO.26'!G30</f>
+        <v/>
+      </c>
+      <c r="E139" s="41" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="41" t="inlineStr">
+      <c r="A140" s="42" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B140" s="41" t="inlineStr">
+      <c r="B140" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C140" s="41" t="inlineStr">
+      <c r="C140" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D140" s="42">
-        <f>'HOLERITE AGO.26'!G29</f>
+      <c r="D140" s="43">
+        <f>'HOLERITE AGO.26'!G31</f>
         <v/>
       </c>
       <c r="E140" s="18" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="43" t="inlineStr">
+      <c r="A141" s="44" t="inlineStr">
         <is>
           <t>SARA</t>
         </is>
       </c>
-      <c r="B141" s="44" t="inlineStr">
+      <c r="B141" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C141" s="44" t="inlineStr">
+      <c r="C141" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D141" s="45">
-        <f>'HOLERITE AGO.26'!G31</f>
-        <v/>
-      </c>
-      <c r="E141" s="46" t="n"/>
+      <c r="D141" s="46">
+        <f>'HOLERITE AGO.26'!G33</f>
+        <v/>
+      </c>
+      <c r="E141" s="47" t="n"/>
     </row>
     <row r="143">
-      <c r="A143" s="29" t="inlineStr">
+      <c r="A143" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B143" s="29" t="inlineStr">
+      <c r="B143" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C143" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D143" s="34">
+      <c r="C143" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D143" s="35">
         <f>'HOLERITE AGO.26'!H6</f>
         <v/>
       </c>
-      <c r="E143" s="40" t="n"/>
+      <c r="E143" s="41" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="29" t="inlineStr">
+      <c r="A144" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B144" s="29" t="inlineStr">
+      <c r="B144" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C144" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D144" s="34">
+      <c r="C144" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D144" s="35">
         <f>'HOLERITE AGO.26'!H7</f>
         <v/>
       </c>
-      <c r="E144" s="40" t="n"/>
+      <c r="E144" s="41" t="n"/>
     </row>
     <row r="145">
-      <c r="A145" s="29" t="inlineStr">
+      <c r="A145" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B145" s="29" t="inlineStr">
+      <c r="B145" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C145" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D145" s="34">
+      <c r="C145" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D145" s="35">
         <f>'HOLERITE AGO.26'!H8</f>
         <v/>
       </c>
-      <c r="E145" s="40" t="n"/>
+      <c r="E145" s="41" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="29" t="inlineStr">
+      <c r="A146" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B146" s="29" t="inlineStr">
+      <c r="B146" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C146" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D146" s="34">
+      <c r="C146" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D146" s="35">
         <f>'HOLERITE AGO.26'!H11</f>
         <v/>
       </c>
-      <c r="E146" s="40" t="n"/>
+      <c r="E146" s="41" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="29" t="inlineStr">
+      <c r="A147" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B147" s="29" t="inlineStr">
+      <c r="B147" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C147" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D147" s="34">
+      <c r="C147" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D147" s="35">
         <f>'HOLERITE AGO.26'!H12</f>
         <v/>
       </c>
-      <c r="E147" s="40" t="n"/>
+      <c r="E147" s="41" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="29" t="inlineStr">
+      <c r="A148" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B148" s="29" t="inlineStr">
+      <c r="B148" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C148" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D148" s="34">
+      <c r="C148" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D148" s="35">
         <f>'HOLERITE AGO.26'!H13</f>
         <v/>
       </c>
-      <c r="E148" s="40" t="n"/>
+      <c r="E148" s="41" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="29" t="inlineStr">
+      <c r="A149" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B149" s="29" t="inlineStr">
+      <c r="B149" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C149" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D149" s="34">
+      <c r="C149" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D149" s="35">
         <f>'HOLERITE AGO.26'!H14</f>
         <v/>
       </c>
-      <c r="E149" s="40" t="n"/>
+      <c r="E149" s="41" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="29" t="inlineStr">
+      <c r="A150" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B150" s="29" t="inlineStr">
+      <c r="B150" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C150" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D150" s="34">
+      <c r="C150" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D150" s="35">
         <f>'HOLERITE AGO.26'!H15</f>
         <v/>
       </c>
-      <c r="E150" s="40" t="n"/>
+      <c r="E150" s="41" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="29" t="inlineStr">
+      <c r="A151" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B151" s="29" t="inlineStr">
+      <c r="B151" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C151" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D151" s="34">
+      <c r="C151" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D151" s="35">
         <f>'HOLERITE AGO.26'!H16</f>
         <v/>
       </c>
-      <c r="E151" s="40" t="n"/>
+      <c r="E151" s="41" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="29" t="inlineStr">
+      <c r="A152" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B152" s="29" t="inlineStr">
+      <c r="B152" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C152" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D152" s="34">
-        <f>'HOLERITE AGO.26'!H17</f>
-        <v/>
-      </c>
-      <c r="E152" s="40" t="n"/>
+      <c r="C152" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D152" s="35">
+        <f>'HOLERITE AGO.26'!H19</f>
+        <v/>
+      </c>
+      <c r="E152" s="41" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="29" t="inlineStr">
+      <c r="A153" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B153" s="29" t="inlineStr">
+      <c r="B153" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C153" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D153" s="34">
-        <f>'HOLERITE AGO.26'!H18</f>
-        <v/>
-      </c>
-      <c r="E153" s="40" t="n"/>
+      <c r="C153" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D153" s="35">
+        <f>'HOLERITE AGO.26'!H20</f>
+        <v/>
+      </c>
+      <c r="E153" s="41" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="29" t="inlineStr">
+      <c r="A154" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B154" s="29" t="inlineStr">
+      <c r="B154" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C154" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D154" s="34">
-        <f>'HOLERITE AGO.26'!H19</f>
-        <v/>
-      </c>
-      <c r="E154" s="40" t="n"/>
+      <c r="C154" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D154" s="35">
+        <f>'HOLERITE AGO.26'!H21</f>
+        <v/>
+      </c>
+      <c r="E154" s="41" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="41" t="inlineStr">
+      <c r="A155" s="42" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B155" s="41" t="inlineStr">
+      <c r="B155" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C155" s="41" t="inlineStr">
+      <c r="C155" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D155" s="42">
-        <f>'HOLERITE AGO.26'!H20</f>
+      <c r="D155" s="43">
+        <f>'HOLERITE AGO.26'!H22</f>
         <v/>
       </c>
       <c r="E155" s="18" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="29" t="inlineStr">
+      <c r="A156" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B156" s="29" t="inlineStr">
+      <c r="B156" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C156" s="29" t="inlineStr">
+      <c r="C156" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D156" s="34">
-        <f>'HOLERITE AGO.26'!H22</f>
-        <v/>
-      </c>
-      <c r="E156" s="40" t="n"/>
+      <c r="D156" s="35">
+        <f>'HOLERITE AGO.26'!H24</f>
+        <v/>
+      </c>
+      <c r="E156" s="41" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="29" t="inlineStr">
+      <c r="A157" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B157" s="29" t="inlineStr">
+      <c r="B157" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C157" s="29" t="inlineStr">
+      <c r="C157" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D157" s="34">
-        <f>'HOLERITE AGO.26'!H23</f>
-        <v/>
-      </c>
-      <c r="E157" s="40" t="n"/>
+      <c r="D157" s="35">
+        <f>'HOLERITE AGO.26'!H25</f>
+        <v/>
+      </c>
+      <c r="E157" s="41" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="29" t="inlineStr">
+      <c r="A158" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B158" s="29" t="inlineStr">
+      <c r="B158" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C158" s="29" t="inlineStr">
+      <c r="C158" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D158" s="34">
-        <f>'HOLERITE AGO.26'!H24</f>
-        <v/>
-      </c>
-      <c r="E158" s="40" t="n"/>
+      <c r="D158" s="35">
+        <f>'HOLERITE AGO.26'!H26</f>
+        <v/>
+      </c>
+      <c r="E158" s="41" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="29" t="inlineStr">
+      <c r="A159" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B159" s="29" t="inlineStr">
+      <c r="B159" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C159" s="29" t="inlineStr">
+      <c r="C159" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D159" s="34">
-        <f>'HOLERITE AGO.26'!H25</f>
-        <v/>
-      </c>
-      <c r="E159" s="40" t="n"/>
+      <c r="D159" s="35">
+        <f>'HOLERITE AGO.26'!H27</f>
+        <v/>
+      </c>
+      <c r="E159" s="41" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="29" t="inlineStr">
+      <c r="A160" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B160" s="29" t="inlineStr">
+      <c r="B160" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C160" s="29" t="inlineStr">
+      <c r="C160" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D160" s="34">
-        <f>'HOLERITE AGO.26'!H26</f>
-        <v/>
-      </c>
-      <c r="E160" s="40" t="n"/>
+      <c r="D160" s="35">
+        <f>'HOLERITE AGO.26'!H28</f>
+        <v/>
+      </c>
+      <c r="E160" s="41" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="29" t="inlineStr">
+      <c r="A161" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B161" s="29" t="inlineStr">
+      <c r="B161" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C161" s="29" t="inlineStr">
+      <c r="C161" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D161" s="34">
-        <f>'HOLERITE AGO.26'!H27</f>
-        <v/>
-      </c>
-      <c r="E161" s="40" t="n"/>
+      <c r="D161" s="35">
+        <f>'HOLERITE AGO.26'!H29</f>
+        <v/>
+      </c>
+      <c r="E161" s="41" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="29" t="inlineStr">
+      <c r="A162" s="30" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B162" s="29" t="inlineStr">
+      <c r="B162" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C162" s="29" t="inlineStr">
+      <c r="C162" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D162" s="34">
-        <f>'HOLERITE AGO.26'!H28</f>
-        <v/>
-      </c>
-      <c r="E162" s="40" t="n"/>
+      <c r="D162" s="35">
+        <f>'HOLERITE AGO.26'!H30</f>
+        <v/>
+      </c>
+      <c r="E162" s="41" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="41" t="inlineStr">
+      <c r="A163" s="42" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B163" s="41" t="inlineStr">
+      <c r="B163" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C163" s="41" t="inlineStr">
+      <c r="C163" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D163" s="42">
-        <f>'HOLERITE AGO.26'!H29</f>
+      <c r="D163" s="43">
+        <f>'HOLERITE AGO.26'!H31</f>
         <v/>
       </c>
       <c r="E163" s="18" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="43" t="inlineStr">
+      <c r="A164" s="44" t="inlineStr">
         <is>
           <t>CAMILA</t>
         </is>
       </c>
-      <c r="B164" s="44" t="inlineStr">
+      <c r="B164" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C164" s="44" t="inlineStr">
+      <c r="C164" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D164" s="45">
-        <f>'HOLERITE AGO.26'!H31</f>
-        <v/>
-      </c>
-      <c r="E164" s="46" t="n"/>
+      <c r="D164" s="46">
+        <f>'HOLERITE AGO.26'!H33</f>
+        <v/>
+      </c>
+      <c r="E164" s="47" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="29" t="inlineStr">
+      <c r="A166" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B166" s="29" t="inlineStr">
+      <c r="B166" s="30" t="inlineStr">
         <is>
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="C166" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D166" s="34">
+      <c r="C166" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D166" s="35">
         <f>'HOLERITE AGO.26'!I6</f>
         <v/>
       </c>
-      <c r="E166" s="40" t="n"/>
+      <c r="E166" s="41" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="29" t="inlineStr">
+      <c r="A167" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B167" s="29" t="inlineStr">
+      <c r="B167" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="C167" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D167" s="34">
+      <c r="C167" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D167" s="35">
         <f>'HOLERITE AGO.26'!I7</f>
         <v/>
       </c>
-      <c r="E167" s="40" t="n"/>
+      <c r="E167" s="41" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="29" t="inlineStr">
+      <c r="A168" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B168" s="29" t="inlineStr">
+      <c r="B168" s="30" t="inlineStr">
         <is>
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="C168" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D168" s="34">
+      <c r="C168" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D168" s="35">
         <f>'HOLERITE AGO.26'!I8</f>
         <v/>
       </c>
-      <c r="E168" s="40" t="n"/>
+      <c r="E168" s="41" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="29" t="inlineStr">
+      <c r="A169" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B169" s="29" t="inlineStr">
+      <c r="B169" s="30" t="inlineStr">
         <is>
           <t>COMISSÃO SOBRE VENDAS</t>
         </is>
       </c>
-      <c r="C169" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D169" s="34">
+      <c r="C169" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D169" s="35">
         <f>'HOLERITE AGO.26'!I11</f>
         <v/>
       </c>
-      <c r="E169" s="40" t="n"/>
+      <c r="E169" s="41" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="29" t="inlineStr">
+      <c r="A170" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B170" s="29" t="inlineStr">
+      <c r="B170" s="30" t="inlineStr">
         <is>
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="C170" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D170" s="34">
+      <c r="C170" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D170" s="35">
         <f>'HOLERITE AGO.26'!I12</f>
         <v/>
       </c>
-      <c r="E170" s="40" t="n"/>
+      <c r="E170" s="41" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="29" t="inlineStr">
+      <c r="A171" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B171" s="29" t="inlineStr">
+      <c r="B171" s="30" t="inlineStr">
         <is>
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="C171" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D171" s="34">
+      <c r="C171" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D171" s="35">
         <f>'HOLERITE AGO.26'!I13</f>
         <v/>
       </c>
-      <c r="E171" s="40" t="n"/>
+      <c r="E171" s="41" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="29" t="inlineStr">
+      <c r="A172" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B172" s="29" t="inlineStr">
+      <c r="B172" s="30" t="inlineStr">
         <is>
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="C172" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D172" s="34">
+      <c r="C172" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D172" s="35">
         <f>'HOLERITE AGO.26'!I14</f>
         <v/>
       </c>
-      <c r="E172" s="40" t="n"/>
+      <c r="E172" s="41" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="29" t="inlineStr">
+      <c r="A173" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B173" s="29" t="inlineStr">
+      <c r="B173" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="C173" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D173" s="34">
+      <c r="C173" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D173" s="35">
         <f>'HOLERITE AGO.26'!I15</f>
         <v/>
       </c>
-      <c r="E173" s="40" t="n"/>
+      <c r="E173" s="41" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="29" t="inlineStr">
+      <c r="A174" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B174" s="29" t="inlineStr">
+      <c r="B174" s="30" t="inlineStr">
         <is>
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="C174" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D174" s="34">
+      <c r="C174" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D174" s="35">
         <f>'HOLERITE AGO.26'!I16</f>
         <v/>
       </c>
-      <c r="E174" s="40" t="n"/>
+      <c r="E174" s="41" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="29" t="inlineStr">
+      <c r="A175" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B175" s="29" t="inlineStr">
+      <c r="B175" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="C175" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D175" s="34">
-        <f>'HOLERITE AGO.26'!I17</f>
-        <v/>
-      </c>
-      <c r="E175" s="40" t="n"/>
+      <c r="C175" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D175" s="35">
+        <f>'HOLERITE AGO.26'!I19</f>
+        <v/>
+      </c>
+      <c r="E175" s="41" t="n"/>
     </row>
     <row r="176">
-      <c r="A176" s="29" t="inlineStr">
+      <c r="A176" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B176" s="29" t="inlineStr">
+      <c r="B176" s="30" t="inlineStr">
         <is>
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="C176" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D176" s="34">
-        <f>'HOLERITE AGO.26'!I18</f>
-        <v/>
-      </c>
-      <c r="E176" s="40" t="n"/>
+      <c r="C176" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D176" s="35">
+        <f>'HOLERITE AGO.26'!I20</f>
+        <v/>
+      </c>
+      <c r="E176" s="41" t="n"/>
     </row>
     <row r="177">
-      <c r="A177" s="29" t="inlineStr">
+      <c r="A177" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B177" s="29" t="inlineStr">
+      <c r="B177" s="30" t="inlineStr">
         <is>
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="C177" s="29" t="inlineStr">
-        <is>
-          <t>Provento</t>
-        </is>
-      </c>
-      <c r="D177" s="34">
-        <f>'HOLERITE AGO.26'!I19</f>
-        <v/>
-      </c>
-      <c r="E177" s="40" t="n"/>
+      <c r="C177" s="30" t="inlineStr">
+        <is>
+          <t>Provento</t>
+        </is>
+      </c>
+      <c r="D177" s="35">
+        <f>'HOLERITE AGO.26'!I21</f>
+        <v/>
+      </c>
+      <c r="E177" s="41" t="n"/>
     </row>
     <row r="178">
-      <c r="A178" s="41" t="inlineStr">
+      <c r="A178" s="42" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B178" s="41" t="inlineStr">
+      <c r="B178" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE PROVENTOS</t>
         </is>
       </c>
-      <c r="C178" s="41" t="inlineStr">
+      <c r="C178" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D178" s="42">
-        <f>'HOLERITE AGO.26'!I20</f>
+      <c r="D178" s="43">
+        <f>'HOLERITE AGO.26'!I22</f>
         <v/>
       </c>
       <c r="E178" s="18" t="n"/>
     </row>
     <row r="179">
-      <c r="A179" s="29" t="inlineStr">
+      <c r="A179" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B179" s="29" t="inlineStr">
+      <c r="B179" s="30" t="inlineStr">
         <is>
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="C179" s="29" t="inlineStr">
+      <c r="C179" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D179" s="34">
-        <f>'HOLERITE AGO.26'!I22</f>
-        <v/>
-      </c>
-      <c r="E179" s="40" t="n"/>
+      <c r="D179" s="35">
+        <f>'HOLERITE AGO.26'!I24</f>
+        <v/>
+      </c>
+      <c r="E179" s="41" t="n"/>
     </row>
     <row r="180">
-      <c r="A180" s="29" t="inlineStr">
+      <c r="A180" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B180" s="29" t="inlineStr">
+      <c r="B180" s="30" t="inlineStr">
         <is>
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="C180" s="29" t="inlineStr">
+      <c r="C180" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D180" s="34">
-        <f>'HOLERITE AGO.26'!I23</f>
-        <v/>
-      </c>
-      <c r="E180" s="40" t="n"/>
+      <c r="D180" s="35">
+        <f>'HOLERITE AGO.26'!I25</f>
+        <v/>
+      </c>
+      <c r="E180" s="41" t="n"/>
     </row>
     <row r="181">
-      <c r="A181" s="29" t="inlineStr">
+      <c r="A181" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B181" s="29" t="inlineStr">
+      <c r="B181" s="30" t="inlineStr">
         <is>
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="C181" s="29" t="inlineStr">
+      <c r="C181" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D181" s="34">
-        <f>'HOLERITE AGO.26'!I24</f>
-        <v/>
-      </c>
-      <c r="E181" s="40" t="n"/>
+      <c r="D181" s="35">
+        <f>'HOLERITE AGO.26'!I26</f>
+        <v/>
+      </c>
+      <c r="E181" s="41" t="n"/>
     </row>
     <row r="182">
-      <c r="A182" s="29" t="inlineStr">
+      <c r="A182" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B182" s="29" t="inlineStr">
+      <c r="B182" s="30" t="inlineStr">
         <is>
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="C182" s="29" t="inlineStr">
+      <c r="C182" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D182" s="34">
-        <f>'HOLERITE AGO.26'!I25</f>
-        <v/>
-      </c>
-      <c r="E182" s="40" t="n"/>
+      <c r="D182" s="35">
+        <f>'HOLERITE AGO.26'!I27</f>
+        <v/>
+      </c>
+      <c r="E182" s="41" t="n"/>
     </row>
     <row r="183">
-      <c r="A183" s="29" t="inlineStr">
+      <c r="A183" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B183" s="29" t="inlineStr">
+      <c r="B183" s="30" t="inlineStr">
         <is>
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="C183" s="29" t="inlineStr">
+      <c r="C183" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D183" s="34">
-        <f>'HOLERITE AGO.26'!I26</f>
-        <v/>
-      </c>
-      <c r="E183" s="40" t="n"/>
+      <c r="D183" s="35">
+        <f>'HOLERITE AGO.26'!I28</f>
+        <v/>
+      </c>
+      <c r="E183" s="41" t="n"/>
     </row>
     <row r="184">
-      <c r="A184" s="29" t="inlineStr">
+      <c r="A184" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B184" s="29" t="inlineStr">
+      <c r="B184" s="30" t="inlineStr">
         <is>
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="C184" s="29" t="inlineStr">
+      <c r="C184" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D184" s="34">
-        <f>'HOLERITE AGO.26'!I27</f>
-        <v/>
-      </c>
-      <c r="E184" s="40" t="n"/>
+      <c r="D184" s="35">
+        <f>'HOLERITE AGO.26'!I29</f>
+        <v/>
+      </c>
+      <c r="E184" s="41" t="n"/>
     </row>
     <row r="185">
-      <c r="A185" s="29" t="inlineStr">
+      <c r="A185" s="30" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B185" s="29" t="inlineStr">
+      <c r="B185" s="30" t="inlineStr">
         <is>
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="C185" s="29" t="inlineStr">
+      <c r="C185" s="30" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D185" s="34">
-        <f>'HOLERITE AGO.26'!I28</f>
-        <v/>
-      </c>
-      <c r="E185" s="40" t="n"/>
+      <c r="D185" s="35">
+        <f>'HOLERITE AGO.26'!I30</f>
+        <v/>
+      </c>
+      <c r="E185" s="41" t="n"/>
     </row>
     <row r="186">
-      <c r="A186" s="41" t="inlineStr">
+      <c r="A186" s="42" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B186" s="41" t="inlineStr">
+      <c r="B186" s="42" t="inlineStr">
         <is>
           <t>TOTAL DE DESCONTOS</t>
         </is>
       </c>
-      <c r="C186" s="41" t="inlineStr">
+      <c r="C186" s="42" t="inlineStr">
         <is>
           <t>Subtotal</t>
         </is>
       </c>
-      <c r="D186" s="42">
-        <f>'HOLERITE AGO.26'!I29</f>
+      <c r="D186" s="43">
+        <f>'HOLERITE AGO.26'!I31</f>
         <v/>
       </c>
       <c r="E186" s="18" t="n"/>
     </row>
     <row r="187">
-      <c r="A187" s="43" t="inlineStr">
+      <c r="A187" s="44" t="inlineStr">
         <is>
           <t>NATI</t>
         </is>
       </c>
-      <c r="B187" s="44" t="inlineStr">
+      <c r="B187" s="45" t="inlineStr">
         <is>
           <t>LÍQUIDO A RECEBER</t>
         </is>
       </c>
-      <c r="C187" s="44" t="inlineStr">
+      <c r="C187" s="45" t="inlineStr">
         <is>
           <t>Líquido</t>
         </is>
       </c>
-      <c r="D187" s="45">
-        <f>'HOLERITE AGO.26'!I31</f>
-        <v/>
-      </c>
-      <c r="E187" s="46" t="n"/>
+      <c r="D187" s="46">
+        <f>'HOLERITE AGO.26'!I33</f>
+        <v/>
+      </c>
+      <c r="E187" s="47" t="n"/>
     </row>
   </sheetData>
+  <autoFilter ref="A4:E187"/>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -822,22 +822,18 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="3" t="inlineStr">
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" s="4" t="inlineStr"/>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha. A comissão apurada no InovaFarma (R$ 975,65) aparece apenas na aba BASE, como informação.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
         </is>
       </c>
     </row>
@@ -849,7 +845,7 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
+          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
         </is>
       </c>
     </row>
@@ -861,7 +857,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
         </is>
       </c>
     </row>
@@ -873,7 +869,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>JOEL: informar o período de FÉRIAS de agosto/2026 para a contabilidade calcular férias, 1/3, média de comissões e o salário proporcional.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -885,7 +881,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>DEAN: apurou R$ 975,65 de comissão em agosto, mas não vinha recebendo comissão em folha — confirmar.</t>
+          <t>JOEL: informar o período de FÉRIAS de agosto/2026 para a contabilidade calcular férias, 1/3, média de comissões e o salário proporcional.</t>
         </is>
       </c>
     </row>
@@ -997,9 +993,9 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A25:B25"/>
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
@@ -1337,7 +1333,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1823,18 +1819,26 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
+          <t>DEAN não recebe comissão em folha: no caso dele a comissão apurada acima é apenas informativa. Os incentivos continuam sendo lançados normalmente — confirmar se também ficam de fora.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="26" customHeight="1">
+      <c r="A24" s="25" t="inlineStr">
+        <is>
           <t>JOEL: venda bruta de apenas R$ 5.057,69 porque esteve de FÉRIAS em agosto/2026 — a comissão apurada (R$ 103,31) corresponde só aos dias trabalhados.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:J12"/>
-  <mergeCells count="6">
+  <mergeCells count="7">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A22:J22"/>
     <mergeCell ref="A21:J21"/>
     <mergeCell ref="A20:J20"/>
+    <mergeCell ref="A24:J24"/>
     <mergeCell ref="A2:J2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2047,9 +2051,8 @@
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="35">
-        <f>'BASE INOVAFARMA AGO.26'!F5</f>
-        <v/>
+      <c r="B9" s="35" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="35">
         <f>'BASE INOVAFARMA AGO.26'!F6</f>
@@ -2085,7 +2088,7 @@
       </c>
       <c r="K9" s="33" t="inlineStr">
         <is>
-          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo. DEAN: R$ 975,65 apurado — em jul/26 não houve lançamento de comissão para ele; confirmar.</t>
+          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). DEAN NÃO RECEBE COMISSÃO — lançado zero (o apurado dele fica só como informação na aba BASE). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -13,12 +13,14 @@
     <sheet name="HOLERITE AGO.26" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="JULHO.26 REVISADO" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="LISTA CONTABILIDADE" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="GANHOS DO COLABORADOR" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$K$36</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$187</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +32,7 @@
     <numFmt numFmtId="164" formatCode="R$ #,##0.00;-R$ #,##0.00;&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="15">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -115,6 +117,24 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
+      <color rgb="000000FF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00008000"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
       <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
@@ -193,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -202,7 +222,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -276,6 +296,13 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -641,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B43"/>
+  <dimension ref="A1:B45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -810,7 +837,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>JOEL: esteve de férias em agosto/2026 — por isso a venda e a comissão do mês ficaram baixas.</t>
+          <t>JOEL: férias de 01 a 31/08/2026 (mês inteiro), já pagas em recibo próprio no início de agosto. Neste holerite ele fica sem salário e sem desconto de vale-transporte; férias e 1/3 NÃO se repetem aqui.</t>
         </is>
       </c>
     </row>
@@ -826,7 +853,7 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha. A comissão apurada no InovaFarma (R$ 975,65) aparece apenas na aba BASE, como informação.</t>
+          <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha (a apurada, R$ 975,65, aparece só na aba BASE). Os incentivos dele continuam sendo pagos normalmente.</t>
         </is>
       </c>
     </row>
@@ -881,7 +908,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>JOEL: informar o período de FÉRIAS de agosto/2026 para a contabilidade calcular férias, 1/3, média de comissões e o salário proporcional.</t>
+          <t>JOEL: o código dele registrou R$ 103,31 de comissão mesmo com o mês inteiro de férias — conferir quem operou o código e zerar a rubrica se as vendas não forem dele.</t>
         </is>
       </c>
     </row>
@@ -893,7 +920,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+          <t>JOEL: confirmar se sobra algum desconto para agosto (convênio, vale ou adiantamento) ou se o holerite dele fica zerado.</t>
         </is>
       </c>
     </row>
@@ -905,7 +932,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
         </is>
       </c>
     </row>
@@ -917,37 +944,41 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
+          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
           <t>DSR de julho/2026 foi calculado com o fator de agosto (5/26) em vez de 4/27 — ver aba JULHO.26 REVISADO e decidir se ajusta em setembro.</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="3" t="inlineStr">
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="inlineStr"/>
-      <c r="B35" s="5" t="inlineStr">
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -955,7 +986,7 @@
       <c r="A38" s="4" t="inlineStr"/>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -963,7 +994,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>GANHOS DO COLABORADOR — escolha o nome na lista e saia o demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -971,7 +1002,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
         </is>
       </c>
     </row>
@@ -979,12 +1010,28 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="4" t="inlineStr"/>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="inlineStr"/>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
           <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="B43" s="7" t="inlineStr">
+    <row r="45">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>Documento gerado a partir da planilha CONISSÕES PLAN.AGOSTO/JULHO ARRAIAL 2026 e do relatório de comissões do InovaFarma.</t>
         </is>
@@ -997,10 +1044,10 @@
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A35:B35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1819,14 +1866,14 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>DEAN não recebe comissão em folha: no caso dele a comissão apurada acima é apenas informativa. Os incentivos continuam sendo lançados normalmente — confirmar se também ficam de fora.</t>
+          <t>DEAN não recebe comissão em folha: no caso dele a comissão apurada acima é apenas informativa. Os incentivos dele continuam sendo lançados normalmente.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>JOEL: venda bruta de apenas R$ 5.057,69 porque esteve de FÉRIAS em agosto/2026 — a comissão apurada (R$ 103,31) corresponde só aos dias trabalhados.</t>
+          <t>JOEL: esteve de FÉRIAS de 01 a 31/08/2026 (mês inteiro), mas o código dele registrou R$ 5.057,69 de venda bruta e R$ 103,31 de comissão — conferir quem operou o código no período.</t>
         </is>
       </c>
     </row>
@@ -1971,7 +2018,7 @@
         <v>1621</v>
       </c>
       <c r="E6" s="31" t="n">
-        <v>1621</v>
+        <v>0</v>
       </c>
       <c r="F6" s="31" t="n">
         <v>1621</v>
@@ -1991,7 +2038,7 @@
       </c>
       <c r="K6" s="33" t="inlineStr">
         <is>
-          <t>Piso 2026 R$ 1.621,00. CAMILA: admitida em jul/26 (salário proporcional naquele mês); agosto é o 1º mês completo. JOEL: ajustar aos dias trabalhados por conta das férias.</t>
+          <t>Piso 2026 R$ 1.621,00. CAMILA: admitida em jul/26 (salário proporcional naquele mês); agosto é o 1º mês completo. JOEL: zerado — esteve de férias de 01 a 31/08/2026, sem dias trabalhados no mês.</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2135,7 @@
       </c>
       <c r="K9" s="33" t="inlineStr">
         <is>
-          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). DEAN NÃO RECEBE COMISSÃO — lançado zero (o apurado dele fica só como informação na aba BASE). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo.</t>
+          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). JOEL: R$ 103,31 apurados no código dele mesmo estando de férias o mês inteiro — conferir quem fez essas vendas e zerar se não forem dele. DEAN NÃO RECEBE COMISSÃO — lançado zero (o apurado dele fica só como informação na aba BASE). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo.</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2384,7 @@
       </c>
       <c r="K17" s="33" t="inlineStr">
         <is>
-          <t>JOEL esteve de FÉRIAS em agosto/2026 — informar o período para a contabilidade calcular férias, média de comissões e o salário proporcional aos dias trabalhados.</t>
+          <t>JOEL: férias de 01 a 31/08/2026, JÁ PAGAS em recibo próprio no início de agosto — NÃO lançar de novo neste holerite. Linha mantida só para o caso de outras férias.</t>
         </is>
       </c>
     </row>
@@ -2361,7 +2408,7 @@
       </c>
       <c r="K18" s="33" t="inlineStr">
         <is>
-          <t>Calculado pela contabilidade sobre o valor das férias.</t>
+          <t>JOEL: também já pago com as férias no início de agosto. Linha mantida para eventuais férias de outros meses.</t>
         </is>
       </c>
     </row>
@@ -2705,9 +2752,7 @@
       <c r="D28" s="31" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="E28" s="31" t="n">
-        <v>-84.29000000000001</v>
-      </c>
+      <c r="E28" s="31" t="n"/>
       <c r="F28" s="31" t="n">
         <v>-84.29000000000001</v>
       </c>
@@ -2722,7 +2767,7 @@
       </c>
       <c r="K28" s="33" t="inlineStr">
         <is>
-          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada.</t>
+          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada. JOEL: zerado, mês inteiro de férias.</t>
         </is>
       </c>
     </row>
@@ -8134,4 +8179,446 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D44"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="58" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>DEMONSTRATIVO DE GANHOS DO COLABORADOR</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Competência AGOSTO/2026 · Pagamento em 05/09/2026 · Farmácia Tropical Multi Econômica</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="48" t="inlineStr">
+        <is>
+          <t>Escolha o colaborador:</t>
+        </is>
+      </c>
+      <c r="C4" s="49" t="inlineStr">
+        <is>
+          <t>DEAN</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>Troque o nome aqui e a tabela abaixo muda sozinha — é o relatório para mandar para cada um.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="19" customHeight="1">
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>PROVENTOS</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="n"/>
+      <c r="D6" s="29" t="n"/>
+    </row>
+    <row r="7">
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Salário base</t>
+        </is>
+      </c>
+      <c r="C7" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="C8" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$7:$I$7,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Horas extras</t>
+        </is>
+      </c>
+      <c r="C9" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$8:$I$8,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Comissão sobre vendas</t>
+        </is>
+      </c>
+      <c r="C10" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$11:$I$11,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>Repouso remunerado / DSR</t>
+        </is>
+      </c>
+      <c r="C11" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$12:$I$12,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Auxílio gerência</t>
+        </is>
+      </c>
+      <c r="C12" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$13:$I$13,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Adicional prêmio meta caixa</t>
+        </is>
+      </c>
+      <c r="C13" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$14:$I$14,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Prêmio cota geral</t>
+        </is>
+      </c>
+      <c r="C14" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$15:$I$15,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>Prêmio pré-vencidos</t>
+        </is>
+      </c>
+      <c r="C15" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$16:$I$16,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="30" t="inlineStr">
+        <is>
+          <t>Férias</t>
+        </is>
+      </c>
+      <c r="C16" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$17:$I$17,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="30" t="inlineStr">
+        <is>
+          <t>1/3 constitucional de férias</t>
+        </is>
+      </c>
+      <c r="C17" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$18:$I$18,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="30" t="inlineStr">
+        <is>
+          <t>Incentivo aplicações</t>
+        </is>
+      </c>
+      <c r="C18" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$19:$I$19,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="30" t="inlineStr">
+        <is>
+          <t>Incentivo vitaminas</t>
+        </is>
+      </c>
+      <c r="C19" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$20:$I$20,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="30" t="inlineStr">
+        <is>
+          <t>Outros incentivos</t>
+        </is>
+      </c>
+      <c r="C20" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$21:$I$21,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL DE PROVENTOS</t>
+        </is>
+      </c>
+      <c r="C21" s="43">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$22:$I$22,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="19" customHeight="1">
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="n"/>
+      <c r="D22" s="29" t="n"/>
+    </row>
+    <row r="23">
+      <c r="B23" s="30" t="inlineStr">
+        <is>
+          <t>Adiantamento / vales</t>
+        </is>
+      </c>
+      <c r="C23" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$24:$I$24,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="30" t="inlineStr">
+        <is>
+          <t>Adiantamento de incentivos e aplicações</t>
+        </is>
+      </c>
+      <c r="C24" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$25:$I$25,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="30" t="inlineStr">
+        <is>
+          <t>Convênio</t>
+        </is>
+      </c>
+      <c r="C25" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$26:$I$26,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="30" t="inlineStr">
+        <is>
+          <t>Faltas / atrasos</t>
+        </is>
+      </c>
+      <c r="C26" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$27:$I$27,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="30" t="inlineStr">
+        <is>
+          <t>Vale transporte 6%</t>
+        </is>
+      </c>
+      <c r="C27" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$28:$I$28,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="30" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="C28" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$29:$I$29,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="30" t="inlineStr">
+        <is>
+          <t>IRRF</t>
+        </is>
+      </c>
+      <c r="C29" s="35">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$30:$I$30,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL DE DESCONTOS</t>
+        </is>
+      </c>
+      <c r="C30" s="43">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$31:$I$31,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31" ht="19" customHeight="1">
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>LÍQUIDO</t>
+        </is>
+      </c>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="29" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="B32" s="50" t="inlineStr">
+        <is>
+          <t>LÍQUIDO A RECEBER EM 05/09/2026</t>
+        </is>
+      </c>
+      <c r="C32" s="51">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$33:$I$33,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="52" t="inlineStr">
+        <is>
+          <t>Vendas do colaborador no mês (InovaFarma):</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="30" t="inlineStr">
+        <is>
+          <t>Venda bruta</t>
+        </is>
+      </c>
+      <c r="C35" s="35">
+        <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$C$5:$C$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="30" t="inlineStr">
+        <is>
+          <t>Descontos concedidos</t>
+        </is>
+      </c>
+      <c r="C36" s="35">
+        <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$D$5:$D$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="30" t="inlineStr">
+        <is>
+          <t>Venda líquida</t>
+        </is>
+      </c>
+      <c r="C37" s="35">
+        <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$E$5:$E$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="30" t="inlineStr">
+        <is>
+          <t>Comissão apurada</t>
+        </is>
+      </c>
+      <c r="C38" s="35">
+        <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$F$5:$F$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" s="30" t="inlineStr">
+        <is>
+          <t>Total de incentivos</t>
+        </is>
+      </c>
+      <c r="C39" s="35">
+        <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$J$5:$J$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>A comissão apurada acima é a apuração do sistema. O que entra na folha é a linha "Comissão sobre vendas" — pode ser diferente (valor fixo acordado, PDV antigos ou quem não recebe comissão).</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>Os valores de INSS e IRRF são calculados pela contabilidade e só aparecem aqui depois de preenchidos na aba HOLERITE AGO.26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>Para mandar para o colaborador: selecione o nome acima e imprima esta aba em PDF (ou tire um print).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>Na aba LISTA CONTABILIDADE também dá para filtrar por FUNCIONÁRIO e ver só os lançamentos de uma pessoa.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <dataValidations count="1">
+    <dataValidation sqref="C4" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" error="Escolha um nome da lista." promptTitle="Colaborador" prompt="Selecione o colaborador para ver os ganhos dele." type="list">
+      <formula1>"DEAN,AGNOR,EDEY,JOEL,VALÉRIA,SARA,CAMILA,NATI"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -837,7 +837,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>JOEL: férias de 01 a 31/08/2026 (mês inteiro), já pagas em recibo próprio no início de agosto. Neste holerite ele fica sem salário e sem desconto de vale-transporte; férias e 1/3 NÃO se repetem aqui.</t>
+          <t>JOEL: por acordo interno saiu em 04/08 e volta em 04/09, mas o recibo de férias saiu como 01 a 31/08 e já foi pago no início de agosto. Por isso ele tem comissão dos dias 01 e 02/08 (R$ 103,31) e fica sem salário e sem desconto de vale-transporte neste holerite; férias e 1/3 NÃO se repetem aqui.</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>JOEL: o código dele registrou R$ 103,31 de comissão mesmo com o mês inteiro de férias — conferir quem operou o código e zerar a rubrica se as vendas não forem dele.</t>
+          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
         </is>
       </c>
     </row>
@@ -920,7 +920,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>JOEL: confirmar se sobra algum desconto para agosto (convênio, vale ou adiantamento) ou se o holerite dele fica zerado.</t>
+          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
-          <t>JOEL: esteve de FÉRIAS de 01 a 31/08/2026 (mês inteiro), mas o código dele registrou R$ 5.057,69 de venda bruta e R$ 103,31 de comissão — conferir quem operou o código no período.</t>
+          <t>JOEL: vendeu R$ 3.684,97 nos dias 01 e 02/08 e saiu de férias em 04/08 (retorno em 04/09) — daí a comissão de R$ 103,31. Constam ainda 2 itens de R$ 11,68 em 07/08 no código dele.</t>
         </is>
       </c>
     </row>
@@ -2038,7 +2038,7 @@
       </c>
       <c r="K6" s="33" t="inlineStr">
         <is>
-          <t>Piso 2026 R$ 1.621,00. CAMILA: admitida em jul/26 (salário proporcional naquele mês); agosto é o 1º mês completo. JOEL: zerado — esteve de férias de 01 a 31/08/2026, sem dias trabalhados no mês.</t>
+          <t>Piso 2026 R$ 1.621,00. CAMILA: admitida em jul/26 (salário proporcional naquele mês); agosto é o 1º mês completo. JOEL: zerado — trabalhou de 01 a 03/08 mas esses dias já estão dentro do recibo de férias (01 a 31/08); se a empresa decidir pagá-los à parte, lançar aqui.</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2135,7 @@
       </c>
       <c r="K9" s="33" t="inlineStr">
         <is>
-          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). JOEL: R$ 103,31 apurados no código dele mesmo estando de férias o mês inteiro — conferir quem fez essas vendas e zerar se não forem dele. DEAN NÃO RECEBE COMISSÃO — lançado zero (o apurado dele fica só como informação na aba BASE). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo.</t>
+          <t>Apurado no InovaFarma (aba BASE INOVAFARMA AGO.26). JOEL: R$ 103,31 das vendas dele nos dias 01 e 02/08, antes de sair de férias em 04/08 (o recibo de férias saiu como 01 a 31/08). DEAN NÃO RECEBE COMISSÃO — lançado zero (o apurado dele fica só como informação na aba BASE). AGNOR: mantido o fixo de R$ 2.000,00 pela linha de complemento abaixo.</t>
         </is>
       </c>
     </row>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="K17" s="33" t="inlineStr">
         <is>
-          <t>JOEL: férias de 01 a 31/08/2026, JÁ PAGAS em recibo próprio no início de agosto — NÃO lançar de novo neste holerite. Linha mantida só para o caso de outras férias.</t>
+          <t>JOEL: recibo de férias de 01 a 31/08/2026, JÁ PAGO no início de agosto — NÃO lançar de novo aqui. Pelo acordo interno ele saiu em 04/08 e volta em 04/09.</t>
         </is>
       </c>
     </row>
@@ -2767,7 +2767,7 @@
       </c>
       <c r="K28" s="33" t="inlineStr">
         <is>
-          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada. JOEL: zerado, mês inteiro de férias.</t>
+          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada. JOEL: zerado, mês de férias.</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2965,7 @@
       </c>
       <c r="K35" s="33" t="inlineStr">
         <is>
-          <t>PREENCHER com as passagens compradas para setembro/2026.</t>
+          <t>PREENCHER com as passagens compradas para setembro/2026. JOEL: só a partir de 04/09, quando volta das férias.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -668,7 +668,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -853,26 +853,22 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
+          <t>SARA: a comissão dela na loja Centro (R$ 2,65) foi somada aqui, na linha COMPLEMENTO / COMISSÃO PDV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="4" t="inlineStr"/>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
           <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha (a apurada, R$ 975,65, aparece só na aba BASE). Os incentivos dele continuam sendo pagos normalmente.</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="3" t="inlineStr">
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
         </is>
       </c>
     </row>
@@ -884,7 +880,7 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
+          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
         </is>
       </c>
     </row>
@@ -896,7 +892,7 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
+          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
         </is>
       </c>
     </row>
@@ -908,7 +904,7 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
         </is>
       </c>
     </row>
@@ -920,7 +916,7 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
+          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
         </is>
       </c>
     </row>
@@ -932,7 +928,7 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
         </is>
       </c>
     </row>
@@ -944,7 +940,7 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
         </is>
       </c>
     </row>
@@ -956,37 +952,41 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
+          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
           <t>DSR de julho/2026 foi calculado com o fator de agosto (5/26) em vez de 4/27 — ver aba JULHO.26 REVISADO e decidir se ajusta em setembro.</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="3" t="inlineStr">
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr"/>
-      <c r="B36" s="5" t="inlineStr">
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="3" t="inlineStr">
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="4" t="inlineStr"/>
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -994,7 +994,7 @@
       <c r="A39" s="4" t="inlineStr"/>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>GANHOS DO COLABORADOR — escolha o nome na lista e saia o demonstrativo individual, pronto para imprimir/mandar.</t>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
@@ -1002,7 +1002,7 @@
       <c r="A40" s="4" t="inlineStr"/>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
+          <t>GANHOS DO COLABORADOR — escolha o nome na lista e saia o demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1010,7 @@
       <c r="A41" s="4" t="inlineStr"/>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       <c r="A42" s="4" t="inlineStr"/>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
@@ -1026,12 +1026,20 @@
       <c r="A43" s="4" t="inlineStr"/>
       <c r="B43" s="5" t="inlineStr">
         <is>
+          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="4" t="inlineStr"/>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
           <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="B45" s="7" t="inlineStr">
+    <row r="46">
+      <c r="B46" s="7" t="inlineStr">
         <is>
           <t>Documento gerado a partir da planilha CONISSÕES PLAN.AGOSTO/JULHO ARRAIAL 2026 e do relatório de comissões do InovaFarma.</t>
         </is>
@@ -1040,14 +1048,14 @@
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="A36:B36"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A27:B27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1380,7 +1388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1866,20 +1874,27 @@
     <row r="23" ht="26" customHeight="1">
       <c r="A23" s="25" t="inlineStr">
         <is>
-          <t>DEAN não recebe comissão em folha: no caso dele a comissão apurada acima é apenas informativa. Os incentivos dele continuam sendo lançados normalmente.</t>
+          <t>SARA também vendeu R$ 365,03 pelo código dela na loja CENTRO, com R$ 2,65 de comissão. Esse valor foi somado à folha dela aqui, na linha COMPLEMENTO / COMISSÃO PDV.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="26" customHeight="1">
       <c r="A24" s="25" t="inlineStr">
         <is>
+          <t>DEAN não recebe comissão em folha: no caso dele a comissão apurada acima é apenas informativa. Os incentivos dele continuam sendo lançados normalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="26" customHeight="1">
+      <c r="A25" s="25" t="inlineStr">
+        <is>
           <t>JOEL: vendeu R$ 3.684,97 nos dias 01 e 02/08 e saiu de férias em 04/08 (retorno em 04/09) — daí a comissão de R$ 103,31. Constam ainda 2 itens de R$ 11,68 em 07/08 no código dele.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:J12"/>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A23:J23"/>
     <mergeCell ref="A22:J22"/>
@@ -1887,6 +1902,7 @@
     <mergeCell ref="A20:J20"/>
     <mergeCell ref="A24:J24"/>
     <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A25:J25"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2153,7 +2169,9 @@
       <c r="D10" s="31" t="n"/>
       <c r="E10" s="31" t="n"/>
       <c r="F10" s="31" t="n"/>
-      <c r="G10" s="31" t="n"/>
+      <c r="G10" s="31" t="n">
+        <v>2.65</v>
+      </c>
       <c r="H10" s="31" t="n"/>
       <c r="I10" s="31" t="n"/>
       <c r="J10" s="32">
@@ -2162,7 +2180,7 @@
       </c>
       <c r="K10" s="33" t="inlineStr">
         <is>
-          <t>AGNOR: complemento até a comissão fixa de R$ 2.000,00 (parâmetro na aba PARÂMETROS). Demais: preencher com PDV antigos, se houver.</t>
+          <t>AGNOR: complemento até a comissão fixa de R$ 2.000,00 (parâmetro na aba PARÂMETROS). SARA: R$ 2,65 de comissão apurada no código dela na loja CENTRO (venda bruta de R$ 365,03), trazida para a folha do Arraial. Demais: preencher com PDV antigos, se houver.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -14,6 +14,7 @@
     <sheet name="JULHO.26 REVISADO" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="LISTA CONTABILIDADE" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="GANHOS DO COLABORADOR" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="PONTO AGO.26" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$12</definedName>
@@ -21,6 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$187</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO AGO.26'!$A$4:$I$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -213,7 +215,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -278,9 +280,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="4" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -303,6 +305,8 @@
     <xf numFmtId="0" fontId="15" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="16" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -668,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B46"/>
+  <dimension ref="A1:B56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -821,7 +825,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>JÁ DEFINIDO PELA EMPRESA</t>
+          <t>APONTAMENTO DE AGOSTO/2026 (aba PONTO AGO.26)</t>
         </is>
       </c>
     </row>
@@ -829,7 +833,7 @@
       <c r="A22" s="4" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>AGNOR: mantida a comissão fixa de R$ 2.000,00 — a linha COMPLEMENTO / COMISSÃO PDV calcula sozinha a diferença (R$ 1.090,49) sobre o apurado de R$ 909,51.</t>
+          <t>EDEY: 24 horas extras normais → R$ 265,25.</t>
         </is>
       </c>
     </row>
@@ -837,7 +841,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>JOEL: por acordo interno saiu em 04/08 e volta em 04/09, mas o recibo de férias saiu como 01 a 31/08 e já foi pago no início de agosto. Por isso ele tem comissão dos dias 01 e 02/08 (R$ 103,31) e fica sem salário e sem desconto de vale-transporte neste holerite; férias e 1/3 NÃO se repetem aqui.</t>
+          <t>NATI: 17 horas noturnas → R$ 25,05 de adicional; e o feriado de 15/08 trabalhado sem folga → R$ 54,03.</t>
         </is>
       </c>
     </row>
@@ -845,7 +849,7 @@
       <c r="A24" s="4" t="inlineStr"/>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>CAMILA: contratada recentemente; agosto é o primeiro mês completo, com salário integral de R$ 1.621,00.</t>
+          <t>CAMILA, SARA e VALÉRIA: dia 15/08 (feriado) trabalhado → R$ 54,03 cada.</t>
         </is>
       </c>
     </row>
@@ -853,7 +857,7 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>SARA: a comissão dela na loja Centro (R$ 2,65) foi somada aqui, na linha COMPLEMENTO / COMISSÃO PDV.</t>
+          <t>VALÉRIA: 2 madrugadas com folga no dia seguinte — cabe só o adicional noturno; falta informar as horas.</t>
         </is>
       </c>
     </row>
@@ -861,98 +865,69 @@
       <c r="A26" s="4" t="inlineStr"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
+          <t>AGNOR: 3 madrugadas com folga — cabe só o adicional noturno; falta informar as horas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="4" t="inlineStr"/>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>DEAN: dia 15/08 trabalhado com folga compensatória — nada a pagar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>JÁ DEFINIDO PELA EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="4" t="inlineStr"/>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>AGNOR: mantida a comissão fixa de R$ 2.000,00 — a linha COMPLEMENTO / COMISSÃO PDV calcula sozinha a diferença (R$ 1.090,49) sobre o apurado de R$ 909,51.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="4" t="inlineStr"/>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>JOEL: por acordo interno saiu em 04/08 e volta em 04/09, mas o recibo de férias saiu como 01 a 31/08 e já foi pago no início de agosto. Por isso ele tem comissão dos dias 01 e 02/08 (R$ 103,31) e fica sem salário e sem desconto de vale-transporte neste holerite; férias e 1/3 NÃO se repetem aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="4" t="inlineStr"/>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>CAMILA: contratada recentemente; agosto é o primeiro mês completo, com salário integral de R$ 1.621,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="4" t="inlineStr"/>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>SARA: a comissão dela na loja Centro (R$ 2,65) foi somada aqui, na linha COMPLEMENTO / COMISSÃO PDV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="4" t="inlineStr"/>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
           <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha (a apurada, R$ 975,65, aparece só na aba BASE). Os incentivos dele continuam sendo pagos normalmente.</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="3" t="inlineStr">
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="inlineStr">
-        <is>
-          <t>Horas extras e adicional noturno de agosto (apontamento do ponto).</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B29" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="inlineStr">
-        <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B31" s="6" t="inlineStr">
-        <is>
-          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="inlineStr">
-        <is>
-          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="inlineStr">
-        <is>
-          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="inlineStr">
-        <is>
-          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
         </is>
       </c>
     </row>
@@ -964,98 +939,215 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
+          <t>VALÉRIA e AGNOR: informar na aba PONTO AGO.26 quantas horas noturnas tiveram as madrugadas trabalhadas (2 e 3 madrugadas).</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>EDEY: o adicional noturno está lançado como valor fixo de R$ 350,00 — conferir com o apontamento do ponto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>Confirmar o critério do feriado trabalhado: está sendo pago 1 salário-dia a mais (R$ 54,03) por feriado sem folga.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="inlineStr">
+        <is>
+          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="inlineStr">
+        <is>
+          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
           <t>DSR de julho/2026 foi calculado com o fator de agosto (5/26) em vez de 4/27 — ver aba JULHO.26 REVISADO e decidir se ajusta em setembro.</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="3" t="inlineStr">
+    <row r="45" ht="20" customHeight="1">
+      <c r="A45" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="inlineStr"/>
-      <c r="B37" s="5" t="inlineStr">
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="4" t="inlineStr"/>
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="3" t="inlineStr">
+    <row r="47" ht="20" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
         <is>
           <t>ABAS DO ARQUIVO</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="4" t="inlineStr"/>
-      <c r="B39" s="5" t="inlineStr">
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="4" t="inlineStr"/>
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="4" t="inlineStr"/>
-      <c r="B40" s="5" t="inlineStr">
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="4" t="inlineStr"/>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>PONTO AGO.26 — apontamento de horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="4" t="inlineStr"/>
+      <c r="B50" s="5" t="inlineStr">
         <is>
           <t>GANHOS DO COLABORADOR — escolha o nome na lista e saia o demonstrativo individual, pronto para imprimir/mandar.</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" s="4" t="inlineStr"/>
-      <c r="B41" s="5" t="inlineStr">
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="4" t="inlineStr"/>
+      <c r="B51" s="5" t="inlineStr">
         <is>
           <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="4" t="inlineStr"/>
-      <c r="B42" s="5" t="inlineStr">
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="4" t="inlineStr"/>
+      <c r="B52" s="5" t="inlineStr">
         <is>
           <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="4" t="inlineStr"/>
-      <c r="B43" s="5" t="inlineStr">
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="4" t="inlineStr"/>
+      <c r="B53" s="5" t="inlineStr">
         <is>
           <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="4" t="inlineStr"/>
-      <c r="B44" s="5" t="inlineStr">
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="4" t="inlineStr"/>
+      <c r="B54" s="5" t="inlineStr">
         <is>
           <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="B46" s="7" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="7" t="inlineStr">
         <is>
           <t>Documento gerado a partir da planilha CONISSÕES PLAN.AGOSTO/JULHO ARRAIAL 2026 e do relatório de comissões do InovaFarma.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="10">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
-    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A34:B34"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1067,7 +1159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1316,54 +1408,114 @@
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>Desconto vale-transporte 6%</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>-84.29000000000001</v>
+          <t>Horas mensais (base do salário-hora)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>220</v>
       </c>
       <c r="C20" s="10" t="inlineStr">
         <is>
-          <t>Valor praticado em jul/2026. 6% do salário base daria R$ 97,26 — CONFERIR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>INSS / IRRF</t>
+          <t>Salário-hora = salário base ÷ 220.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Adicional de hora extra</t>
+        </is>
+      </c>
+      <c r="B21" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>50% sobre a hora normal (hora extra = salário-hora × 1,5).</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>INSS</t>
-        </is>
-      </c>
-      <c r="B22" s="9" t="inlineStr">
-        <is>
-          <t>a calcular</t>
-        </is>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="n">
+        <v>0.2</v>
       </c>
       <c r="C22" s="10" t="inlineStr">
         <is>
-          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
+          <t>20% sobre a hora normal, nas horas entre 22h e 5h.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
+          <t>Dias do mês para o salário-dia</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>Salário-dia = salário base ÷ 30. Usado no feriado trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>Desconto vale-transporte 6%</t>
+        </is>
+      </c>
+      <c r="B24" s="12" t="n">
+        <v>-84.29000000000001</v>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
+        <is>
+          <t>Valor praticado em jul/2026. 6% do salário base daria R$ 97,26 — CONFERIR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>INSS / IRRF</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>INSS</t>
+        </is>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>a calcular</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>Calculado pela contabilidade sobre o total de proventos (tabela progressiva vigente).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
           <t>IRRF</t>
         </is>
       </c>
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B27" s="9" t="inlineStr">
         <is>
           <t>a calcular</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>Calculado pela contabilidade após dedução do INSS e dependentes.</t>
         </is>
@@ -1371,10 +1523,10 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A8:C8"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
@@ -2064,23 +2216,45 @@
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="31" t="n"/>
-      <c r="D7" s="31" t="n">
-        <v>350</v>
-      </c>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="31" t="n"/>
-      <c r="H7" s="31" t="n"/>
-      <c r="I7" s="31" t="n"/>
+      <c r="B7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,B$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="C7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,C$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="D7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,D$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="E7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,E$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="F7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,F$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="G7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,G$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="H7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,H$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
+      <c r="I7" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,I$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <v/>
+      </c>
       <c r="J7" s="32">
         <f>SUM(B7:I7)</f>
         <v/>
       </c>
       <c r="K7" s="33" t="inlineStr">
         <is>
-          <t>Conforme apontamento do ponto (jul/26: EDEY R$ 350,00).</t>
+          <t>Somado automaticamente da aba PONTO AGO.26 (apontamento de agosto/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
@@ -2090,21 +2264,45 @@
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n"/>
-      <c r="E8" s="34" t="n"/>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
-      <c r="H8" s="34" t="n"/>
-      <c r="I8" s="34" t="n"/>
+      <c r="B8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,B$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="C8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,C$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="D8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,D$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="E8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,E$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="F8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,F$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="G8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,G$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="H8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,H$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
+      <c r="I8" s="34">
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,I$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <v/>
+      </c>
       <c r="J8" s="20">
         <f>SUM(B8:I8)</f>
         <v/>
       </c>
       <c r="K8" s="33" t="inlineStr">
         <is>
-          <t>PREENCHER com o apurado no ponto de agosto/2026.</t>
+          <t>Somado automaticamente da aba PONTO AGO.26 (apontamento de agosto/2026). Para mudar, edite lá.</t>
         </is>
       </c>
     </row>
@@ -2114,34 +2312,34 @@
           <t>COMISSÃO PRODUTOS (INOVAFARMA)</t>
         </is>
       </c>
-      <c r="B9" s="35" t="n">
+      <c r="B9" s="34" t="n">
         <v>0</v>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F6</f>
         <v/>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F7</f>
         <v/>
       </c>
-      <c r="E9" s="35">
+      <c r="E9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F8</f>
         <v/>
       </c>
-      <c r="F9" s="35">
+      <c r="F9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F9</f>
         <v/>
       </c>
-      <c r="G9" s="35">
+      <c r="G9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F10</f>
         <v/>
       </c>
-      <c r="H9" s="35">
+      <c r="H9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F11</f>
         <v/>
       </c>
-      <c r="I9" s="35">
+      <c r="I9" s="34">
         <f>'BASE INOVAFARMA AGO.26'!F12</f>
         <v/>
       </c>
@@ -2237,35 +2435,35 @@
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B12" s="36">
+      <c r="B12" s="35">
         <f>ROUND((B11+B8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="35">
         <f>ROUND((C11+C8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="D12" s="36">
+      <c r="D12" s="35">
         <f>ROUND((D11+D8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="E12" s="36">
+      <c r="E12" s="35">
         <f>ROUND((E11+E8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="35">
         <f>ROUND((F11+F8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="G12" s="36">
+      <c r="G12" s="35">
         <f>ROUND((G11+G8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="H12" s="36">
+      <c r="H12" s="35">
         <f>ROUND((H11+H8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
-      <c r="I12" s="36">
+      <c r="I12" s="35">
         <f>ROUND((I11+I8)*PARÂMETROS!$B$12,2)</f>
         <v/>
       </c>
@@ -2340,14 +2538,14 @@
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="34" t="n"/>
-      <c r="D15" s="34" t="n"/>
-      <c r="E15" s="34" t="n"/>
-      <c r="F15" s="34" t="n"/>
-      <c r="G15" s="34" t="n"/>
-      <c r="H15" s="34" t="n"/>
-      <c r="I15" s="34" t="n"/>
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n"/>
+      <c r="D15" s="36" t="n"/>
+      <c r="E15" s="36" t="n"/>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
       <c r="J15" s="20">
         <f>SUM(B15:I15)</f>
         <v/>
@@ -2364,14 +2562,14 @@
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n"/>
-      <c r="F16" s="34" t="n"/>
-      <c r="G16" s="34" t="n"/>
-      <c r="H16" s="34" t="n"/>
-      <c r="I16" s="34" t="n"/>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
       <c r="J16" s="20">
         <f>SUM(B16:I16)</f>
         <v/>
@@ -2436,35 +2634,35 @@
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="B19" s="35">
+      <c r="B19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G5</f>
         <v/>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G6</f>
         <v/>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G7</f>
         <v/>
       </c>
-      <c r="E19" s="35">
+      <c r="E19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G8</f>
         <v/>
       </c>
-      <c r="F19" s="35">
+      <c r="F19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G9</f>
         <v/>
       </c>
-      <c r="G19" s="35">
+      <c r="G19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G10</f>
         <v/>
       </c>
-      <c r="H19" s="35">
+      <c r="H19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G11</f>
         <v/>
       </c>
-      <c r="I19" s="35">
+      <c r="I19" s="34">
         <f>'BASE INOVAFARMA AGO.26'!G12</f>
         <v/>
       </c>
@@ -2484,35 +2682,35 @@
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="B20" s="35">
+      <c r="B20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H5</f>
         <v/>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H6</f>
         <v/>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H7</f>
         <v/>
       </c>
-      <c r="E20" s="35">
+      <c r="E20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H8</f>
         <v/>
       </c>
-      <c r="F20" s="35">
+      <c r="F20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H9</f>
         <v/>
       </c>
-      <c r="G20" s="35">
+      <c r="G20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H10</f>
         <v/>
       </c>
-      <c r="H20" s="35">
+      <c r="H20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H11</f>
         <v/>
       </c>
-      <c r="I20" s="35">
+      <c r="I20" s="34">
         <f>'BASE INOVAFARMA AGO.26'!H12</f>
         <v/>
       </c>
@@ -2532,35 +2730,35 @@
           <t>OUTROS INCENTIVOS</t>
         </is>
       </c>
-      <c r="B21" s="35">
+      <c r="B21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I5</f>
         <v/>
       </c>
-      <c r="C21" s="35">
+      <c r="C21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I6</f>
         <v/>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I7</f>
         <v/>
       </c>
-      <c r="E21" s="35">
+      <c r="E21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I8</f>
         <v/>
       </c>
-      <c r="F21" s="35">
+      <c r="F21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I9</f>
         <v/>
       </c>
-      <c r="G21" s="35">
+      <c r="G21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I10</f>
         <v/>
       </c>
-      <c r="H21" s="35">
+      <c r="H21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I11</f>
         <v/>
       </c>
-      <c r="I21" s="35">
+      <c r="I21" s="34">
         <f>'BASE INOVAFARMA AGO.26'!I12</f>
         <v/>
       </c>
@@ -2645,14 +2843,14 @@
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="B24" s="34" t="n"/>
-      <c r="C24" s="34" t="n"/>
-      <c r="D24" s="34" t="n"/>
-      <c r="E24" s="34" t="n"/>
-      <c r="F24" s="34" t="n"/>
-      <c r="G24" s="34" t="n"/>
-      <c r="H24" s="34" t="n"/>
-      <c r="I24" s="34" t="n"/>
+      <c r="B24" s="36" t="n"/>
+      <c r="C24" s="36" t="n"/>
+      <c r="D24" s="36" t="n"/>
+      <c r="E24" s="36" t="n"/>
+      <c r="F24" s="36" t="n"/>
+      <c r="G24" s="36" t="n"/>
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n"/>
       <c r="J24" s="20">
         <f>SUM(B24:I24)</f>
         <v/>
@@ -2717,14 +2915,14 @@
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="B26" s="34" t="n"/>
-      <c r="C26" s="34" t="n"/>
-      <c r="D26" s="34" t="n"/>
-      <c r="E26" s="34" t="n"/>
-      <c r="F26" s="34" t="n"/>
-      <c r="G26" s="34" t="n"/>
-      <c r="H26" s="34" t="n"/>
-      <c r="I26" s="34" t="n"/>
+      <c r="B26" s="36" t="n"/>
+      <c r="C26" s="36" t="n"/>
+      <c r="D26" s="36" t="n"/>
+      <c r="E26" s="36" t="n"/>
+      <c r="F26" s="36" t="n"/>
+      <c r="G26" s="36" t="n"/>
+      <c r="H26" s="36" t="n"/>
+      <c r="I26" s="36" t="n"/>
       <c r="J26" s="20">
         <f>SUM(B26:I26)</f>
         <v/>
@@ -2741,14 +2939,14 @@
           <t>DESCONTO FALTAS / ATRASOS</t>
         </is>
       </c>
-      <c r="B27" s="34" t="n"/>
-      <c r="C27" s="34" t="n"/>
-      <c r="D27" s="34" t="n"/>
-      <c r="E27" s="34" t="n"/>
-      <c r="F27" s="34" t="n"/>
-      <c r="G27" s="34" t="n"/>
-      <c r="H27" s="34" t="n"/>
-      <c r="I27" s="34" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="36" t="n"/>
+      <c r="D27" s="36" t="n"/>
+      <c r="E27" s="36" t="n"/>
+      <c r="F27" s="36" t="n"/>
+      <c r="G27" s="36" t="n"/>
+      <c r="H27" s="36" t="n"/>
+      <c r="I27" s="36" t="n"/>
       <c r="J27" s="20">
         <f>SUM(B27:I27)</f>
         <v/>
@@ -2795,14 +2993,14 @@
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="B29" s="34" t="n"/>
-      <c r="C29" s="34" t="n"/>
-      <c r="D29" s="34" t="n"/>
-      <c r="E29" s="34" t="n"/>
-      <c r="F29" s="34" t="n"/>
-      <c r="G29" s="34" t="n"/>
-      <c r="H29" s="34" t="n"/>
-      <c r="I29" s="34" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="C29" s="36" t="n"/>
+      <c r="D29" s="36" t="n"/>
+      <c r="E29" s="36" t="n"/>
+      <c r="F29" s="36" t="n"/>
+      <c r="G29" s="36" t="n"/>
+      <c r="H29" s="36" t="n"/>
+      <c r="I29" s="36" t="n"/>
       <c r="J29" s="20">
         <f>SUM(B29:I29)</f>
         <v/>
@@ -2819,14 +3017,14 @@
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="B30" s="34" t="n"/>
-      <c r="C30" s="34" t="n"/>
-      <c r="D30" s="34" t="n"/>
-      <c r="E30" s="34" t="n"/>
-      <c r="F30" s="34" t="n"/>
-      <c r="G30" s="34" t="n"/>
-      <c r="H30" s="34" t="n"/>
-      <c r="I30" s="34" t="n"/>
+      <c r="B30" s="36" t="n"/>
+      <c r="C30" s="36" t="n"/>
+      <c r="D30" s="36" t="n"/>
+      <c r="E30" s="36" t="n"/>
+      <c r="F30" s="36" t="n"/>
+      <c r="G30" s="36" t="n"/>
+      <c r="H30" s="36" t="n"/>
+      <c r="I30" s="36" t="n"/>
       <c r="J30" s="20">
         <f>SUM(B30:I30)</f>
         <v/>
@@ -2969,14 +3167,14 @@
           <t>VALE TRANSPORTE (compra set/26)</t>
         </is>
       </c>
-      <c r="B35" s="34" t="n"/>
-      <c r="C35" s="34" t="n"/>
-      <c r="D35" s="34" t="n"/>
-      <c r="E35" s="34" t="n"/>
-      <c r="F35" s="34" t="n"/>
-      <c r="G35" s="34" t="n"/>
-      <c r="H35" s="34" t="n"/>
-      <c r="I35" s="34" t="n"/>
+      <c r="B35" s="36" t="n"/>
+      <c r="C35" s="36" t="n"/>
+      <c r="D35" s="36" t="n"/>
+      <c r="E35" s="36" t="n"/>
+      <c r="F35" s="36" t="n"/>
+      <c r="G35" s="36" t="n"/>
+      <c r="H35" s="36" t="n"/>
+      <c r="I35" s="36" t="n"/>
       <c r="J35" s="20">
         <f>SUM(B35:I35)</f>
         <v/>
@@ -2993,14 +3191,14 @@
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B36" s="34" t="n"/>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n"/>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="34" t="n"/>
-      <c r="G36" s="34" t="n"/>
-      <c r="H36" s="34" t="n"/>
-      <c r="I36" s="34" t="n"/>
+      <c r="B36" s="36" t="n"/>
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n"/>
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n"/>
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n"/>
+      <c r="I36" s="36" t="n"/>
       <c r="J36" s="20">
         <f>SUM(B36:I36)</f>
         <v/>
@@ -3198,28 +3396,28 @@
           <t>SALÁRIO BASE</t>
         </is>
       </c>
-      <c r="B6" s="34" t="n">
+      <c r="B6" s="36" t="n">
         <v>5648.41</v>
       </c>
-      <c r="C6" s="34" t="n">
+      <c r="C6" s="36" t="n">
         <v>1621</v>
       </c>
-      <c r="D6" s="34" t="n">
+      <c r="D6" s="36" t="n">
         <v>1621</v>
       </c>
-      <c r="E6" s="34" t="n">
+      <c r="E6" s="36" t="n">
         <v>1621</v>
       </c>
-      <c r="F6" s="34" t="n">
+      <c r="F6" s="36" t="n">
         <v>1621</v>
       </c>
-      <c r="G6" s="34" t="n">
+      <c r="G6" s="36" t="n">
         <v>1621</v>
       </c>
-      <c r="H6" s="34" t="n">
+      <c r="H6" s="36" t="n">
         <v>595</v>
       </c>
-      <c r="I6" s="34" t="n">
+      <c r="I6" s="36" t="n">
         <v>1621</v>
       </c>
       <c r="J6" s="20">
@@ -3238,16 +3436,16 @@
           <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
-      <c r="B7" s="34" t="n"/>
-      <c r="C7" s="34" t="n"/>
-      <c r="D7" s="34" t="n">
+      <c r="B7" s="36" t="n"/>
+      <c r="C7" s="36" t="n"/>
+      <c r="D7" s="36" t="n">
         <v>350</v>
       </c>
-      <c r="E7" s="34" t="n"/>
-      <c r="F7" s="34" t="n"/>
-      <c r="G7" s="34" t="n"/>
-      <c r="H7" s="34" t="n"/>
-      <c r="I7" s="34" t="n"/>
+      <c r="E7" s="36" t="n"/>
+      <c r="F7" s="36" t="n"/>
+      <c r="G7" s="36" t="n"/>
+      <c r="H7" s="36" t="n"/>
+      <c r="I7" s="36" t="n"/>
       <c r="J7" s="20">
         <f>SUM(B7:I7)</f>
         <v/>
@@ -3260,16 +3458,16 @@
           <t>HORAS EXTRAS</t>
         </is>
       </c>
-      <c r="B8" s="34" t="n"/>
-      <c r="C8" s="34" t="n"/>
-      <c r="D8" s="34" t="n">
+      <c r="B8" s="36" t="n"/>
+      <c r="C8" s="36" t="n"/>
+      <c r="D8" s="36" t="n">
         <v>442.09</v>
       </c>
-      <c r="E8" s="34" t="n"/>
-      <c r="F8" s="34" t="n"/>
-      <c r="G8" s="34" t="n"/>
-      <c r="H8" s="34" t="n"/>
-      <c r="I8" s="34" t="n">
+      <c r="E8" s="36" t="n"/>
+      <c r="F8" s="36" t="n"/>
+      <c r="G8" s="36" t="n"/>
+      <c r="H8" s="36" t="n"/>
+      <c r="I8" s="36" t="n">
         <v>221.05</v>
       </c>
       <c r="J8" s="20">
@@ -3288,26 +3486,26 @@
           <t>COMISSÃO PRODUTOS + PDV</t>
         </is>
       </c>
-      <c r="B9" s="34" t="n"/>
-      <c r="C9" s="34" t="n">
+      <c r="B9" s="36" t="n"/>
+      <c r="C9" s="36" t="n">
         <v>2000</v>
       </c>
-      <c r="D9" s="34" t="n">
+      <c r="D9" s="36" t="n">
         <v>1202</v>
       </c>
-      <c r="E9" s="34" t="n">
+      <c r="E9" s="36" t="n">
         <v>1693.68</v>
       </c>
-      <c r="F9" s="34" t="n">
+      <c r="F9" s="36" t="n">
         <v>1071</v>
       </c>
-      <c r="G9" s="34" t="n">
+      <c r="G9" s="36" t="n">
         <v>345</v>
       </c>
-      <c r="H9" s="34" t="n">
+      <c r="H9" s="36" t="n">
         <v>120</v>
       </c>
-      <c r="I9" s="34" t="n">
+      <c r="I9" s="36" t="n">
         <v>280</v>
       </c>
       <c r="J9" s="20">
@@ -3326,24 +3524,24 @@
           <t>REPOUSO REMUNERADO / DSR</t>
         </is>
       </c>
-      <c r="B10" s="34" t="n"/>
-      <c r="C10" s="34" t="n">
+      <c r="B10" s="36" t="n"/>
+      <c r="C10" s="36" t="n">
         <v>384.62</v>
       </c>
-      <c r="D10" s="34" t="n">
+      <c r="D10" s="36" t="n">
         <v>401.19</v>
       </c>
-      <c r="E10" s="34" t="n">
+      <c r="E10" s="36" t="n">
         <v>325.71</v>
       </c>
-      <c r="F10" s="34" t="n">
+      <c r="F10" s="36" t="n">
         <v>205.96</v>
       </c>
-      <c r="G10" s="34" t="n">
+      <c r="G10" s="36" t="n">
         <v>66.34999999999999</v>
       </c>
-      <c r="H10" s="34" t="n"/>
-      <c r="I10" s="34" t="n">
+      <c r="H10" s="36" t="n"/>
+      <c r="I10" s="36" t="n">
         <v>138.87</v>
       </c>
       <c r="J10" s="20">
@@ -3362,18 +3560,18 @@
           <t>AUXÍLIO GERÊNCIA</t>
         </is>
       </c>
-      <c r="B11" s="34" t="n"/>
-      <c r="C11" s="34" t="n">
+      <c r="B11" s="36" t="n"/>
+      <c r="C11" s="36" t="n">
         <v>810.5</v>
       </c>
-      <c r="D11" s="34" t="n"/>
-      <c r="E11" s="34" t="n"/>
-      <c r="F11" s="34" t="n"/>
-      <c r="G11" s="34" t="n">
+      <c r="D11" s="36" t="n"/>
+      <c r="E11" s="36" t="n"/>
+      <c r="F11" s="36" t="n"/>
+      <c r="G11" s="36" t="n">
         <v>810.5</v>
       </c>
-      <c r="H11" s="34" t="n"/>
-      <c r="I11" s="34" t="n"/>
+      <c r="H11" s="36" t="n"/>
+      <c r="I11" s="36" t="n"/>
       <c r="J11" s="20">
         <f>SUM(B11:I11)</f>
         <v/>
@@ -3386,16 +3584,16 @@
           <t>ADICIONAL PRÊMIO META CAIXA</t>
         </is>
       </c>
-      <c r="B12" s="34" t="n"/>
-      <c r="C12" s="34" t="n"/>
-      <c r="D12" s="34" t="n"/>
-      <c r="E12" s="34" t="n"/>
-      <c r="F12" s="34" t="n">
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+      <c r="E12" s="36" t="n"/>
+      <c r="F12" s="36" t="n">
         <v>307.99</v>
       </c>
-      <c r="G12" s="34" t="n"/>
-      <c r="H12" s="34" t="n"/>
-      <c r="I12" s="34" t="n">
+      <c r="G12" s="36" t="n"/>
+      <c r="H12" s="36" t="n"/>
+      <c r="I12" s="36" t="n">
         <v>307.99</v>
       </c>
       <c r="J12" s="20">
@@ -3410,22 +3608,22 @@
           <t>PRÊMIO COTA GERAL</t>
         </is>
       </c>
-      <c r="B13" s="34" t="n"/>
-      <c r="C13" s="34" t="n"/>
-      <c r="D13" s="34" t="n">
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n">
         <v>250</v>
       </c>
-      <c r="E13" s="34" t="n">
+      <c r="E13" s="36" t="n">
         <v>250</v>
       </c>
-      <c r="F13" s="34" t="n">
+      <c r="F13" s="36" t="n">
         <v>250</v>
       </c>
-      <c r="G13" s="34" t="n">
+      <c r="G13" s="36" t="n">
         <v>150</v>
       </c>
-      <c r="H13" s="34" t="n"/>
-      <c r="I13" s="34" t="n">
+      <c r="H13" s="36" t="n"/>
+      <c r="I13" s="36" t="n">
         <v>150</v>
       </c>
       <c r="J13" s="20">
@@ -3440,22 +3638,22 @@
           <t>PRÊMIO PRÉ-VENCIDOS</t>
         </is>
       </c>
-      <c r="B14" s="34" t="n"/>
-      <c r="C14" s="34" t="n"/>
-      <c r="D14" s="34" t="n">
+      <c r="B14" s="36" t="n"/>
+      <c r="C14" s="36" t="n"/>
+      <c r="D14" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="E14" s="34" t="n">
+      <c r="E14" s="36" t="n">
         <v>200</v>
       </c>
-      <c r="F14" s="34" t="n">
+      <c r="F14" s="36" t="n">
         <v>250</v>
       </c>
-      <c r="G14" s="34" t="n">
+      <c r="G14" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="H14" s="34" t="n"/>
-      <c r="I14" s="34" t="n">
+      <c r="H14" s="36" t="n"/>
+      <c r="I14" s="36" t="n">
         <v>100</v>
       </c>
       <c r="J14" s="20">
@@ -3470,22 +3668,22 @@
           <t>INCENTIVO APLICAÇÕES</t>
         </is>
       </c>
-      <c r="B15" s="34" t="n"/>
-      <c r="C15" s="34" t="n">
+      <c r="B15" s="36" t="n"/>
+      <c r="C15" s="36" t="n">
         <v>264</v>
       </c>
-      <c r="D15" s="34" t="n">
+      <c r="D15" s="36" t="n">
         <v>100</v>
       </c>
-      <c r="E15" s="34" t="n">
+      <c r="E15" s="36" t="n">
         <v>290</v>
       </c>
-      <c r="F15" s="34" t="n">
+      <c r="F15" s="36" t="n">
         <v>292</v>
       </c>
-      <c r="G15" s="34" t="n"/>
-      <c r="H15" s="34" t="n"/>
-      <c r="I15" s="34" t="n"/>
+      <c r="G15" s="36" t="n"/>
+      <c r="H15" s="36" t="n"/>
+      <c r="I15" s="36" t="n"/>
       <c r="J15" s="20">
         <f>SUM(B15:I15)</f>
         <v/>
@@ -3498,16 +3696,16 @@
           <t>INCENTIVO VITAMINAS</t>
         </is>
       </c>
-      <c r="B16" s="34" t="n"/>
-      <c r="C16" s="34" t="n"/>
-      <c r="D16" s="34" t="n"/>
-      <c r="E16" s="34" t="n"/>
-      <c r="F16" s="34" t="n">
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+      <c r="E16" s="36" t="n"/>
+      <c r="F16" s="36" t="n">
         <v>40</v>
       </c>
-      <c r="G16" s="34" t="n"/>
-      <c r="H16" s="34" t="n"/>
-      <c r="I16" s="34" t="n"/>
+      <c r="G16" s="36" t="n"/>
+      <c r="H16" s="36" t="n"/>
+      <c r="I16" s="36" t="n"/>
       <c r="J16" s="20">
         <f>SUM(B16:I16)</f>
         <v/>
@@ -3581,24 +3779,24 @@
           <t>ADIANTAMENTO / VALES</t>
         </is>
       </c>
-      <c r="B19" s="34" t="n"/>
-      <c r="C19" s="34" t="n">
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n">
         <v>-2300</v>
       </c>
-      <c r="D19" s="34" t="n">
+      <c r="D19" s="36" t="n">
         <v>-1500</v>
       </c>
-      <c r="E19" s="34" t="n">
+      <c r="E19" s="36" t="n">
         <v>-1300</v>
       </c>
-      <c r="F19" s="34" t="n">
+      <c r="F19" s="36" t="n">
         <v>-1300</v>
       </c>
-      <c r="G19" s="34" t="n">
+      <c r="G19" s="36" t="n">
         <v>-1200</v>
       </c>
-      <c r="H19" s="34" t="n"/>
-      <c r="I19" s="34" t="n"/>
+      <c r="H19" s="36" t="n"/>
+      <c r="I19" s="36" t="n"/>
       <c r="J19" s="20">
         <f>SUM(B19:I19)</f>
         <v/>
@@ -3611,22 +3809,22 @@
           <t>ADIANT. VALES INCENT. E APLIC.</t>
         </is>
       </c>
-      <c r="B20" s="34" t="n"/>
-      <c r="C20" s="34" t="n">
+      <c r="B20" s="36" t="n"/>
+      <c r="C20" s="36" t="n">
         <v>-264</v>
       </c>
-      <c r="D20" s="34" t="n">
+      <c r="D20" s="36" t="n">
         <v>-100</v>
       </c>
-      <c r="E20" s="34" t="n">
+      <c r="E20" s="36" t="n">
         <v>-290</v>
       </c>
-      <c r="F20" s="34" t="n">
+      <c r="F20" s="36" t="n">
         <v>-332</v>
       </c>
-      <c r="G20" s="34" t="n"/>
-      <c r="H20" s="34" t="n"/>
-      <c r="I20" s="34" t="n"/>
+      <c r="G20" s="36" t="n"/>
+      <c r="H20" s="36" t="n"/>
+      <c r="I20" s="36" t="n"/>
       <c r="J20" s="20">
         <f>SUM(B20:I20)</f>
         <v/>
@@ -3639,22 +3837,22 @@
           <t>CONVÊNIO</t>
         </is>
       </c>
-      <c r="B21" s="34" t="n"/>
-      <c r="C21" s="34" t="n">
+      <c r="B21" s="36" t="n"/>
+      <c r="C21" s="36" t="n">
         <v>-300</v>
       </c>
-      <c r="D21" s="34" t="n"/>
-      <c r="E21" s="34" t="n">
+      <c r="D21" s="36" t="n"/>
+      <c r="E21" s="36" t="n">
         <v>-500</v>
       </c>
-      <c r="F21" s="34" t="n">
+      <c r="F21" s="36" t="n">
         <v>-300</v>
       </c>
-      <c r="G21" s="34" t="n">
+      <c r="G21" s="36" t="n">
         <v>-300</v>
       </c>
-      <c r="H21" s="34" t="n"/>
-      <c r="I21" s="34" t="n"/>
+      <c r="H21" s="36" t="n"/>
+      <c r="I21" s="36" t="n"/>
       <c r="J21" s="20">
         <f>SUM(B21:I21)</f>
         <v/>
@@ -3667,14 +3865,14 @@
           <t>DESCONTO FALTAS</t>
         </is>
       </c>
-      <c r="B22" s="34" t="n"/>
-      <c r="C22" s="34" t="n"/>
-      <c r="D22" s="34" t="n"/>
-      <c r="E22" s="34" t="n"/>
-      <c r="F22" s="34" t="n"/>
-      <c r="G22" s="34" t="n"/>
-      <c r="H22" s="34" t="n"/>
-      <c r="I22" s="34" t="n"/>
+      <c r="B22" s="36" t="n"/>
+      <c r="C22" s="36" t="n"/>
+      <c r="D22" s="36" t="n"/>
+      <c r="E22" s="36" t="n"/>
+      <c r="F22" s="36" t="n"/>
+      <c r="G22" s="36" t="n"/>
+      <c r="H22" s="36" t="n"/>
+      <c r="I22" s="36" t="n"/>
       <c r="J22" s="20">
         <f>SUM(B22:I22)</f>
         <v/>
@@ -3687,20 +3885,20 @@
           <t>DESCONTO VALE TRANSPORTE 6%</t>
         </is>
       </c>
-      <c r="B23" s="34" t="n"/>
-      <c r="C23" s="34" t="n"/>
-      <c r="D23" s="34" t="n">
+      <c r="B23" s="36" t="n"/>
+      <c r="C23" s="36" t="n"/>
+      <c r="D23" s="36" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="E23" s="34" t="n">
+      <c r="E23" s="36" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="F23" s="34" t="n">
+      <c r="F23" s="36" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="G23" s="34" t="n"/>
-      <c r="H23" s="34" t="n"/>
-      <c r="I23" s="34" t="n">
+      <c r="G23" s="36" t="n"/>
+      <c r="H23" s="36" t="n"/>
+      <c r="I23" s="36" t="n">
         <v>-84.29000000000001</v>
       </c>
       <c r="J23" s="20">
@@ -3715,26 +3913,26 @@
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="B24" s="34" t="n">
+      <c r="B24" s="36" t="n">
         <v>-592.27</v>
       </c>
-      <c r="C24" s="34" t="n">
+      <c r="C24" s="36" t="n">
         <v>-480.85</v>
       </c>
-      <c r="D24" s="34" t="n">
+      <c r="D24" s="36" t="n">
         <v>-426.78</v>
       </c>
-      <c r="E24" s="34" t="n">
+      <c r="E24" s="36" t="n">
         <v>-414.75</v>
       </c>
-      <c r="F24" s="34" t="n">
+      <c r="F24" s="36" t="n">
         <v>-373.14</v>
       </c>
-      <c r="G24" s="34" t="n">
+      <c r="G24" s="36" t="n">
         <v>-213.94</v>
       </c>
-      <c r="H24" s="34" t="n"/>
-      <c r="I24" s="34" t="n">
+      <c r="H24" s="36" t="n"/>
+      <c r="I24" s="36" t="n">
         <v>-229.38</v>
       </c>
       <c r="J24" s="20">
@@ -3749,16 +3947,16 @@
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="B25" s="34" t="n">
+      <c r="B25" s="36" t="n">
         <v>-251.04</v>
       </c>
-      <c r="C25" s="34" t="n"/>
-      <c r="D25" s="34" t="n"/>
-      <c r="E25" s="34" t="n"/>
-      <c r="F25" s="34" t="n"/>
-      <c r="G25" s="34" t="n"/>
-      <c r="H25" s="34" t="n"/>
-      <c r="I25" s="34" t="n"/>
+      <c r="C25" s="36" t="n"/>
+      <c r="D25" s="36" t="n"/>
+      <c r="E25" s="36" t="n"/>
+      <c r="F25" s="36" t="n"/>
+      <c r="G25" s="36" t="n"/>
+      <c r="H25" s="36" t="n"/>
+      <c r="I25" s="36" t="n"/>
       <c r="J25" s="20">
         <f>SUM(B25:I25)</f>
         <v/>
@@ -3876,28 +4074,28 @@
           <t>SALDO FINAL DA PLANILHA ORIGINAL</t>
         </is>
       </c>
-      <c r="B29" s="34" t="n">
+      <c r="B29" s="36" t="n">
         <v>4805.1</v>
       </c>
-      <c r="C29" s="34" t="n">
+      <c r="C29" s="36" t="n">
         <v>1735.27</v>
       </c>
-      <c r="D29" s="34" t="n">
+      <c r="D29" s="36" t="n">
         <v>2355.21</v>
       </c>
-      <c r="E29" s="34" t="n">
+      <c r="E29" s="36" t="n">
         <v>1791.35</v>
       </c>
-      <c r="F29" s="34" t="n">
+      <c r="F29" s="36" t="n">
         <v>1648.52</v>
       </c>
-      <c r="G29" s="34" t="n">
+      <c r="G29" s="36" t="n">
         <v>1378.91</v>
       </c>
-      <c r="H29" s="34" t="n">
+      <c r="H29" s="36" t="n">
         <v>715</v>
       </c>
-      <c r="I29" s="34" t="n">
+      <c r="I29" s="36" t="n">
         <v>2505.24</v>
       </c>
       <c r="J29" s="20">
@@ -3981,35 +4179,35 @@
           <t>DSR pago (fator 5/26)</t>
         </is>
       </c>
-      <c r="B32" s="36">
+      <c r="B32" s="35">
         <f>B10</f>
         <v/>
       </c>
-      <c r="C32" s="36">
+      <c r="C32" s="35">
         <f>C10</f>
         <v/>
       </c>
-      <c r="D32" s="36">
+      <c r="D32" s="35">
         <f>D10</f>
         <v/>
       </c>
-      <c r="E32" s="36">
+      <c r="E32" s="35">
         <f>E10</f>
         <v/>
       </c>
-      <c r="F32" s="36">
+      <c r="F32" s="35">
         <f>F10</f>
         <v/>
       </c>
-      <c r="G32" s="36">
+      <c r="G32" s="35">
         <f>G10</f>
         <v/>
       </c>
-      <c r="H32" s="36">
+      <c r="H32" s="35">
         <f>H10</f>
         <v/>
       </c>
-      <c r="I32" s="36">
+      <c r="I32" s="35">
         <f>I10</f>
         <v/>
       </c>
@@ -4029,35 +4227,35 @@
           <t>DSR recalculado (fator 4/27 · comissão + HE)</t>
         </is>
       </c>
-      <c r="B33" s="36">
+      <c r="B33" s="35">
         <f>ROUND((B9+B8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="35">
         <f>ROUND((C9+C8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="35">
         <f>ROUND((D9+D8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="35">
         <f>ROUND((E9+E8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="35">
         <f>ROUND((F9+F8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="35">
         <f>ROUND((G9+G8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="35">
         <f>ROUND((H9+H8)*4/27,2)</f>
         <v/>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="35">
         <f>ROUND((I9+I8)*4/27,2)</f>
         <v/>
       </c>
@@ -4142,22 +4340,22 @@
           <t>VALE TRANSPORTE (passagens de agosto)</t>
         </is>
       </c>
-      <c r="B36" s="34" t="n">
+      <c r="B36" s="36" t="n">
         <v>350</v>
       </c>
-      <c r="C36" s="34" t="n"/>
-      <c r="D36" s="34" t="n">
+      <c r="C36" s="36" t="n"/>
+      <c r="D36" s="36" t="n">
         <v>416</v>
       </c>
-      <c r="E36" s="34" t="n"/>
-      <c r="F36" s="34" t="n">
+      <c r="E36" s="36" t="n"/>
+      <c r="F36" s="36" t="n">
         <v>500</v>
       </c>
-      <c r="G36" s="34" t="n"/>
-      <c r="H36" s="34" t="n">
+      <c r="G36" s="36" t="n"/>
+      <c r="H36" s="36" t="n">
         <v>135</v>
       </c>
-      <c r="I36" s="34" t="n">
+      <c r="I36" s="36" t="n">
         <v>288</v>
       </c>
       <c r="J36" s="20">
@@ -4176,26 +4374,26 @@
           <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
         </is>
       </c>
-      <c r="B37" s="34" t="n">
+      <c r="B37" s="36" t="n">
         <v>647</v>
       </c>
-      <c r="C37" s="34" t="n">
+      <c r="C37" s="36" t="n">
         <v>84</v>
       </c>
-      <c r="D37" s="34" t="n">
+      <c r="D37" s="36" t="n">
         <v>48</v>
       </c>
-      <c r="E37" s="34" t="n">
+      <c r="E37" s="36" t="n">
         <v>50</v>
       </c>
-      <c r="F37" s="34" t="n">
+      <c r="F37" s="36" t="n">
         <v>75</v>
       </c>
-      <c r="G37" s="34" t="n">
+      <c r="G37" s="36" t="n">
         <v>84</v>
       </c>
-      <c r="H37" s="34" t="n"/>
-      <c r="I37" s="34" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
       <c r="J37" s="20">
         <f>SUM(B37:I37)</f>
         <v/>
@@ -4333,7 +4531,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D5" s="35">
+      <c r="D5" s="34">
         <f>'HOLERITE AGO.26'!B6</f>
         <v/>
       </c>
@@ -4355,7 +4553,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="34">
         <f>'HOLERITE AGO.26'!B7</f>
         <v/>
       </c>
@@ -4377,7 +4575,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D7" s="35">
+      <c r="D7" s="34">
         <f>'HOLERITE AGO.26'!B8</f>
         <v/>
       </c>
@@ -4399,7 +4597,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D8" s="35">
+      <c r="D8" s="34">
         <f>'HOLERITE AGO.26'!B11</f>
         <v/>
       </c>
@@ -4421,7 +4619,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D9" s="35">
+      <c r="D9" s="34">
         <f>'HOLERITE AGO.26'!B12</f>
         <v/>
       </c>
@@ -4443,7 +4641,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D10" s="35">
+      <c r="D10" s="34">
         <f>'HOLERITE AGO.26'!B13</f>
         <v/>
       </c>
@@ -4465,7 +4663,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D11" s="35">
+      <c r="D11" s="34">
         <f>'HOLERITE AGO.26'!B14</f>
         <v/>
       </c>
@@ -4487,7 +4685,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D12" s="35">
+      <c r="D12" s="34">
         <f>'HOLERITE AGO.26'!B15</f>
         <v/>
       </c>
@@ -4509,7 +4707,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="34">
         <f>'HOLERITE AGO.26'!B16</f>
         <v/>
       </c>
@@ -4531,7 +4729,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="34">
         <f>'HOLERITE AGO.26'!B19</f>
         <v/>
       </c>
@@ -4553,7 +4751,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="34">
         <f>'HOLERITE AGO.26'!B20</f>
         <v/>
       </c>
@@ -4575,7 +4773,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D16" s="35">
+      <c r="D16" s="34">
         <f>'HOLERITE AGO.26'!B21</f>
         <v/>
       </c>
@@ -4619,7 +4817,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D18" s="35">
+      <c r="D18" s="34">
         <f>'HOLERITE AGO.26'!B24</f>
         <v/>
       </c>
@@ -4641,7 +4839,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D19" s="35">
+      <c r="D19" s="34">
         <f>'HOLERITE AGO.26'!B25</f>
         <v/>
       </c>
@@ -4663,7 +4861,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D20" s="35">
+      <c r="D20" s="34">
         <f>'HOLERITE AGO.26'!B26</f>
         <v/>
       </c>
@@ -4685,7 +4883,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D21" s="35">
+      <c r="D21" s="34">
         <f>'HOLERITE AGO.26'!B27</f>
         <v/>
       </c>
@@ -4707,7 +4905,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D22" s="35">
+      <c r="D22" s="34">
         <f>'HOLERITE AGO.26'!B28</f>
         <v/>
       </c>
@@ -4729,7 +4927,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D23" s="35">
+      <c r="D23" s="34">
         <f>'HOLERITE AGO.26'!B29</f>
         <v/>
       </c>
@@ -4751,7 +4949,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D24" s="35">
+      <c r="D24" s="34">
         <f>'HOLERITE AGO.26'!B30</f>
         <v/>
       </c>
@@ -4817,7 +5015,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D28" s="35">
+      <c r="D28" s="34">
         <f>'HOLERITE AGO.26'!C6</f>
         <v/>
       </c>
@@ -4839,7 +5037,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D29" s="35">
+      <c r="D29" s="34">
         <f>'HOLERITE AGO.26'!C7</f>
         <v/>
       </c>
@@ -4861,7 +5059,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="34">
         <f>'HOLERITE AGO.26'!C8</f>
         <v/>
       </c>
@@ -4883,7 +5081,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="34">
         <f>'HOLERITE AGO.26'!C11</f>
         <v/>
       </c>
@@ -4905,7 +5103,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D32" s="35">
+      <c r="D32" s="34">
         <f>'HOLERITE AGO.26'!C12</f>
         <v/>
       </c>
@@ -4927,7 +5125,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="34">
         <f>'HOLERITE AGO.26'!C13</f>
         <v/>
       </c>
@@ -4949,7 +5147,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="34">
         <f>'HOLERITE AGO.26'!C14</f>
         <v/>
       </c>
@@ -4971,7 +5169,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="34">
         <f>'HOLERITE AGO.26'!C15</f>
         <v/>
       </c>
@@ -4993,7 +5191,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="34">
         <f>'HOLERITE AGO.26'!C16</f>
         <v/>
       </c>
@@ -5015,7 +5213,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D37" s="35">
+      <c r="D37" s="34">
         <f>'HOLERITE AGO.26'!C19</f>
         <v/>
       </c>
@@ -5037,7 +5235,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="34">
         <f>'HOLERITE AGO.26'!C20</f>
         <v/>
       </c>
@@ -5059,7 +5257,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D39" s="35">
+      <c r="D39" s="34">
         <f>'HOLERITE AGO.26'!C21</f>
         <v/>
       </c>
@@ -5103,7 +5301,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D41" s="35">
+      <c r="D41" s="34">
         <f>'HOLERITE AGO.26'!C24</f>
         <v/>
       </c>
@@ -5125,7 +5323,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D42" s="35">
+      <c r="D42" s="34">
         <f>'HOLERITE AGO.26'!C25</f>
         <v/>
       </c>
@@ -5147,7 +5345,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D43" s="35">
+      <c r="D43" s="34">
         <f>'HOLERITE AGO.26'!C26</f>
         <v/>
       </c>
@@ -5169,7 +5367,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D44" s="35">
+      <c r="D44" s="34">
         <f>'HOLERITE AGO.26'!C27</f>
         <v/>
       </c>
@@ -5191,7 +5389,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D45" s="35">
+      <c r="D45" s="34">
         <f>'HOLERITE AGO.26'!C28</f>
         <v/>
       </c>
@@ -5213,7 +5411,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D46" s="35">
+      <c r="D46" s="34">
         <f>'HOLERITE AGO.26'!C29</f>
         <v/>
       </c>
@@ -5235,7 +5433,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D47" s="35">
+      <c r="D47" s="34">
         <f>'HOLERITE AGO.26'!C30</f>
         <v/>
       </c>
@@ -5301,7 +5499,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D51" s="35">
+      <c r="D51" s="34">
         <f>'HOLERITE AGO.26'!D6</f>
         <v/>
       </c>
@@ -5323,7 +5521,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D52" s="35">
+      <c r="D52" s="34">
         <f>'HOLERITE AGO.26'!D7</f>
         <v/>
       </c>
@@ -5345,7 +5543,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D53" s="35">
+      <c r="D53" s="34">
         <f>'HOLERITE AGO.26'!D8</f>
         <v/>
       </c>
@@ -5367,7 +5565,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D54" s="35">
+      <c r="D54" s="34">
         <f>'HOLERITE AGO.26'!D11</f>
         <v/>
       </c>
@@ -5389,7 +5587,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D55" s="35">
+      <c r="D55" s="34">
         <f>'HOLERITE AGO.26'!D12</f>
         <v/>
       </c>
@@ -5411,7 +5609,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D56" s="35">
+      <c r="D56" s="34">
         <f>'HOLERITE AGO.26'!D13</f>
         <v/>
       </c>
@@ -5433,7 +5631,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="34">
         <f>'HOLERITE AGO.26'!D14</f>
         <v/>
       </c>
@@ -5455,7 +5653,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D58" s="35">
+      <c r="D58" s="34">
         <f>'HOLERITE AGO.26'!D15</f>
         <v/>
       </c>
@@ -5477,7 +5675,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D59" s="35">
+      <c r="D59" s="34">
         <f>'HOLERITE AGO.26'!D16</f>
         <v/>
       </c>
@@ -5499,7 +5697,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D60" s="35">
+      <c r="D60" s="34">
         <f>'HOLERITE AGO.26'!D19</f>
         <v/>
       </c>
@@ -5521,7 +5719,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D61" s="35">
+      <c r="D61" s="34">
         <f>'HOLERITE AGO.26'!D20</f>
         <v/>
       </c>
@@ -5543,7 +5741,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D62" s="35">
+      <c r="D62" s="34">
         <f>'HOLERITE AGO.26'!D21</f>
         <v/>
       </c>
@@ -5587,7 +5785,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D64" s="35">
+      <c r="D64" s="34">
         <f>'HOLERITE AGO.26'!D24</f>
         <v/>
       </c>
@@ -5609,7 +5807,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D65" s="35">
+      <c r="D65" s="34">
         <f>'HOLERITE AGO.26'!D25</f>
         <v/>
       </c>
@@ -5631,7 +5829,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D66" s="35">
+      <c r="D66" s="34">
         <f>'HOLERITE AGO.26'!D26</f>
         <v/>
       </c>
@@ -5653,7 +5851,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D67" s="35">
+      <c r="D67" s="34">
         <f>'HOLERITE AGO.26'!D27</f>
         <v/>
       </c>
@@ -5675,7 +5873,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D68" s="35">
+      <c r="D68" s="34">
         <f>'HOLERITE AGO.26'!D28</f>
         <v/>
       </c>
@@ -5697,7 +5895,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D69" s="35">
+      <c r="D69" s="34">
         <f>'HOLERITE AGO.26'!D29</f>
         <v/>
       </c>
@@ -5719,7 +5917,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D70" s="35">
+      <c r="D70" s="34">
         <f>'HOLERITE AGO.26'!D30</f>
         <v/>
       </c>
@@ -5785,7 +5983,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D74" s="35">
+      <c r="D74" s="34">
         <f>'HOLERITE AGO.26'!E6</f>
         <v/>
       </c>
@@ -5807,7 +6005,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D75" s="35">
+      <c r="D75" s="34">
         <f>'HOLERITE AGO.26'!E7</f>
         <v/>
       </c>
@@ -5829,7 +6027,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D76" s="35">
+      <c r="D76" s="34">
         <f>'HOLERITE AGO.26'!E8</f>
         <v/>
       </c>
@@ -5851,7 +6049,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D77" s="35">
+      <c r="D77" s="34">
         <f>'HOLERITE AGO.26'!E11</f>
         <v/>
       </c>
@@ -5873,7 +6071,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D78" s="35">
+      <c r="D78" s="34">
         <f>'HOLERITE AGO.26'!E12</f>
         <v/>
       </c>
@@ -5895,7 +6093,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D79" s="35">
+      <c r="D79" s="34">
         <f>'HOLERITE AGO.26'!E13</f>
         <v/>
       </c>
@@ -5917,7 +6115,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D80" s="35">
+      <c r="D80" s="34">
         <f>'HOLERITE AGO.26'!E14</f>
         <v/>
       </c>
@@ -5939,7 +6137,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D81" s="35">
+      <c r="D81" s="34">
         <f>'HOLERITE AGO.26'!E15</f>
         <v/>
       </c>
@@ -5961,7 +6159,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D82" s="35">
+      <c r="D82" s="34">
         <f>'HOLERITE AGO.26'!E16</f>
         <v/>
       </c>
@@ -5983,7 +6181,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D83" s="35">
+      <c r="D83" s="34">
         <f>'HOLERITE AGO.26'!E19</f>
         <v/>
       </c>
@@ -6005,7 +6203,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D84" s="35">
+      <c r="D84" s="34">
         <f>'HOLERITE AGO.26'!E20</f>
         <v/>
       </c>
@@ -6027,7 +6225,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D85" s="35">
+      <c r="D85" s="34">
         <f>'HOLERITE AGO.26'!E21</f>
         <v/>
       </c>
@@ -6071,7 +6269,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D87" s="35">
+      <c r="D87" s="34">
         <f>'HOLERITE AGO.26'!E24</f>
         <v/>
       </c>
@@ -6093,7 +6291,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D88" s="35">
+      <c r="D88" s="34">
         <f>'HOLERITE AGO.26'!E25</f>
         <v/>
       </c>
@@ -6115,7 +6313,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D89" s="35">
+      <c r="D89" s="34">
         <f>'HOLERITE AGO.26'!E26</f>
         <v/>
       </c>
@@ -6137,7 +6335,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D90" s="35">
+      <c r="D90" s="34">
         <f>'HOLERITE AGO.26'!E27</f>
         <v/>
       </c>
@@ -6159,7 +6357,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D91" s="35">
+      <c r="D91" s="34">
         <f>'HOLERITE AGO.26'!E28</f>
         <v/>
       </c>
@@ -6181,7 +6379,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D92" s="35">
+      <c r="D92" s="34">
         <f>'HOLERITE AGO.26'!E29</f>
         <v/>
       </c>
@@ -6203,7 +6401,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D93" s="35">
+      <c r="D93" s="34">
         <f>'HOLERITE AGO.26'!E30</f>
         <v/>
       </c>
@@ -6269,7 +6467,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D97" s="35">
+      <c r="D97" s="34">
         <f>'HOLERITE AGO.26'!F6</f>
         <v/>
       </c>
@@ -6291,7 +6489,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D98" s="35">
+      <c r="D98" s="34">
         <f>'HOLERITE AGO.26'!F7</f>
         <v/>
       </c>
@@ -6313,7 +6511,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D99" s="35">
+      <c r="D99" s="34">
         <f>'HOLERITE AGO.26'!F8</f>
         <v/>
       </c>
@@ -6335,7 +6533,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D100" s="35">
+      <c r="D100" s="34">
         <f>'HOLERITE AGO.26'!F11</f>
         <v/>
       </c>
@@ -6357,7 +6555,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D101" s="35">
+      <c r="D101" s="34">
         <f>'HOLERITE AGO.26'!F12</f>
         <v/>
       </c>
@@ -6379,7 +6577,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D102" s="35">
+      <c r="D102" s="34">
         <f>'HOLERITE AGO.26'!F13</f>
         <v/>
       </c>
@@ -6401,7 +6599,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D103" s="35">
+      <c r="D103" s="34">
         <f>'HOLERITE AGO.26'!F14</f>
         <v/>
       </c>
@@ -6423,7 +6621,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D104" s="35">
+      <c r="D104" s="34">
         <f>'HOLERITE AGO.26'!F15</f>
         <v/>
       </c>
@@ -6445,7 +6643,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D105" s="35">
+      <c r="D105" s="34">
         <f>'HOLERITE AGO.26'!F16</f>
         <v/>
       </c>
@@ -6467,7 +6665,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D106" s="35">
+      <c r="D106" s="34">
         <f>'HOLERITE AGO.26'!F19</f>
         <v/>
       </c>
@@ -6489,7 +6687,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D107" s="35">
+      <c r="D107" s="34">
         <f>'HOLERITE AGO.26'!F20</f>
         <v/>
       </c>
@@ -6511,7 +6709,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D108" s="35">
+      <c r="D108" s="34">
         <f>'HOLERITE AGO.26'!F21</f>
         <v/>
       </c>
@@ -6555,7 +6753,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D110" s="35">
+      <c r="D110" s="34">
         <f>'HOLERITE AGO.26'!F24</f>
         <v/>
       </c>
@@ -6577,7 +6775,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D111" s="35">
+      <c r="D111" s="34">
         <f>'HOLERITE AGO.26'!F25</f>
         <v/>
       </c>
@@ -6599,7 +6797,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D112" s="35">
+      <c r="D112" s="34">
         <f>'HOLERITE AGO.26'!F26</f>
         <v/>
       </c>
@@ -6621,7 +6819,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D113" s="35">
+      <c r="D113" s="34">
         <f>'HOLERITE AGO.26'!F27</f>
         <v/>
       </c>
@@ -6643,7 +6841,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D114" s="35">
+      <c r="D114" s="34">
         <f>'HOLERITE AGO.26'!F28</f>
         <v/>
       </c>
@@ -6665,7 +6863,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D115" s="35">
+      <c r="D115" s="34">
         <f>'HOLERITE AGO.26'!F29</f>
         <v/>
       </c>
@@ -6687,7 +6885,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D116" s="35">
+      <c r="D116" s="34">
         <f>'HOLERITE AGO.26'!F30</f>
         <v/>
       </c>
@@ -6753,7 +6951,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D120" s="35">
+      <c r="D120" s="34">
         <f>'HOLERITE AGO.26'!G6</f>
         <v/>
       </c>
@@ -6775,7 +6973,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D121" s="35">
+      <c r="D121" s="34">
         <f>'HOLERITE AGO.26'!G7</f>
         <v/>
       </c>
@@ -6797,7 +6995,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D122" s="35">
+      <c r="D122" s="34">
         <f>'HOLERITE AGO.26'!G8</f>
         <v/>
       </c>
@@ -6819,7 +7017,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D123" s="35">
+      <c r="D123" s="34">
         <f>'HOLERITE AGO.26'!G11</f>
         <v/>
       </c>
@@ -6841,7 +7039,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D124" s="35">
+      <c r="D124" s="34">
         <f>'HOLERITE AGO.26'!G12</f>
         <v/>
       </c>
@@ -6863,7 +7061,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D125" s="35">
+      <c r="D125" s="34">
         <f>'HOLERITE AGO.26'!G13</f>
         <v/>
       </c>
@@ -6885,7 +7083,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D126" s="35">
+      <c r="D126" s="34">
         <f>'HOLERITE AGO.26'!G14</f>
         <v/>
       </c>
@@ -6907,7 +7105,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D127" s="35">
+      <c r="D127" s="34">
         <f>'HOLERITE AGO.26'!G15</f>
         <v/>
       </c>
@@ -6929,7 +7127,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D128" s="35">
+      <c r="D128" s="34">
         <f>'HOLERITE AGO.26'!G16</f>
         <v/>
       </c>
@@ -6951,7 +7149,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D129" s="35">
+      <c r="D129" s="34">
         <f>'HOLERITE AGO.26'!G19</f>
         <v/>
       </c>
@@ -6973,7 +7171,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D130" s="35">
+      <c r="D130" s="34">
         <f>'HOLERITE AGO.26'!G20</f>
         <v/>
       </c>
@@ -6995,7 +7193,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D131" s="35">
+      <c r="D131" s="34">
         <f>'HOLERITE AGO.26'!G21</f>
         <v/>
       </c>
@@ -7039,7 +7237,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D133" s="35">
+      <c r="D133" s="34">
         <f>'HOLERITE AGO.26'!G24</f>
         <v/>
       </c>
@@ -7061,7 +7259,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D134" s="35">
+      <c r="D134" s="34">
         <f>'HOLERITE AGO.26'!G25</f>
         <v/>
       </c>
@@ -7083,7 +7281,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D135" s="35">
+      <c r="D135" s="34">
         <f>'HOLERITE AGO.26'!G26</f>
         <v/>
       </c>
@@ -7105,7 +7303,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D136" s="35">
+      <c r="D136" s="34">
         <f>'HOLERITE AGO.26'!G27</f>
         <v/>
       </c>
@@ -7127,7 +7325,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D137" s="35">
+      <c r="D137" s="34">
         <f>'HOLERITE AGO.26'!G28</f>
         <v/>
       </c>
@@ -7149,7 +7347,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D138" s="35">
+      <c r="D138" s="34">
         <f>'HOLERITE AGO.26'!G29</f>
         <v/>
       </c>
@@ -7171,7 +7369,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D139" s="35">
+      <c r="D139" s="34">
         <f>'HOLERITE AGO.26'!G30</f>
         <v/>
       </c>
@@ -7237,7 +7435,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D143" s="35">
+      <c r="D143" s="34">
         <f>'HOLERITE AGO.26'!H6</f>
         <v/>
       </c>
@@ -7259,7 +7457,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D144" s="35">
+      <c r="D144" s="34">
         <f>'HOLERITE AGO.26'!H7</f>
         <v/>
       </c>
@@ -7281,7 +7479,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D145" s="35">
+      <c r="D145" s="34">
         <f>'HOLERITE AGO.26'!H8</f>
         <v/>
       </c>
@@ -7303,7 +7501,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D146" s="35">
+      <c r="D146" s="34">
         <f>'HOLERITE AGO.26'!H11</f>
         <v/>
       </c>
@@ -7325,7 +7523,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D147" s="35">
+      <c r="D147" s="34">
         <f>'HOLERITE AGO.26'!H12</f>
         <v/>
       </c>
@@ -7347,7 +7545,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D148" s="35">
+      <c r="D148" s="34">
         <f>'HOLERITE AGO.26'!H13</f>
         <v/>
       </c>
@@ -7369,7 +7567,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D149" s="35">
+      <c r="D149" s="34">
         <f>'HOLERITE AGO.26'!H14</f>
         <v/>
       </c>
@@ -7391,7 +7589,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D150" s="35">
+      <c r="D150" s="34">
         <f>'HOLERITE AGO.26'!H15</f>
         <v/>
       </c>
@@ -7413,7 +7611,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D151" s="35">
+      <c r="D151" s="34">
         <f>'HOLERITE AGO.26'!H16</f>
         <v/>
       </c>
@@ -7435,7 +7633,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D152" s="35">
+      <c r="D152" s="34">
         <f>'HOLERITE AGO.26'!H19</f>
         <v/>
       </c>
@@ -7457,7 +7655,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D153" s="35">
+      <c r="D153" s="34">
         <f>'HOLERITE AGO.26'!H20</f>
         <v/>
       </c>
@@ -7479,7 +7677,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D154" s="35">
+      <c r="D154" s="34">
         <f>'HOLERITE AGO.26'!H21</f>
         <v/>
       </c>
@@ -7523,7 +7721,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D156" s="35">
+      <c r="D156" s="34">
         <f>'HOLERITE AGO.26'!H24</f>
         <v/>
       </c>
@@ -7545,7 +7743,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D157" s="35">
+      <c r="D157" s="34">
         <f>'HOLERITE AGO.26'!H25</f>
         <v/>
       </c>
@@ -7567,7 +7765,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D158" s="35">
+      <c r="D158" s="34">
         <f>'HOLERITE AGO.26'!H26</f>
         <v/>
       </c>
@@ -7589,7 +7787,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D159" s="35">
+      <c r="D159" s="34">
         <f>'HOLERITE AGO.26'!H27</f>
         <v/>
       </c>
@@ -7611,7 +7809,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D160" s="35">
+      <c r="D160" s="34">
         <f>'HOLERITE AGO.26'!H28</f>
         <v/>
       </c>
@@ -7633,7 +7831,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D161" s="35">
+      <c r="D161" s="34">
         <f>'HOLERITE AGO.26'!H29</f>
         <v/>
       </c>
@@ -7655,7 +7853,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D162" s="35">
+      <c r="D162" s="34">
         <f>'HOLERITE AGO.26'!H30</f>
         <v/>
       </c>
@@ -7721,7 +7919,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D166" s="35">
+      <c r="D166" s="34">
         <f>'HOLERITE AGO.26'!I6</f>
         <v/>
       </c>
@@ -7743,7 +7941,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D167" s="35">
+      <c r="D167" s="34">
         <f>'HOLERITE AGO.26'!I7</f>
         <v/>
       </c>
@@ -7765,7 +7963,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D168" s="35">
+      <c r="D168" s="34">
         <f>'HOLERITE AGO.26'!I8</f>
         <v/>
       </c>
@@ -7787,7 +7985,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D169" s="35">
+      <c r="D169" s="34">
         <f>'HOLERITE AGO.26'!I11</f>
         <v/>
       </c>
@@ -7809,7 +8007,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D170" s="35">
+      <c r="D170" s="34">
         <f>'HOLERITE AGO.26'!I12</f>
         <v/>
       </c>
@@ -7831,7 +8029,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D171" s="35">
+      <c r="D171" s="34">
         <f>'HOLERITE AGO.26'!I13</f>
         <v/>
       </c>
@@ -7853,7 +8051,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D172" s="35">
+      <c r="D172" s="34">
         <f>'HOLERITE AGO.26'!I14</f>
         <v/>
       </c>
@@ -7875,7 +8073,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D173" s="35">
+      <c r="D173" s="34">
         <f>'HOLERITE AGO.26'!I15</f>
         <v/>
       </c>
@@ -7897,7 +8095,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D174" s="35">
+      <c r="D174" s="34">
         <f>'HOLERITE AGO.26'!I16</f>
         <v/>
       </c>
@@ -7919,7 +8117,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D175" s="35">
+      <c r="D175" s="34">
         <f>'HOLERITE AGO.26'!I19</f>
         <v/>
       </c>
@@ -7941,7 +8139,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D176" s="35">
+      <c r="D176" s="34">
         <f>'HOLERITE AGO.26'!I20</f>
         <v/>
       </c>
@@ -7963,7 +8161,7 @@
           <t>Provento</t>
         </is>
       </c>
-      <c r="D177" s="35">
+      <c r="D177" s="34">
         <f>'HOLERITE AGO.26'!I21</f>
         <v/>
       </c>
@@ -8007,7 +8205,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D179" s="35">
+      <c r="D179" s="34">
         <f>'HOLERITE AGO.26'!I24</f>
         <v/>
       </c>
@@ -8029,7 +8227,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D180" s="35">
+      <c r="D180" s="34">
         <f>'HOLERITE AGO.26'!I25</f>
         <v/>
       </c>
@@ -8051,7 +8249,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D181" s="35">
+      <c r="D181" s="34">
         <f>'HOLERITE AGO.26'!I26</f>
         <v/>
       </c>
@@ -8073,7 +8271,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D182" s="35">
+      <c r="D182" s="34">
         <f>'HOLERITE AGO.26'!I27</f>
         <v/>
       </c>
@@ -8095,7 +8293,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D183" s="35">
+      <c r="D183" s="34">
         <f>'HOLERITE AGO.26'!I28</f>
         <v/>
       </c>
@@ -8117,7 +8315,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D184" s="35">
+      <c r="D184" s="34">
         <f>'HOLERITE AGO.26'!I29</f>
         <v/>
       </c>
@@ -8139,7 +8337,7 @@
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D185" s="35">
+      <c r="D185" s="34">
         <f>'HOLERITE AGO.26'!I30</f>
         <v/>
       </c>
@@ -8260,7 +8458,7 @@
           <t>Salário base</t>
         </is>
       </c>
-      <c r="C7" s="35">
+      <c r="C7" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8271,7 +8469,7 @@
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C8" s="35">
+      <c r="C8" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$7:$I$7,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8282,7 +8480,7 @@
           <t>Horas extras</t>
         </is>
       </c>
-      <c r="C9" s="35">
+      <c r="C9" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$8:$I$8,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8293,7 +8491,7 @@
           <t>Comissão sobre vendas</t>
         </is>
       </c>
-      <c r="C10" s="35">
+      <c r="C10" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$11:$I$11,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8304,7 +8502,7 @@
           <t>Repouso remunerado / DSR</t>
         </is>
       </c>
-      <c r="C11" s="35">
+      <c r="C11" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$12:$I$12,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8315,7 +8513,7 @@
           <t>Auxílio gerência</t>
         </is>
       </c>
-      <c r="C12" s="35">
+      <c r="C12" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$13:$I$13,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8326,7 +8524,7 @@
           <t>Adicional prêmio meta caixa</t>
         </is>
       </c>
-      <c r="C13" s="35">
+      <c r="C13" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$14:$I$14,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8337,7 +8535,7 @@
           <t>Prêmio cota geral</t>
         </is>
       </c>
-      <c r="C14" s="35">
+      <c r="C14" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$15:$I$15,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8348,7 +8546,7 @@
           <t>Prêmio pré-vencidos</t>
         </is>
       </c>
-      <c r="C15" s="35">
+      <c r="C15" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$16:$I$16,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8359,7 +8557,7 @@
           <t>Férias</t>
         </is>
       </c>
-      <c r="C16" s="35">
+      <c r="C16" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$17:$I$17,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8370,7 +8568,7 @@
           <t>1/3 constitucional de férias</t>
         </is>
       </c>
-      <c r="C17" s="35">
+      <c r="C17" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$18:$I$18,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8381,7 +8579,7 @@
           <t>Incentivo aplicações</t>
         </is>
       </c>
-      <c r="C18" s="35">
+      <c r="C18" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$19:$I$19,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8392,7 +8590,7 @@
           <t>Incentivo vitaminas</t>
         </is>
       </c>
-      <c r="C19" s="35">
+      <c r="C19" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$20:$I$20,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8403,7 +8601,7 @@
           <t>Outros incentivos</t>
         </is>
       </c>
-      <c r="C20" s="35">
+      <c r="C20" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$21:$I$21,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8434,7 +8632,7 @@
           <t>Adiantamento / vales</t>
         </is>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$24:$I$24,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8445,7 +8643,7 @@
           <t>Adiantamento de incentivos e aplicações</t>
         </is>
       </c>
-      <c r="C24" s="35">
+      <c r="C24" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$25:$I$25,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8456,7 +8654,7 @@
           <t>Convênio</t>
         </is>
       </c>
-      <c r="C25" s="35">
+      <c r="C25" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$26:$I$26,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8467,7 +8665,7 @@
           <t>Faltas / atrasos</t>
         </is>
       </c>
-      <c r="C26" s="35">
+      <c r="C26" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$27:$I$27,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8478,7 +8676,7 @@
           <t>Vale transporte 6%</t>
         </is>
       </c>
-      <c r="C27" s="35">
+      <c r="C27" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$28:$I$28,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8489,7 +8687,7 @@
           <t>INSS</t>
         </is>
       </c>
-      <c r="C28" s="35">
+      <c r="C28" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$29:$I$29,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8500,7 +8698,7 @@
           <t>IRRF</t>
         </is>
       </c>
-      <c r="C29" s="35">
+      <c r="C29" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$30:$I$30,1,MATCH($C$4,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
@@ -8549,7 +8747,7 @@
           <t>Venda bruta</t>
         </is>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="34">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$C$5:$C$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
         <v/>
       </c>
@@ -8560,7 +8758,7 @@
           <t>Descontos concedidos</t>
         </is>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="34">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$D$5:$D$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
         <v/>
       </c>
@@ -8571,7 +8769,7 @@
           <t>Venda líquida</t>
         </is>
       </c>
-      <c r="C37" s="35">
+      <c r="C37" s="34">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$E$5:$E$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
         <v/>
       </c>
@@ -8582,7 +8780,7 @@
           <t>Comissão apurada</t>
         </is>
       </c>
-      <c r="C38" s="35">
+      <c r="C38" s="34">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$F$5:$F$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
         <v/>
       </c>
@@ -8593,7 +8791,7 @@
           <t>Total de incentivos</t>
         </is>
       </c>
-      <c r="C39" s="35">
+      <c r="C39" s="34">
         <f>IFERROR(INDEX('BASE INOVAFARMA AGO.26'!$J$5:$J$12,MATCH($C$4,'BASE INOVAFARMA AGO.26'!$B$5:$B$12,0)),0)</f>
         <v/>
       </c>
@@ -8639,4 +8837,661 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup fitToHeight="1" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="62" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="26" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>APONTAMENTO DO PONTO — AGOSTO/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="18" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Horas extras, adicional noturno e feriado trabalhado · alimenta as rubricas da aba HOLERITE AGO.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="26" customHeight="1">
+      <c r="A4" s="13" t="inlineStr">
+        <is>
+          <t>FUNCIONÁRIO</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>OCORRÊNCIA</t>
+        </is>
+      </c>
+      <c r="C4" s="13" t="inlineStr">
+        <is>
+          <t>QTDE</t>
+        </is>
+      </c>
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>UNIDADE</t>
+        </is>
+      </c>
+      <c r="E4" s="13" t="inlineStr">
+        <is>
+          <t>SALÁRIO BASE</t>
+        </is>
+      </c>
+      <c r="F4" s="13" t="inlineStr">
+        <is>
+          <t>VALOR UNITÁRIO</t>
+        </is>
+      </c>
+      <c r="G4" s="13" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="H4" s="13" t="inlineStr">
+        <is>
+          <t>RUBRICA DESTINO</t>
+        </is>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>OBSERVAÇÃO</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>EDEY</t>
+        </is>
+      </c>
+      <c r="B5" s="30" t="inlineStr">
+        <is>
+          <t>Horas extras 50%</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="E5" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A5,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F5" s="35">
+        <f>ROUND(E5/PARÂMETROS!$B$20*(1+PARÂMETROS!$B$21),4)</f>
+        <v/>
+      </c>
+      <c r="G5" s="20">
+        <f>ROUND(C5*F5,2)</f>
+        <v/>
+      </c>
+      <c r="H5" s="53" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I5" s="33" t="inlineStr">
+        <is>
+          <t>24 horas extras normais em agosto/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="inlineStr">
+        <is>
+          <t>EDEY</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr">
+        <is>
+          <t>Adicional noturno (valor fixo)</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>valor</t>
+        </is>
+      </c>
+      <c r="E6" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A6,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>350</v>
+      </c>
+      <c r="G6" s="20">
+        <f>ROUND(C6*F6,2)</f>
+        <v/>
+      </c>
+      <c r="H6" s="53" t="inlineStr">
+        <is>
+          <t>ADICIONAL NOTURNO</t>
+        </is>
+      </c>
+      <c r="I6" s="33" t="inlineStr">
+        <is>
+          <t>Adicional noturno lançado como valor fixo desde jul/26 — CONFERIR com o apontamento do ponto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="inlineStr">
+        <is>
+          <t>NATI</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="E7" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A7,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F7" s="35">
+        <f>ROUND(E7/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
+        <v/>
+      </c>
+      <c r="G7" s="20">
+        <f>ROUND(C7*F7,2)</f>
+        <v/>
+      </c>
+      <c r="H7" s="53" t="inlineStr">
+        <is>
+          <t>ADICIONAL NOTURNO</t>
+        </is>
+      </c>
+      <c r="I7" s="33" t="inlineStr">
+        <is>
+          <t>17 horas noturnas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="inlineStr">
+        <is>
+          <t>NATI</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>Feriado trabalhado (dobra)</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
+      <c r="E8" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A8,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F8" s="35">
+        <f>ROUND(E8/PARÂMETROS!$B$23,2)</f>
+        <v/>
+      </c>
+      <c r="G8" s="20">
+        <f>ROUND(C8*F8,2)</f>
+        <v/>
+      </c>
+      <c r="H8" s="53" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I8" s="33" t="inlineStr">
+        <is>
+          <t>Feriado de 15/08/2026 trabalhado, sem folga compensatória — pago em dobro (1 dia a mais).</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="inlineStr">
+        <is>
+          <t>CAMILA</t>
+        </is>
+      </c>
+      <c r="B9" s="30" t="inlineStr">
+        <is>
+          <t>Feriado trabalhado (dobra)</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
+      <c r="E9" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A9,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F9" s="35">
+        <f>ROUND(E9/PARÂMETROS!$B$23,2)</f>
+        <v/>
+      </c>
+      <c r="G9" s="20">
+        <f>ROUND(C9*F9,2)</f>
+        <v/>
+      </c>
+      <c r="H9" s="53" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I9" s="33" t="inlineStr">
+        <is>
+          <t>Dia 15/08/2026 (feriado) trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
+          <t>SARA</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="inlineStr">
+        <is>
+          <t>Feriado trabalhado (dobra)</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
+      <c r="E10" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A10,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F10" s="35">
+        <f>ROUND(E10/PARÂMETROS!$B$23,2)</f>
+        <v/>
+      </c>
+      <c r="G10" s="20">
+        <f>ROUND(C10*F10,2)</f>
+        <v/>
+      </c>
+      <c r="H10" s="53" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I10" s="33" t="inlineStr">
+        <is>
+          <t>Dia 15/08/2026 (feriado) trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>VALÉRIA</t>
+        </is>
+      </c>
+      <c r="B11" s="30" t="inlineStr">
+        <is>
+          <t>Feriado trabalhado (dobra)</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
+      <c r="E11" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A11,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F11" s="35">
+        <f>ROUND(E11/PARÂMETROS!$B$23,2)</f>
+        <v/>
+      </c>
+      <c r="G11" s="20">
+        <f>ROUND(C11*F11,2)</f>
+        <v/>
+      </c>
+      <c r="H11" s="53" t="inlineStr">
+        <is>
+          <t>HORAS EXTRAS</t>
+        </is>
+      </c>
+      <c r="I11" s="33" t="inlineStr">
+        <is>
+          <t>Dia 15/08/2026 (feriado) trabalhado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
+          <t>VALÉRIA</t>
+        </is>
+      </c>
+      <c r="B12" s="30" t="inlineStr">
+        <is>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="n"/>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="E12" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A12,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F12" s="35">
+        <f>ROUND(E12/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
+        <v/>
+      </c>
+      <c r="G12" s="20">
+        <f>ROUND(C12*F12,2)</f>
+        <v/>
+      </c>
+      <c r="H12" s="53" t="inlineStr">
+        <is>
+          <t>ADICIONAL NOTURNO</t>
+        </is>
+      </c>
+      <c r="I12" s="33" t="inlineStr">
+        <is>
+          <t>2 madrugadas trabalhadas, com folga normal no dia seguinte — cabe só o adicional noturno. INFORMAR o total de horas noturnas das 2 madrugadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="inlineStr">
+        <is>
+          <t>AGNOR</t>
+        </is>
+      </c>
+      <c r="B13" s="30" t="inlineStr">
+        <is>
+          <t>Adicional noturno</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="14" t="inlineStr">
+        <is>
+          <t>horas</t>
+        </is>
+      </c>
+      <c r="E13" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A13,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F13" s="35">
+        <f>ROUND(E13/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
+        <v/>
+      </c>
+      <c r="G13" s="20">
+        <f>ROUND(C13*F13,2)</f>
+        <v/>
+      </c>
+      <c r="H13" s="53" t="inlineStr">
+        <is>
+          <t>ADICIONAL NOTURNO</t>
+        </is>
+      </c>
+      <c r="I13" s="33" t="inlineStr">
+        <is>
+          <t>3 madrugadas trabalhadas, com folga normal — cabe só o adicional noturno. INFORMAR o total de horas noturnas das 3 madrugadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="inlineStr">
+        <is>
+          <t>DEAN</t>
+        </is>
+      </c>
+      <c r="B14" s="30" t="inlineStr">
+        <is>
+          <t>Feriado com folga compensatória</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
+      <c r="E14" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A14,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F14" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="20">
+        <f>ROUND(C14*F14,2)</f>
+        <v/>
+      </c>
+      <c r="H14" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I14" s="33" t="inlineStr">
+        <is>
+          <t>Dia 15/08/2026 trabalhado, com folga compensatória — nada a pagar, registro apenas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="54" t="n"/>
+      <c r="B15" s="54" t="n"/>
+      <c r="C15" s="54" t="n"/>
+      <c r="D15" s="54" t="n"/>
+      <c r="E15" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A15,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F15" s="36" t="n"/>
+      <c r="G15" s="20">
+        <f>ROUND(C15*F15,2)</f>
+        <v/>
+      </c>
+      <c r="H15" s="54" t="n"/>
+      <c r="I15" s="54" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="54" t="n"/>
+      <c r="B16" s="54" t="n"/>
+      <c r="C16" s="54" t="n"/>
+      <c r="D16" s="54" t="n"/>
+      <c r="E16" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A16,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F16" s="36" t="n"/>
+      <c r="G16" s="20">
+        <f>ROUND(C16*F16,2)</f>
+        <v/>
+      </c>
+      <c r="H16" s="54" t="n"/>
+      <c r="I16" s="54" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="54" t="n"/>
+      <c r="B17" s="54" t="n"/>
+      <c r="C17" s="54" t="n"/>
+      <c r="D17" s="54" t="n"/>
+      <c r="E17" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A17,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F17" s="36" t="n"/>
+      <c r="G17" s="20">
+        <f>ROUND(C17*F17,2)</f>
+        <v/>
+      </c>
+      <c r="H17" s="54" t="n"/>
+      <c r="I17" s="54" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="54" t="n"/>
+      <c r="B18" s="54" t="n"/>
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A18,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F18" s="36" t="n"/>
+      <c r="G18" s="20">
+        <f>ROUND(C18*F18,2)</f>
+        <v/>
+      </c>
+      <c r="H18" s="54" t="n"/>
+      <c r="I18" s="54" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="54" t="n"/>
+      <c r="B19" s="54" t="n"/>
+      <c r="C19" s="54" t="n"/>
+      <c r="D19" s="54" t="n"/>
+      <c r="E19" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A19,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F19" s="36" t="n"/>
+      <c r="G19" s="20">
+        <f>ROUND(C19*F19,2)</f>
+        <v/>
+      </c>
+      <c r="H19" s="54" t="n"/>
+      <c r="I19" s="54" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="54" t="n"/>
+      <c r="B20" s="54" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A20,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F20" s="36" t="n"/>
+      <c r="G20" s="20">
+        <f>ROUND(C20*F20,2)</f>
+        <v/>
+      </c>
+      <c r="H20" s="54" t="n"/>
+      <c r="I20" s="54" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="19" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="18" t="n"/>
+      <c r="G21" s="20">
+        <f>SUM(G5:G20)</f>
+        <v/>
+      </c>
+      <c r="H21" s="18" t="n"/>
+      <c r="I21" s="18" t="n"/>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="10" t="inlineStr">
+        <is>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Confira: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 no salário de R$ 1.621,00 — é a mesma conta usada na planilha de julho.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>As linhas em branco no fim da tabela são para acrescentar outras ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE AGO.26 — não digite nada por cima lá.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I20"/>
+  <mergeCells count="6">
+    <mergeCell ref="A25:I25"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A26:I26"/>
+    <mergeCell ref="A24:I24"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -857,7 +857,7 @@
       <c r="A25" s="4" t="inlineStr"/>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>VALÉRIA: 2 madrugadas com folga no dia seguinte — cabe só o adicional noturno; falta informar as horas.</t>
+          <t>VALÉRIA: 2 madrugadas de 8 horas (16 h) com folga no dia seguinte → R$ 23,58 de adicional noturno.</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       <c r="A26" s="4" t="inlineStr"/>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>AGNOR: 3 madrugadas com folga — cabe só o adicional noturno; falta informar as horas.</t>
+          <t>AGNOR: 3 madrugadas de 8 horas (24 h) com folga → R$ 35,37 de adicional noturno.</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>VALÉRIA e AGNOR: informar na aba PONTO AGO.26 quantas horas noturnas tiveram as madrugadas trabalhadas (2 e 3 madrugadas).</t>
+          <t>VALÉRIA e AGNOR: as madrugadas entraram como 8 horas cada (jornada normal com intervalo). Se só parte dessas horas ficou entre 22h e 5h, ajustar a quantidade na aba PONTO AGO.26.</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="C18" s="10" t="inlineStr">
         <is>
-          <t>Conforme jul/2026 — conferir apontamento do ponto.</t>
+          <t>Referência de jul/2026. O valor efetivo é lançado na aba PONTO AGO.26 — conferir com o apontamento.</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
         <v/>
       </c>
       <c r="K12" s="33">
-        <f> (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026 (fator na aba PARÂMETROS).</f>
+        <f> (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026 (fator na aba PARÂMETROS). A linha HORAS EXTRAS inclui o feriado trabalhado vindo da aba PONTO AGO.26.</f>
         <v/>
       </c>
     </row>
@@ -9224,7 +9224,9 @@
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
           <t>horas</t>
@@ -9249,7 +9251,7 @@
       </c>
       <c r="I12" s="33" t="inlineStr">
         <is>
-          <t>2 madrugadas trabalhadas, com folga normal no dia seguinte — cabe só o adicional noturno. INFORMAR o total de horas noturnas das 2 madrugadas.</t>
+          <t>2 madrugadas de jornada normal de 8 horas com intervalo (2 × 8 = 16 h), com folga normal no dia seguinte — cabe só o adicional noturno.</t>
         </is>
       </c>
     </row>
@@ -9264,7 +9266,9 @@
           <t>Adicional noturno</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>24</v>
+      </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
           <t>horas</t>
@@ -9289,7 +9293,7 @@
       </c>
       <c r="I13" s="33" t="inlineStr">
         <is>
-          <t>3 madrugadas trabalhadas, com folga normal — cabe só o adicional noturno. INFORMAR o total de horas noturnas das 3 madrugadas.</t>
+          <t>3 madrugadas de jornada normal de 8 horas com intervalo (3 × 8 = 24 h), com folga normal — cabe só o adicional noturno.</t>
         </is>
       </c>
     </row>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$187</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO AGO.26'!$A$4:$I$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'PONTO AGO.26'!$A$4:$I$21</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -841,7 +841,7 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NATI: 17 horas noturnas → R$ 25,05 de adicional; e o feriado de 15/08 trabalhado sem folga → R$ 54,03.</t>
+          <t>NATI: 17 horas extras noturnas → R$ 187,89 de hora extra mais R$ 25,05 de adicional noturno; e o feriado de 15/08 trabalhado sem folga → R$ 54,03.</t>
         </is>
       </c>
     </row>
@@ -2217,35 +2217,35 @@
         </is>
       </c>
       <c r="B7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,B$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,B$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="C7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,C$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,C$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="D7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,D$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,D$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="E7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,E$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,E$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="F7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,F$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,F$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="G7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,G$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,G$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="H7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,H$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,H$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="I7" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,I$4,'PONTO AGO.26'!$H$5:$H$20,"ADICIONAL NOTURNO")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,I$4,'PONTO AGO.26'!$H$5:$H$21,"ADICIONAL NOTURNO")</f>
         <v/>
       </c>
       <c r="J7" s="32">
@@ -2265,35 +2265,35 @@
         </is>
       </c>
       <c r="B8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,B$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,B$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="C8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,C$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,C$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="D8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,D$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,D$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="E8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,E$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,E$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="F8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,F$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,F$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="G8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,G$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,G$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="H8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,H$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,H$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="I8" s="34">
-        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$20,'PONTO AGO.26'!$A$5:$A$20,I$4,'PONTO AGO.26'!$H$5:$H$20,"HORAS EXTRAS")</f>
+        <f>SUMIFS('PONTO AGO.26'!$G$5:$G$21,'PONTO AGO.26'!$A$5:$A$21,I$4,'PONTO AGO.26'!$H$5:$H$21,"HORAS EXTRAS")</f>
         <v/>
       </c>
       <c r="J8" s="20">
@@ -2383,9 +2383,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15">
-        <f> COMISSÃO TOTAL</f>
-        <v/>
+      <c r="A11" s="15" t="inlineStr">
+        <is>
+          <t>COMISSÃO TOTAL (soma)</t>
+        </is>
       </c>
       <c r="B11" s="20">
         <f>SUM(B9:B10)</f>
@@ -2471,9 +2472,10 @@
         <f>SUM(B12:I12)</f>
         <v/>
       </c>
-      <c r="K12" s="33">
-        <f> (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026 (fator na aba PARÂMETROS). A linha HORAS EXTRAS inclui o feriado trabalhado vindo da aba PONTO AGO.26.</f>
-        <v/>
+      <c r="K12" s="33" t="inlineStr">
+        <is>
+          <t>Cálculo: (comissão total + horas extras) × 5 domingos ÷ 26 dias úteis de agosto/2026 (fator na aba PARÂMETROS). A linha HORAS EXTRAS inclui o feriado trabalhado vindo da aba PONTO AGO.26.</t>
+        </is>
       </c>
     </row>
     <row r="13">
@@ -8845,7 +8847,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -9011,7 +9013,7 @@
       </c>
       <c r="B7" s="30" t="inlineStr">
         <is>
-          <t>Adicional noturno</t>
+          <t>Horas extras 50%</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
@@ -9027,7 +9029,7 @@
         <v/>
       </c>
       <c r="F7" s="35">
-        <f>ROUND(E7/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
+        <f>ROUND(E7/PARÂMETROS!$B$20*(1+PARÂMETROS!$B$21),4)</f>
         <v/>
       </c>
       <c r="G7" s="20">
@@ -9036,12 +9038,12 @@
       </c>
       <c r="H7" s="53" t="inlineStr">
         <is>
-          <t>ADICIONAL NOTURNO</t>
+          <t>HORAS EXTRAS</t>
         </is>
       </c>
       <c r="I7" s="33" t="inlineStr">
         <is>
-          <t>17 horas noturnas.</t>
+          <t>17 horas extras noturnas — parcela de hora extra (50%).</t>
         </is>
       </c>
     </row>
@@ -9053,15 +9055,15 @@
       </c>
       <c r="B8" s="30" t="inlineStr">
         <is>
-          <t>Feriado trabalhado (dobra)</t>
+          <t>Adicional noturno</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>dias</t>
+          <t>horas</t>
         </is>
       </c>
       <c r="E8" s="34">
@@ -9069,7 +9071,7 @@
         <v/>
       </c>
       <c r="F8" s="35">
-        <f>ROUND(E8/PARÂMETROS!$B$23,2)</f>
+        <f>ROUND(E8/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
         <v/>
       </c>
       <c r="G8" s="20">
@@ -9078,19 +9080,19 @@
       </c>
       <c r="H8" s="53" t="inlineStr">
         <is>
-          <t>HORAS EXTRAS</t>
+          <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
       <c r="I8" s="33" t="inlineStr">
         <is>
-          <t>Feriado de 15/08/2026 trabalhado, sem folga compensatória — pago em dobro (1 dia a mais).</t>
+          <t>17 horas extras noturnas — parcela do adicional noturno (20%).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>CAMILA</t>
+          <t>NATI</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
@@ -9125,14 +9127,14 @@
       </c>
       <c r="I9" s="33" t="inlineStr">
         <is>
-          <t>Dia 15/08/2026 (feriado) trabalhado.</t>
+          <t>Feriado de 15/08/2026 trabalhado, sem folga compensatória — pago em dobro (1 dia a mais).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>SARA</t>
+          <t>CAMILA</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -9174,7 +9176,7 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>VALÉRIA</t>
+          <t>SARA</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
@@ -9221,15 +9223,15 @@
       </c>
       <c r="B12" s="30" t="inlineStr">
         <is>
-          <t>Adicional noturno</t>
+          <t>Feriado trabalhado (dobra)</t>
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="D12" s="14" t="inlineStr">
         <is>
-          <t>horas</t>
+          <t>dias</t>
         </is>
       </c>
       <c r="E12" s="34">
@@ -9237,7 +9239,7 @@
         <v/>
       </c>
       <c r="F12" s="35">
-        <f>ROUND(E12/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
+        <f>ROUND(E12/PARÂMETROS!$B$23,2)</f>
         <v/>
       </c>
       <c r="G12" s="20">
@@ -9246,19 +9248,19 @@
       </c>
       <c r="H12" s="53" t="inlineStr">
         <is>
-          <t>ADICIONAL NOTURNO</t>
+          <t>HORAS EXTRAS</t>
         </is>
       </c>
       <c r="I12" s="33" t="inlineStr">
         <is>
-          <t>2 madrugadas de jornada normal de 8 horas com intervalo (2 × 8 = 16 h), com folga normal no dia seguinte — cabe só o adicional noturno.</t>
+          <t>Dia 15/08/2026 (feriado) trabalhado.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>AGNOR</t>
+          <t>VALÉRIA</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -9267,7 +9269,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="D13" s="14" t="inlineStr">
         <is>
@@ -9293,35 +9295,36 @@
       </c>
       <c r="I13" s="33" t="inlineStr">
         <is>
-          <t>3 madrugadas de jornada normal de 8 horas com intervalo (3 × 8 = 24 h), com folga normal — cabe só o adicional noturno.</t>
+          <t>2 madrugadas de jornada normal de 8 horas com intervalo (2 × 8 = 16 h), com folga normal no dia seguinte — cabe só o adicional noturno.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
-          <t>DEAN</t>
+          <t>AGNOR</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
         <is>
-          <t>Feriado com folga compensatória</t>
+          <t>Adicional noturno</t>
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="D14" s="14" t="inlineStr">
         <is>
-          <t>dias</t>
+          <t>horas</t>
         </is>
       </c>
       <c r="E14" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A14,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F14" s="35" t="n">
-        <v>0</v>
+      <c r="F14" s="35">
+        <f>ROUND(E14/PARÂMETROS!$B$20*PARÂMETROS!$B$22,4)</f>
+        <v/>
       </c>
       <c r="G14" s="20">
         <f>ROUND(C14*F14,2)</f>
@@ -9329,31 +9332,55 @@
       </c>
       <c r="H14" s="53" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ADICIONAL NOTURNO</t>
         </is>
       </c>
       <c r="I14" s="33" t="inlineStr">
         <is>
-          <t>Dia 15/08/2026 trabalhado, com folga compensatória — nada a pagar, registro apenas.</t>
+          <t>3 madrugadas de jornada normal de 8 horas com intervalo (3 × 8 = 24 h), com folga normal — cabe só o adicional noturno.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="54" t="n"/>
-      <c r="B15" s="54" t="n"/>
-      <c r="C15" s="54" t="n"/>
-      <c r="D15" s="54" t="n"/>
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>DEAN</t>
+        </is>
+      </c>
+      <c r="B15" s="30" t="inlineStr">
+        <is>
+          <t>Feriado com folga compensatória</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D15" s="14" t="inlineStr">
+        <is>
+          <t>dias</t>
+        </is>
+      </c>
       <c r="E15" s="34">
         <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A15,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
         <v/>
       </c>
-      <c r="F15" s="36" t="n"/>
+      <c r="F15" s="35" t="n">
+        <v>0</v>
+      </c>
       <c r="G15" s="20">
         <f>ROUND(C15*F15,2)</f>
         <v/>
       </c>
-      <c r="H15" s="54" t="n"/>
-      <c r="I15" s="54" t="n"/>
+      <c r="H15" s="53" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I15" s="33" t="inlineStr">
+        <is>
+          <t>Dia 15/08/2026 trabalhado, com folga compensatória — nada a pagar, registro apenas.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="54" t="n"/>
@@ -9441,58 +9468,75 @@
       <c r="I20" s="54" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="18" t="n"/>
-      <c r="B21" s="19" t="inlineStr">
+      <c r="A21" s="54" t="n"/>
+      <c r="B21" s="54" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="34">
+        <f>IFERROR(INDEX('HOLERITE AGO.26'!$B$6:$I$6,1,MATCH(A21,'HOLERITE AGO.26'!$B$4:$I$4,0)),0)</f>
+        <v/>
+      </c>
+      <c r="F21" s="36" t="n"/>
+      <c r="G21" s="20">
+        <f>ROUND(C21*F21,2)</f>
+        <v/>
+      </c>
+      <c r="H21" s="54" t="n"/>
+      <c r="I21" s="54" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="19" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
-      <c r="D21" s="18" t="n"/>
-      <c r="E21" s="18" t="n"/>
-      <c r="F21" s="18" t="n"/>
-      <c r="G21" s="20">
-        <f>SUM(G5:G20)</f>
-        <v/>
-      </c>
-      <c r="H21" s="18" t="n"/>
-      <c r="I21" s="18" t="n"/>
-    </row>
-    <row r="23" ht="24" customHeight="1">
-      <c r="A23" s="10" t="inlineStr">
-        <is>
-          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
-        </is>
-      </c>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="18" t="n"/>
+      <c r="G22" s="20">
+        <f>SUM(G5:G21)</f>
+        <v/>
+      </c>
+      <c r="H22" s="18" t="n"/>
+      <c r="I22" s="18" t="n"/>
     </row>
     <row r="24" ht="24" customHeight="1">
       <c r="A24" s="10" t="inlineStr">
         <is>
-          <t>Confira: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 no salário de R$ 1.621,00 — é a mesma conta usada na planilha de julho.</t>
+          <t>Salário-hora = salário base ÷ 220. Hora extra = salário-hora × 1,5. Adicional noturno = salário-hora × 20%. Feriado trabalhado sem folga = 1 salário-dia a mais (salário base ÷ 30).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1">
       <c r="A25" s="10" t="inlineStr">
         <is>
-          <t>As linhas em branco no fim da tabela são para acrescentar outras ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+          <t>Confira: 40 horas extras dão R$ 442,09 e 24 horas dão R$ 265,25 no salário de R$ 1.621,00 — é a mesma conta usada na planilha de julho.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="A26" s="10" t="inlineStr">
         <is>
+          <t>As linhas em branco no fim da tabela são para acrescentar outras ocorrências: preencha funcionário, ocorrência, quantidade, valor unitário e a rubrica de destino (HORAS EXTRAS ou ADICIONAL NOTURNO).</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
           <t>Os totais desta aba entram sozinhos nas linhas HORAS EXTRAS e ADICIONAL NOTURNO da aba HOLERITE AGO.26 — não digite nada por cima lá.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I20"/>
+  <autoFilter ref="A4:I21"/>
   <mergeCells count="6">
     <mergeCell ref="A25:I25"/>
     <mergeCell ref="A2:I2"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A23:I23"/>
+    <mergeCell ref="A27:I27"/>
     <mergeCell ref="A26:I26"/>
     <mergeCell ref="A24:I24"/>
   </mergeCells>

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$K$36</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$K$37</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$187</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
@@ -2066,7 +2066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K42"/>
+  <dimension ref="A1:K43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2842,7 +2842,7 @@
     <row r="24">
       <c r="A24" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="B24" s="36" t="n"/>
@@ -3211,70 +3211,94 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr"/>
+    <row r="37">
+      <c r="A37" s="30" t="inlineStr">
+        <is>
+          <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
+        </is>
+      </c>
+      <c r="B37" s="31" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
+      <c r="H37" s="31" t="n"/>
+      <c r="I37" s="31" t="n"/>
+      <c r="J37" s="32">
+        <f>SUM(B37:I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="33" t="inlineStr">
+        <is>
+          <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. JOEL: férias de 01 a 31/08/2026, pagas no início de agosto — informar o valor.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="inlineStr">
         <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula laranja</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B42" s="7" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K36"/>
+  <autoFilter ref="A4:K37"/>
   <mergeCells count="7">
     <mergeCell ref="B41:K41"/>
     <mergeCell ref="B40:K40"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B43:K43"/>
     <mergeCell ref="B39:K39"/>
-    <mergeCell ref="B38:K38"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -4811,7 +4835,7 @@
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C18" s="30" t="inlineStr">
@@ -5295,7 +5319,7 @@
       </c>
       <c r="B41" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C41" s="30" t="inlineStr">
@@ -5779,7 +5803,7 @@
       </c>
       <c r="B64" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C64" s="30" t="inlineStr">
@@ -6263,7 +6287,7 @@
       </c>
       <c r="B87" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C87" s="30" t="inlineStr">
@@ -6747,7 +6771,7 @@
       </c>
       <c r="B110" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C110" s="30" t="inlineStr">
@@ -7231,7 +7255,7 @@
       </c>
       <c r="B133" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C133" s="30" t="inlineStr">
@@ -7715,7 +7739,7 @@
       </c>
       <c r="B156" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C156" s="30" t="inlineStr">
@@ -8199,7 +8223,7 @@
       </c>
       <c r="B179" s="30" t="inlineStr">
         <is>
-          <t>ADIANTAMENTO / VALES</t>
+          <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
       <c r="C179" s="30" t="inlineStr">

--- a/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
+++ b/relatorios/contabilidade/RELATORIO_HOLERITE_AGOSTO_2026_pgto_05-09-2026.xlsx
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'BASE INOVAFARMA AGO.26'!$A$4:$J$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$K$37</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'HOLERITE AGO.26'!$A$4:$K$39</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'JULHO.26 REVISADO'!$A$4:$K$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'LISTA CONTABILIDADE'!$A$4:$E$187</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'GANHOS DO COLABORADOR'!$A$1:$D$45</definedName>
@@ -672,7 +672,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B56"/>
+  <dimension ref="A1:B62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -825,7 +825,7 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>APONTAMENTO DE AGOSTO/2026 (aba PONTO AGO.26)</t>
+          <t>CONFERÊNCIA COM O HOLERITE DA BETEL CONTABILIDADE</t>
         </is>
       </c>
     </row>
@@ -833,7 +833,7 @@
       <c r="A22" s="4" t="inlineStr"/>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>EDEY: 24 horas extras normais → R$ 265,25.</t>
+          <t>Os valores de prêmios, vales, vale-transporte, INSS e IRRF foram lidos do demonstrativo de agosto/2026 emitido pela Betel e lançados nas linhas correspondentes.</t>
         </is>
       </c>
     </row>
@@ -841,46 +841,58 @@
       <c r="A23" s="4" t="inlineStr"/>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>NATI: 17 horas extras noturnas → R$ 187,89 de hora extra mais R$ 25,05 de adicional noturno; e o feriado de 15/08 trabalhado sem folga → R$ 54,03.</t>
+          <t>A linha DIFERENÇA (planilha − holerite) fecha em zero para todos, exceto JOEL — ver as pendências abaixo.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" s="4" t="inlineStr"/>
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>CAMILA, SARA e VALÉRIA: dia 15/08 (feriado) trabalhado → R$ 54,03 cada.</t>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>DSR EM DUPLICIDADE: a rubrica 420 (Repouso Remunerado) já foi calculada sobre comissão + horas extras, e a Betel ainda lançou a rubrica 057 (DSR/hora extra). São R$ 51,01 do EDEY, R$ 46,51 da NATI e R$ 10,38 de VALÉRIA, SARA e CAMILA — R$ 128,66 na loja. Confirmar com a contabilidade.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" s="4" t="inlineStr"/>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>VALÉRIA: 2 madrugadas de 8 horas (16 h) com folga no dia seguinte → R$ 23,58 de adicional noturno.</t>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>JOEL: a comissão de R$ 103,31 (dias 01 e 02/08) e o DSR não entraram no holerite dele — só saiu o salário família. Verificar se entra em folha complementar ou no recibo de férias.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="4" t="inlineStr"/>
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>AGNOR: 3 madrugadas de 8 horas (24 h) com folga → R$ 35,37 de adicional noturno.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="4" t="inlineStr"/>
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>DEAN: dia 15/08 trabalhado com folga compensatória — nada a pagar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>JÁ DEFINIDO PELA EMPRESA</t>
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="inlineStr">
+        <is>
+          <t>Os incentivos de aplicações e vitaminas não constam no holerite: são pagos em dinheiro durante o mês. Por isso entram aqui como provento e como desconto, sem afetar o líquido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>APONTAMENTO DE AGOSTO/2026 (aba PONTO AGO.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="4" t="inlineStr"/>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>EDEY: 24 horas extras normais → R$ 265,25.</t>
         </is>
       </c>
     </row>
@@ -888,7 +900,7 @@
       <c r="A29" s="4" t="inlineStr"/>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>AGNOR: mantida a comissão fixa de R$ 2.000,00 — a linha COMPLEMENTO / COMISSÃO PDV calcula sozinha a diferença (R$ 1.090,49) sobre o apurado de R$ 909,51.</t>
+          <t>NATI: 17 horas extras noturnas → R$ 187,89 de hora extra mais R$ 25,05 de adicional noturno; e o feriado de 15/08 trabalhado sem folga → R$ 54,03.</t>
         </is>
       </c>
     </row>
@@ -896,7 +908,7 @@
       <c r="A30" s="4" t="inlineStr"/>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>JOEL: por acordo interno saiu em 04/08 e volta em 04/09, mas o recibo de férias saiu como 01 a 31/08 e já foi pago no início de agosto. Por isso ele tem comissão dos dias 01 e 02/08 (R$ 103,31) e fica sem salário e sem desconto de vale-transporte neste holerite; férias e 1/3 NÃO se repetem aqui.</t>
+          <t>CAMILA, SARA e VALÉRIA: dia 15/08 (feriado) trabalhado → R$ 54,03 cada.</t>
         </is>
       </c>
     </row>
@@ -904,7 +916,7 @@
       <c r="A31" s="4" t="inlineStr"/>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>CAMILA: contratada recentemente; agosto é o primeiro mês completo, com salário integral de R$ 1.621,00.</t>
+          <t>VALÉRIA: 2 madrugadas de 8 horas (16 h) com folga no dia seguinte → R$ 23,58 de adicional noturno.</t>
         </is>
       </c>
     </row>
@@ -912,7 +924,7 @@
       <c r="A32" s="4" t="inlineStr"/>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>SARA: a comissão dela na loja Centro (R$ 2,65) foi somada aqui, na linha COMPLEMENTO / COMISSÃO PDV.</t>
+          <t>AGNOR: 3 madrugadas de 8 horas (24 h) com folga → R$ 35,37 de adicional noturno.</t>
         </is>
       </c>
     </row>
@@ -920,86 +932,61 @@
       <c r="A33" s="4" t="inlineStr"/>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha (a apurada, R$ 975,65, aparece só na aba BASE). Os incentivos dele continuam sendo pagos normalmente.</t>
+          <t>DEAN: dia 15/08 trabalhado com folga compensatória — nada a pagar.</t>
         </is>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="3" t="inlineStr">
         <is>
+          <t>JÁ DEFINIDO PELA EMPRESA</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="4" t="inlineStr"/>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>AGNOR: mantida a comissão fixa de R$ 2.000,00 — a linha COMPLEMENTO / COMISSÃO PDV calcula sozinha a diferença (R$ 1.090,49) sobre o apurado de R$ 909,51.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="4" t="inlineStr"/>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>JOEL: por acordo interno saiu em 04/08 e volta em 04/09, mas o recibo de férias saiu como 01 a 31/08 e já foi pago no início de agosto. Por isso ele tem comissão dos dias 01 e 02/08 (R$ 103,31) e fica sem salário e sem desconto de vale-transporte neste holerite; férias e 1/3 NÃO se repetem aqui.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="4" t="inlineStr"/>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>CAMILA: contratada recentemente; agosto é o primeiro mês completo, com salário integral de R$ 1.621,00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="17" customHeight="1">
+      <c r="A38" s="4" t="inlineStr"/>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>SARA: a comissão dela na loja Centro (R$ 2,65) foi somada aqui, na linha COMPLEMENTO / COMISSÃO PDV.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="17" customHeight="1">
+      <c r="A39" s="4" t="inlineStr"/>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>DEAN: não recebe comissão sobre vendas — a rubrica fica zerada na folha (a apurada, R$ 975,65, aparece só na aba BASE). Os incentivos dele continuam sendo pagos normalmente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
           <t>PENDÊNCIAS — CONFIRMAR ANTES DE ENVIAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B35" s="6" t="inlineStr">
-        <is>
-          <t>VALÉRIA e AGNOR: as madrugadas entraram como 8 horas cada (jornada normal com intervalo). Se só parte dessas horas ficou entre 22h e 5h, ajustar a quantidade na aba PONTO AGO.26.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="inlineStr">
-        <is>
-          <t>EDEY: o adicional noturno está lançado como valor fixo de R$ 350,00 — conferir com o apontamento do ponto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B37" s="6" t="inlineStr">
-        <is>
-          <t>Confirmar o critério do feriado trabalhado: está sendo pago 1 salário-dia a mais (R$ 54,03) por feriado sem folga.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="inlineStr">
-        <is>
-          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B39" s="6" t="inlineStr">
-        <is>
-          <t>Vales adiantados, convênio e faltas de agosto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>•</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="inlineStr">
-        <is>
-          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
         </is>
       </c>
     </row>
@@ -1011,7 +998,7 @@
       </c>
       <c r="B41" s="6" t="inlineStr">
         <is>
-          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
+          <t>VALÉRIA e AGNOR: as madrugadas entraram como 8 horas cada (jornada normal com intervalo). Se só parte dessas horas ficou entre 22h e 5h, ajustar a quantidade na aba PONTO AGO.26.</t>
         </is>
       </c>
     </row>
@@ -1023,7 +1010,7 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+          <t>EDEY: o adicional noturno está lançado como valor fixo de R$ 350,00 — conferir com o apontamento do ponto.</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1022,7 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+          <t>Confirmar o critério do feriado trabalhado: está sendo pago 1 salário-dia a mais (R$ 54,03) por feriado sem folga.</t>
         </is>
       </c>
     </row>
@@ -1047,61 +1034,86 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
+          <t>Prêmio cota geral e prêmio pré-vencidos de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="inlineStr">
+        <is>
+          <t>Vales adiantados, convênio e faltas de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="17" customHeight="1">
+      <c r="A46" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="inlineStr">
+        <is>
+          <t>JOEL: confirmar se há algum desconto para agosto (convênio, vale ou adiantamento) — hoje o holerite dele fica só com a comissão de R$ 103,31 e o DSR.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="17" customHeight="1">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="inlineStr">
+        <is>
+          <t>JOEL: como o retorno é em 04/09, o vale-transporte de setembro deve ser proporcional e o holerite de setembro ainda pega os dias 01 a 03/09 de férias, já pagos no recibo de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="inlineStr">
+        <is>
+          <t>Comissões de PDV antigos, que em julho eram somadas à comissão do sistema.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="inlineStr">
+        <is>
+          <t>Desconto de vale-transporte: vem sendo lançado R$ 84,29; 6% do salário de R$ 1.621,00 seria R$ 97,26.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>•</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
           <t>DSR de julho/2026 foi calculado com o fator de agosto (5/26) em vez de 4/27 — ver aba JULHO.26 REVISADO e decidir se ajusta em setembro.</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="20" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+    <row r="51" ht="20" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>OBSERVAÇÃO TÉCNICA</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="17" customHeight="1">
-      <c r="A46" s="4" t="inlineStr"/>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1">
-      <c r="A47" s="3" t="inlineStr">
-        <is>
-          <t>ABAS DO ARQUIVO</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" s="4" t="inlineStr"/>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" s="4" t="inlineStr"/>
-      <c r="B49" s="5" t="inlineStr">
-        <is>
-          <t>PONTO AGO.26 — apontamento de horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="4" t="inlineStr"/>
-      <c r="B50" s="5" t="inlineStr">
-        <is>
-          <t>GANHOS DO COLABORADOR — escolha o nome na lista e saia o demonstrativo individual, pronto para imprimir/mandar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="4" t="inlineStr"/>
-      <c r="B51" s="5" t="inlineStr">
-        <is>
-          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
         </is>
       </c>
     </row>
@@ -1109,15 +1121,14 @@
       <c r="A52" s="4" t="inlineStr"/>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="4" t="inlineStr"/>
-      <c r="B53" s="5" t="inlineStr">
-        <is>
-          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+          <t>As células de total e de cálculo são fórmulas. Ao abrir o arquivo no Excel ou no Google Planilhas os valores aparecem calculados automaticamente; em visualizadores simples (prévia de celular, por exemplo) elas podem aparecer em branco até o arquivo ser aberto de fato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="20" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>ABAS DO ARQUIVO</t>
         </is>
       </c>
     </row>
@@ -1125,29 +1136,78 @@
       <c r="A54" s="4" t="inlineStr"/>
       <c r="B54" s="5" t="inlineStr">
         <is>
+          <t>HOLERITE AGO.26 — relatório principal da competência agosto/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="4" t="inlineStr"/>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>PONTO AGO.26 — apontamento de horas extras, adicional noturno e feriado trabalhado; alimenta o holerite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="17" customHeight="1">
+      <c r="A56" s="4" t="inlineStr"/>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>GANHOS DO COLABORADOR — escolha o nome na lista e saia o demonstrativo individual, pronto para imprimir/mandar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="17" customHeight="1">
+      <c r="A57" s="4" t="inlineStr"/>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>LISTA CONTABILIDADE — os mesmos lançamentos em formato de lista por funcionário.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" s="4" t="inlineStr"/>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>BASE INOVAFARMA AGO.26 — apuração de comissões e incentivos por vendedor.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" s="4" t="inlineStr"/>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>JULHO.26 REVISADO — a folha de julho reorganizada e conferida (valores pagos preservados).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="4" t="inlineStr"/>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
           <t>PARÂMETROS — calendário do mês, fator do DSR e valores fixos.</t>
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="B56" s="7" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="7" t="inlineStr">
         <is>
           <t>Documento gerado a partir da planilha CONISSÕES PLAN.AGOSTO/JULHO ARRAIAL 2026 e do relatório de comissões do InovaFarma.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="11">
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="A2:B2"/>
+    <mergeCell ref="A51:B51"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A45:B45"/>
-    <mergeCell ref="A47:B47"/>
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A53:B53"/>
     <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2066,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2845,21 +2905,31 @@
           <t>ADIANTAMENTO SALARIAL / VALES</t>
         </is>
       </c>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="36" t="n"/>
-      <c r="D24" s="36" t="n"/>
-      <c r="E24" s="36" t="n"/>
-      <c r="F24" s="36" t="n"/>
-      <c r="G24" s="36" t="n"/>
-      <c r="H24" s="36" t="n"/>
-      <c r="I24" s="36" t="n"/>
-      <c r="J24" s="20">
+      <c r="B24" s="31" t="n">
+        <v>-705</v>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>-2694</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>-247</v>
+      </c>
+      <c r="E24" s="31" t="n"/>
+      <c r="F24" s="31" t="n">
+        <v>-2351</v>
+      </c>
+      <c r="G24" s="31" t="n">
+        <v>-310</v>
+      </c>
+      <c r="H24" s="31" t="n"/>
+      <c r="I24" s="31" t="n"/>
+      <c r="J24" s="32">
         <f>SUM(B24:I24)</f>
         <v/>
       </c>
       <c r="K24" s="33" t="inlineStr">
         <is>
-          <t>PREENCHER com os vales adiantados durante agosto.</t>
+          <t>Rubrica 630 (Desconto - verbas / Adiantamento) do holerite da Betel.</t>
         </is>
       </c>
     </row>
@@ -2970,7 +3040,9 @@
       <c r="D28" s="31" t="n">
         <v>-84.29000000000001</v>
       </c>
-      <c r="E28" s="31" t="n"/>
+      <c r="E28" s="31" t="n">
+        <v>-3.24</v>
+      </c>
       <c r="F28" s="31" t="n">
         <v>-84.29000000000001</v>
       </c>
@@ -2985,7 +3057,7 @@
       </c>
       <c r="K28" s="33" t="inlineStr">
         <is>
-          <t>Valor praticado em jul/26. 6% sobre R$ 1.621,00 seria R$ 97,26 — CONFERIR a base usada. JOEL: zerado, mês de férias.</t>
+          <t>Rubrica 604 do holerite da Betel. JOEL: R$ 3,24, com a contrapartida na insuficiência de saldo.</t>
         </is>
       </c>
     </row>
@@ -2995,21 +3067,35 @@
           <t>DESCONTO INSS</t>
         </is>
       </c>
-      <c r="B29" s="36" t="n"/>
-      <c r="C29" s="36" t="n"/>
-      <c r="D29" s="36" t="n"/>
-      <c r="E29" s="36" t="n"/>
-      <c r="F29" s="36" t="n"/>
-      <c r="G29" s="36" t="n"/>
-      <c r="H29" s="36" t="n"/>
-      <c r="I29" s="36" t="n"/>
-      <c r="J29" s="20">
+      <c r="B29" s="31" t="n">
+        <v>-592.27</v>
+      </c>
+      <c r="C29" s="31" t="n">
+        <v>-480.71</v>
+      </c>
+      <c r="D29" s="31" t="n">
+        <v>-336.19</v>
+      </c>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="31" t="n">
+        <v>-337.12</v>
+      </c>
+      <c r="G29" s="31" t="n">
+        <v>-284.48</v>
+      </c>
+      <c r="H29" s="31" t="n">
+        <v>-176.71</v>
+      </c>
+      <c r="I29" s="31" t="n">
+        <v>-230.27</v>
+      </c>
+      <c r="J29" s="32">
         <f>SUM(B29:I29)</f>
         <v/>
       </c>
       <c r="K29" s="33" t="inlineStr">
         <is>
-          <t>A CALCULAR PELA CONTABILIDADE sobre o total de proventos (tabela progressiva vigente).</t>
+          <t>Rubrica 903 do holerite da Betel.</t>
         </is>
       </c>
     </row>
@@ -3019,21 +3105,23 @@
           <t>DESCONTO IRRF</t>
         </is>
       </c>
-      <c r="B30" s="36" t="n"/>
-      <c r="C30" s="36" t="n"/>
-      <c r="D30" s="36" t="n"/>
-      <c r="E30" s="36" t="n"/>
-      <c r="F30" s="36" t="n"/>
-      <c r="G30" s="36" t="n"/>
-      <c r="H30" s="36" t="n"/>
-      <c r="I30" s="36" t="n"/>
-      <c r="J30" s="20">
+      <c r="B30" s="31" t="n">
+        <v>-251.04</v>
+      </c>
+      <c r="C30" s="31" t="n"/>
+      <c r="D30" s="31" t="n"/>
+      <c r="E30" s="31" t="n"/>
+      <c r="F30" s="31" t="n"/>
+      <c r="G30" s="31" t="n"/>
+      <c r="H30" s="31" t="n"/>
+      <c r="I30" s="31" t="n"/>
+      <c r="J30" s="32">
         <f>SUM(B30:I30)</f>
         <v/>
       </c>
       <c r="K30" s="33" t="inlineStr">
         <is>
-          <t>A CALCULAR PELA CONTABILIDADE.</t>
+          <t>Rubrica 914 do holerite da Betel.</t>
         </is>
       </c>
     </row>
@@ -3146,159 +3234,247 @@
         </is>
       </c>
     </row>
-    <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
-        </is>
-      </c>
-      <c r="B34" s="29" t="n"/>
-      <c r="C34" s="29" t="n"/>
-      <c r="D34" s="29" t="n"/>
-      <c r="E34" s="29" t="n"/>
-      <c r="F34" s="29" t="n"/>
-      <c r="G34" s="29" t="n"/>
-      <c r="H34" s="29" t="n"/>
-      <c r="I34" s="29" t="n"/>
-      <c r="J34" s="29" t="n"/>
-      <c r="K34" s="29" t="n"/>
+    <row r="34">
+      <c r="A34" s="30" t="inlineStr">
+        <is>
+          <t>LÍQUIDO DO HOLERITE (BETEL)</t>
+        </is>
+      </c>
+      <c r="B34" s="31" t="n">
+        <v>4100.1</v>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>1676.78</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>3062.58</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>67.54000000000001</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>965.35</v>
+      </c>
+      <c r="G34" s="31" t="n">
+        <v>2704.61</v>
+      </c>
+      <c r="H34" s="31" t="n">
+        <v>2056.96</v>
+      </c>
+      <c r="I34" s="31" t="n">
+        <v>2514.26</v>
+      </c>
+      <c r="J34" s="32">
+        <f>SUM(B34:I34)</f>
+        <v/>
+      </c>
+      <c r="K34" s="33" t="inlineStr">
+        <is>
+          <t>Valor líquido que consta no demonstrativo de pagamento emitido pela Betel Contabilidade.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
-      <c r="A35" s="30" t="inlineStr">
-        <is>
-          <t>VALE TRANSPORTE (compra set/26)</t>
-        </is>
-      </c>
-      <c r="B35" s="36" t="n"/>
-      <c r="C35" s="36" t="n"/>
-      <c r="D35" s="36" t="n"/>
-      <c r="E35" s="36" t="n"/>
-      <c r="F35" s="36" t="n"/>
-      <c r="G35" s="36" t="n"/>
-      <c r="H35" s="36" t="n"/>
-      <c r="I35" s="36" t="n"/>
+      <c r="A35" s="15" t="inlineStr">
+        <is>
+          <t>DIFERENÇA (planilha − holerite)</t>
+        </is>
+      </c>
+      <c r="B35" s="20">
+        <f>ROUND(B33-B34,2)</f>
+        <v/>
+      </c>
+      <c r="C35" s="20">
+        <f>ROUND(C33-C34,2)</f>
+        <v/>
+      </c>
+      <c r="D35" s="20">
+        <f>ROUND(D33-D34,2)</f>
+        <v/>
+      </c>
+      <c r="E35" s="20">
+        <f>ROUND(E33-E34,2)</f>
+        <v/>
+      </c>
+      <c r="F35" s="20">
+        <f>ROUND(F33-F34,2)</f>
+        <v/>
+      </c>
+      <c r="G35" s="20">
+        <f>ROUND(G33-G34,2)</f>
+        <v/>
+      </c>
+      <c r="H35" s="20">
+        <f>ROUND(H33-H34,2)</f>
+        <v/>
+      </c>
+      <c r="I35" s="20">
+        <f>ROUND(I33-I34,2)</f>
+        <v/>
+      </c>
       <c r="J35" s="20">
         <f>SUM(B35:I35)</f>
         <v/>
       </c>
       <c r="K35" s="33" t="inlineStr">
         <is>
-          <t>PREENCHER com as passagens compradas para setembro/2026. JOEL: só a partir de 04/09, quando volta das férias.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="30" t="inlineStr">
-        <is>
-          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
-        </is>
-      </c>
-      <c r="B36" s="36" t="n"/>
-      <c r="C36" s="36" t="n"/>
-      <c r="D36" s="36" t="n"/>
-      <c r="E36" s="36" t="n"/>
-      <c r="F36" s="36" t="n"/>
-      <c r="G36" s="36" t="n"/>
-      <c r="H36" s="36" t="n"/>
-      <c r="I36" s="36" t="n"/>
-      <c r="J36" s="20">
-        <f>SUM(B36:I36)</f>
-        <v/>
-      </c>
-      <c r="K36" s="33" t="inlineStr">
-        <is>
-          <t>PREENCHER conforme escala de domingos/feriados de agosto.</t>
-        </is>
-      </c>
+          <t>Deve ser zero. Os incentivos entram como provento e como desconto, então não afetam o líquido.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="28" t="inlineStr">
+        <is>
+          <t>INFORMATIVO — PAGO PELA EMPRESA, NÃO ENTRA NO HOLERITE</t>
+        </is>
+      </c>
+      <c r="B36" s="29" t="n"/>
+      <c r="C36" s="29" t="n"/>
+      <c r="D36" s="29" t="n"/>
+      <c r="E36" s="29" t="n"/>
+      <c r="F36" s="29" t="n"/>
+      <c r="G36" s="29" t="n"/>
+      <c r="H36" s="29" t="n"/>
+      <c r="I36" s="29" t="n"/>
+      <c r="J36" s="29" t="n"/>
+      <c r="K36" s="29" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="30" t="inlineStr">
         <is>
+          <t>VALE TRANSPORTE (compra set/26)</t>
+        </is>
+      </c>
+      <c r="B37" s="36" t="n"/>
+      <c r="C37" s="36" t="n"/>
+      <c r="D37" s="36" t="n"/>
+      <c r="E37" s="36" t="n"/>
+      <c r="F37" s="36" t="n"/>
+      <c r="G37" s="36" t="n"/>
+      <c r="H37" s="36" t="n"/>
+      <c r="I37" s="36" t="n"/>
+      <c r="J37" s="20">
+        <f>SUM(B37:I37)</f>
+        <v/>
+      </c>
+      <c r="K37" s="33" t="inlineStr">
+        <is>
+          <t>PREENCHER com as passagens compradas para setembro/2026. JOEL: só a partir de 04/09, quando volta das férias.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="30" t="inlineStr">
+        <is>
+          <t>VALE ALIMENTAÇÃO FERIADOS E DOMINGOS</t>
+        </is>
+      </c>
+      <c r="B38" s="36" t="n"/>
+      <c r="C38" s="36" t="n"/>
+      <c r="D38" s="36" t="n"/>
+      <c r="E38" s="36" t="n"/>
+      <c r="F38" s="36" t="n"/>
+      <c r="G38" s="36" t="n"/>
+      <c r="H38" s="36" t="n"/>
+      <c r="I38" s="36" t="n"/>
+      <c r="J38" s="20">
+        <f>SUM(B38:I38)</f>
+        <v/>
+      </c>
+      <c r="K38" s="33" t="inlineStr">
+        <is>
+          <t>PREENCHER conforme escala de domingos/feriados de agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="30" t="inlineStr">
+        <is>
           <t>FÉRIAS PAGAS À PARTE (CONTAS A PAGAR)</t>
         </is>
       </c>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="31" t="n"/>
-      <c r="D37" s="31" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="31" t="n"/>
-      <c r="G37" s="31" t="n"/>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="31" t="n"/>
-      <c r="J37" s="32">
-        <f>SUM(B37:I37)</f>
-        <v/>
-      </c>
-      <c r="K37" s="33" t="inlineStr">
+      <c r="B39" s="31" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
+      <c r="H39" s="31" t="n"/>
+      <c r="I39" s="31" t="n"/>
+      <c r="J39" s="32">
+        <f>SUM(B39:I39)</f>
+        <v/>
+      </c>
+      <c r="K39" s="33" t="inlineStr">
         <is>
           <t>Recibo de férias pago fora do holerite — lembrete para o contas a pagar. JOEL: férias de 01 a 31/08/2026, pagas no início de agosto — informar o valor.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="21" t="inlineStr">
-        <is>
-          <t>LEGENDA</t>
-        </is>
-      </c>
-      <c r="B39" s="7" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="21" t="inlineStr">
-        <is>
-          <t>Célula amarela, texto azul</t>
-        </is>
-      </c>
-      <c r="B40" s="7" t="inlineStr">
-        <is>
-          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="inlineStr">
         <is>
-          <t>Célula laranja</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
-        </is>
-      </c>
+          <t>LEGENDA</t>
+        </is>
+      </c>
+      <c r="B41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="21" t="inlineStr">
         <is>
-          <t>Texto verde</t>
+          <t>Célula amarela, texto azul</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+          <t>valor digitado — PREENCHER ou conferir antes de enviar.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="inlineStr">
         <is>
+          <t>Célula laranja</t>
+        </is>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>valor repetido de julho/2026 — CONFERIR se continua válido em agosto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Texto verde</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>valor puxado da aba BASE INOVAFARMA AGO.26 (não digitar por cima).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="21" t="inlineStr">
+        <is>
           <t>Texto preto em célula verde</t>
         </is>
       </c>
-      <c r="B43" s="7" t="inlineStr">
+      <c r="B45" s="7" t="inlineStr">
         <is>
           <t>resultado de fórmula — não alterar.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:K37"/>
+  <autoFilter ref="A4:K39"/>
   <mergeCells count="7">
+    <mergeCell ref="B45:K45"/>
     <mergeCell ref="B41:K41"/>
-    <mergeCell ref="B40:K40"/>
+    <mergeCell ref="B44:K44"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="B43:K43"/>
-    <mergeCell ref="B39:K39"/>
     <mergeCell ref="B42:K42"/>
     <mergeCell ref="A1:K1"/>
   </mergeCells>
